--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y943"/>
+  <dimension ref="A1:Y951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -86359,7 +86359,7 @@
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G942" t="n">
@@ -86404,7 +86404,17 @@
         <v>105.39</v>
       </c>
       <c r="U942" t="inlineStr"/>
-      <c r="X942" t="inlineStr"/>
+      <c r="V942" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="W942" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="X942" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
       <c r="Y942" t="inlineStr">
         <is>
           <t>IV rank 29% — default sell</t>
@@ -86496,6 +86506,710 @@
       <c r="Y943" t="inlineStr">
         <is>
           <t>IV rank 34% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-09-13T00:21</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="E944" t="n">
+        <v>70</v>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G944" t="n">
+        <v>77274.2</v>
+      </c>
+      <c r="H944" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="I944" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K944" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L944" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M944" t="n">
+        <v>76200</v>
+      </c>
+      <c r="N944" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O944" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P944" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="Q944" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="S944" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="T944" t="n">
+        <v>107.29</v>
+      </c>
+      <c r="U944" t="inlineStr">
+        <is>
+          <t>77274.2</t>
+        </is>
+      </c>
+      <c r="V944" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="W944" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="X944" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Y944" t="inlineStr">
+        <is>
+          <t>IV rank 48% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-09-13T00:21</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="E945" t="n">
+        <v>210</v>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G945" t="n">
+        <v>2525.46</v>
+      </c>
+      <c r="H945" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I945" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K945" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L945" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M945" t="n">
+        <v>2480</v>
+      </c>
+      <c r="N945" t="n">
+        <v>2660</v>
+      </c>
+      <c r="O945" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P945" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="Q945" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="S945" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="T945" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="U945" t="inlineStr">
+        <is>
+          <t>2525.46</t>
+        </is>
+      </c>
+      <c r="V945" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="W945" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="X945" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Y945" t="inlineStr">
+        <is>
+          <t>IV rank 69% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-09-13T05:07</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="E946" t="n">
+        <v>60</v>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G946" t="n">
+        <v>77223.89999999999</v>
+      </c>
+      <c r="H946" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I946" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K946" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L946" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M946" t="n">
+        <v>76600</v>
+      </c>
+      <c r="N946" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O946" t="n">
+        <v>0</v>
+      </c>
+      <c r="P946" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="Q946" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="S946" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T946" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="U946" t="inlineStr">
+        <is>
+          <t>77223.9</t>
+        </is>
+      </c>
+      <c r="V946" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W946" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="X946" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Y946" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-09-13T05:07</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="E947" t="n">
+        <v>210</v>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G947" t="n">
+        <v>2521.36</v>
+      </c>
+      <c r="H947" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="I947" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K947" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L947" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M947" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N947" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O947" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P947" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="Q947" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S947" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="T947" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="U947" t="inlineStr">
+        <is>
+          <t>2521.36</t>
+        </is>
+      </c>
+      <c r="V947" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="W947" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="X947" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Y947" t="inlineStr">
+        <is>
+          <t>IV rank 36% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-09-13T10:15</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="E948" t="n">
+        <v>220</v>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G948" t="n">
+        <v>2483.22</v>
+      </c>
+      <c r="H948" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I948" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K948" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L948" t="n">
+        <v>2490</v>
+      </c>
+      <c r="M948" t="n">
+        <v>2460</v>
+      </c>
+      <c r="N948" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O948" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P948" t="n">
+        <v>0.7483</v>
+      </c>
+      <c r="Q948" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="S948" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="T948" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="U948" t="inlineStr">
+        <is>
+          <t>2483.22</t>
+        </is>
+      </c>
+      <c r="V948" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="W948" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="X948" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Y948" t="inlineStr">
+        <is>
+          <t>IV rank 48% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-09-13T14:32</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E949" t="n">
+        <v>70</v>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G949" t="n">
+        <v>77113.7</v>
+      </c>
+      <c r="H949" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="I949" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K949" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L949" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M949" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N949" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O949" t="n">
+        <v>0</v>
+      </c>
+      <c r="P949" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Q949" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="S949" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="T949" t="n">
+        <v>101.93</v>
+      </c>
+      <c r="U949" t="inlineStr"/>
+      <c r="X949" t="inlineStr"/>
+      <c r="Y949" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-09-13T14:32</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E950" t="n">
+        <v>290</v>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G950" t="n">
+        <v>2491.37</v>
+      </c>
+      <c r="H950" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I950" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K950" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L950" t="n">
+        <v>2490</v>
+      </c>
+      <c r="M950" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N950" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O950" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P950" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="Q950" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="S950" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="T950" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="U950" t="inlineStr"/>
+      <c r="V950" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="W950" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="X950" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Y950" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-09-13T19:47</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E951" t="n">
+        <v>230</v>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G951" t="n">
+        <v>2505.43</v>
+      </c>
+      <c r="H951" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I951" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K951" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L951" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M951" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N951" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O951" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P951" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="Q951" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S951" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="T951" t="n">
+        <v>100.99</v>
+      </c>
+      <c r="U951" t="inlineStr"/>
+      <c r="X951" t="inlineStr"/>
+      <c r="Y951" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
         </is>
       </c>
     </row>
@@ -86566,22 +87280,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="E2" t="n">
-        <v>2529.57</v>
+        <v>2567.42</v>
       </c>
       <c r="F2" t="n">
         <v>5.34</v>
       </c>
       <c r="G2" t="n">
-        <v>252.96</v>
+        <v>256.74</v>
       </c>
     </row>
     <row r="3">
@@ -86795,7 +87509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -87189,7 +87903,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12T12:58</t>
+          <t>2026-09-13T14:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -87204,7 +87918,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -87216,51 +87930,129 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>77293.7</v>
+        <v>77113.7</v>
       </c>
       <c r="H5" t="n">
-        <v>13.7</v>
+        <v>26.95</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>77400</v>
+        <v>77000</v>
       </c>
       <c r="M5" t="n">
-        <v>76200</v>
+        <v>76000</v>
       </c>
       <c r="N5" t="n">
-        <v>81600</v>
+        <v>82000</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1362</v>
+        <v>0.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0181</v>
+        <v>-0.0119</v>
       </c>
       <c r="S5" t="n">
-        <v>6.62</v>
+        <v>10.07</v>
       </c>
       <c r="T5" t="n">
-        <v>105.39</v>
+        <v>101.93</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 29% — default sell</t>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-13T19:47</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>230</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2505.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100.99</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
         </is>
       </c>
     </row>
@@ -87281,7 +88073,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-12T21:48:13.484470 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-13T21:54:26.651452 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y951"/>
+  <dimension ref="A1:Y963"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -82417,7 +82417,7 @@
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G898" t="n">
@@ -82462,7 +82462,17 @@
         <v>96.14</v>
       </c>
       <c r="U898" t="inlineStr"/>
-      <c r="X898" t="inlineStr"/>
+      <c r="V898" t="n">
+        <v>13</v>
+      </c>
+      <c r="W898" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X898" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="Y898" t="inlineStr">
         <is>
           <t>IV rank 97% rich — sell premium</t>
@@ -86995,7 +87005,7 @@
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G949" t="n">
@@ -87039,8 +87049,22 @@
       <c r="T949" t="n">
         <v>101.93</v>
       </c>
-      <c r="U949" t="inlineStr"/>
-      <c r="X949" t="inlineStr"/>
+      <c r="U949" t="inlineStr">
+        <is>
+          <t>76954.7</t>
+        </is>
+      </c>
+      <c r="V949" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="W949" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="X949" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="Y949" t="inlineStr">
         <is>
           <t>IV rank 83% rich — sell premium</t>
@@ -87161,7 +87185,7 @@
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G951" t="n">
@@ -87205,11 +87229,1075 @@
       <c r="T951" t="n">
         <v>100.99</v>
       </c>
-      <c r="U951" t="inlineStr"/>
-      <c r="X951" t="inlineStr"/>
+      <c r="U951" t="inlineStr">
+        <is>
+          <t>2485.12</t>
+        </is>
+      </c>
+      <c r="V951" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="W951" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="X951" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="Y951" t="inlineStr">
         <is>
           <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:53</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E952" t="n">
+        <v>70</v>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G952" t="n">
+        <v>77635.10000000001</v>
+      </c>
+      <c r="H952" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I952" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K952" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L952" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M952" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N952" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O952" t="n">
+        <v>0</v>
+      </c>
+      <c r="P952" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="Q952" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="S952" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="T952" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="U952" t="inlineStr">
+        <is>
+          <t>77635.1</t>
+        </is>
+      </c>
+      <c r="V952" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W952" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="X952" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y952" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:53</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E953" t="n">
+        <v>220</v>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G953" t="n">
+        <v>2514.83</v>
+      </c>
+      <c r="H953" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="I953" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K953" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L953" t="n">
+        <v>2510</v>
+      </c>
+      <c r="M953" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N953" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O953" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P953" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="Q953" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S953" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="T953" t="n">
+        <v>101.84</v>
+      </c>
+      <c r="U953" t="inlineStr">
+        <is>
+          <t>2514.83</t>
+        </is>
+      </c>
+      <c r="V953" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="W953" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="X953" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y953" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:17</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E954" t="n">
+        <v>60</v>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G954" t="n">
+        <v>78028.5</v>
+      </c>
+      <c r="H954" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I954" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K954" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L954" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M954" t="n">
+        <v>77800</v>
+      </c>
+      <c r="N954" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O954" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P954" t="n">
+        <v>0.8603</v>
+      </c>
+      <c r="Q954" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="S954" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T954" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="U954" t="inlineStr">
+        <is>
+          <t>78028.5</t>
+        </is>
+      </c>
+      <c r="V954" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W954" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="X954" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y954" t="inlineStr">
+        <is>
+          <t>IV rank 35% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:17</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E955" t="n">
+        <v>4310</v>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G955" t="n">
+        <v>78028.5</v>
+      </c>
+      <c r="H955" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I955" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K955" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L955" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M955" t="n">
+        <v>77800</v>
+      </c>
+      <c r="N955" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O955" t="n">
+        <v>0</v>
+      </c>
+      <c r="P955" t="n">
+        <v>-0.6415</v>
+      </c>
+      <c r="Q955" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="S955" t="n">
+        <v>-99.98999999999999</v>
+      </c>
+      <c r="T955" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="U955" t="inlineStr">
+        <is>
+          <t>78028.5</t>
+        </is>
+      </c>
+      <c r="V955" t="n">
+        <v>-104.3</v>
+      </c>
+      <c r="W955" t="n">
+        <v>-10.43</v>
+      </c>
+      <c r="X955" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y955" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:17</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E956" t="n">
+        <v>490</v>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G956" t="n">
+        <v>78028.5</v>
+      </c>
+      <c r="H956" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I956" t="n">
+        <v>1</v>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K956" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L956" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M956" t="n">
+        <v>77800</v>
+      </c>
+      <c r="N956" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O956" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P956" t="n">
+        <v>-0.1847</v>
+      </c>
+      <c r="Q956" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R956" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S956" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="T956" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="U956" t="inlineStr">
+        <is>
+          <t>78028.5</t>
+        </is>
+      </c>
+      <c r="V956" t="n">
+        <v>-84.62</v>
+      </c>
+      <c r="W956" t="n">
+        <v>-8.462</v>
+      </c>
+      <c r="X956" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y956" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 2.0 · 1.7h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:17</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E957" t="n">
+        <v>4920</v>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G957" t="n">
+        <v>2519.08</v>
+      </c>
+      <c r="H957" t="n">
+        <v>16</v>
+      </c>
+      <c r="I957" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K957" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L957" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M957" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N957" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O957" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P957" t="n">
+        <v>-0.4071</v>
+      </c>
+      <c r="Q957" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="S957" t="n">
+        <v>-99.88</v>
+      </c>
+      <c r="T957" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="U957" t="inlineStr">
+        <is>
+          <t>2519.08</t>
+        </is>
+      </c>
+      <c r="V957" t="n">
+        <v>-103.81</v>
+      </c>
+      <c r="W957" t="n">
+        <v>-10.381</v>
+      </c>
+      <c r="X957" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y957" t="inlineStr">
+        <is>
+          <t>IV rank 12% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:17</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E958" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G958" t="n">
+        <v>2519.08</v>
+      </c>
+      <c r="H958" t="n">
+        <v>16</v>
+      </c>
+      <c r="I958" t="n">
+        <v>1</v>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K958" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L958" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M958" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N958" t="n">
+        <v>2640</v>
+      </c>
+      <c r="O958" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="P958" t="n">
+        <v>-0.2331</v>
+      </c>
+      <c r="Q958" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="R958" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="S958" t="n">
+        <v>-99.94</v>
+      </c>
+      <c r="T958" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="U958" t="inlineStr">
+        <is>
+          <t>2519.08</t>
+        </is>
+      </c>
+      <c r="V958" t="n">
+        <v>-432.28</v>
+      </c>
+      <c r="W958" t="n">
+        <v>-43.228</v>
+      </c>
+      <c r="X958" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y958" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 9.7 · 1.7h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:26</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E959" t="n">
+        <v>70</v>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G959" t="n">
+        <v>78743.5</v>
+      </c>
+      <c r="H959" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="I959" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K959" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L959" t="n">
+        <v>78200</v>
+      </c>
+      <c r="M959" t="n">
+        <v>75600</v>
+      </c>
+      <c r="N959" t="n">
+        <v>80000</v>
+      </c>
+      <c r="O959" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P959" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="Q959" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="S959" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="T959" t="n">
+        <v>104.94</v>
+      </c>
+      <c r="U959" t="inlineStr"/>
+      <c r="X959" t="inlineStr"/>
+      <c r="Y959" t="inlineStr">
+        <is>
+          <t>IV rank 77% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:26</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E960" t="n">
+        <v>60</v>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G960" t="n">
+        <v>78743.5</v>
+      </c>
+      <c r="H960" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="I960" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K960" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L960" t="n">
+        <v>81000</v>
+      </c>
+      <c r="M960" t="n">
+        <v>81000</v>
+      </c>
+      <c r="N960" t="n">
+        <v>89000</v>
+      </c>
+      <c r="O960" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P960" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="Q960" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="S960" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="T960" t="n">
+        <v>102.27</v>
+      </c>
+      <c r="U960" t="inlineStr"/>
+      <c r="X960" t="inlineStr"/>
+      <c r="Y960" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:26</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E961" t="n">
+        <v>190</v>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G961" t="n">
+        <v>2523.49</v>
+      </c>
+      <c r="H961" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="I961" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K961" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L961" t="n">
+        <v>2510</v>
+      </c>
+      <c r="M961" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N961" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O961" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P961" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="Q961" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="S961" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="T961" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="U961" t="inlineStr"/>
+      <c r="V961" t="n">
+        <v>-38.49</v>
+      </c>
+      <c r="W961" t="n">
+        <v>-3.849</v>
+      </c>
+      <c r="X961" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y961" t="inlineStr">
+        <is>
+          <t>IV rank 88% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:23</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E962" t="n">
+        <v>280</v>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G962" t="n">
+        <v>2598.25</v>
+      </c>
+      <c r="H962" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="I962" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K962" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L962" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M962" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N962" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O962" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="P962" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="Q962" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="S962" t="n">
+        <v>-99.31999999999999</v>
+      </c>
+      <c r="T962" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="U962" t="inlineStr"/>
+      <c r="X962" t="inlineStr"/>
+      <c r="Y962" t="inlineStr">
+        <is>
+          <t>trending up +5.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:23</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E963" t="n">
+        <v>330</v>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G963" t="n">
+        <v>2598.25</v>
+      </c>
+      <c r="H963" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="I963" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K963" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L963" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M963" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N963" t="n">
+        <v>2900</v>
+      </c>
+      <c r="O963" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="P963" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="Q963" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S963" t="n">
+        <v>-98.59999999999999</v>
+      </c>
+      <c r="T963" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="U963" t="inlineStr"/>
+      <c r="X963" t="inlineStr"/>
+      <c r="Y963" t="inlineStr">
+        <is>
+          <t>trending up +5.6% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -87280,22 +88368,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C2" t="n">
-        <v>96.7</v>
+        <v>96.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.29</v>
+        <v>5.03</v>
       </c>
       <c r="E2" t="n">
-        <v>2567.42</v>
+        <v>2569.02</v>
       </c>
       <c r="F2" t="n">
-        <v>5.34</v>
+        <v>5.28</v>
       </c>
       <c r="G2" t="n">
-        <v>256.74</v>
+        <v>256.9</v>
       </c>
     </row>
     <row r="3">
@@ -87380,22 +88468,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="E6" t="n">
-        <v>-280.58</v>
+        <v>-267.58</v>
       </c>
       <c r="F6" t="n">
-        <v>-11.22</v>
+        <v>-10.29</v>
       </c>
       <c r="G6" t="n">
-        <v>-28.06</v>
+        <v>-26.76</v>
       </c>
     </row>
     <row r="7">
@@ -87430,22 +88518,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="D8" t="n">
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>-3290.43</v>
+        <v>-3807.33</v>
       </c>
       <c r="F8" t="n">
-        <v>-60.93</v>
+        <v>-67.98999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-329.04</v>
+        <v>-380.73</v>
       </c>
     </row>
     <row r="9">
@@ -87455,7 +88543,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>1.3</v>
@@ -87464,13 +88552,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-7844.78</v>
+        <v>-7948.59</v>
       </c>
       <c r="F9" t="n">
-        <v>-100.57</v>
+        <v>-100.62</v>
       </c>
       <c r="G9" t="n">
-        <v>-784.48</v>
+        <v>-794.86</v>
       </c>
     </row>
     <row r="10">
@@ -87480,7 +88568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -87489,13 +88577,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-9668.76</v>
+        <v>-9773.059999999999</v>
       </c>
       <c r="F10" t="n">
         <v>-103.97</v>
       </c>
       <c r="G10" t="n">
-        <v>-966.88</v>
+        <v>-977.3099999999999</v>
       </c>
     </row>
   </sheetData>
@@ -87509,7 +88597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -87674,7 +88762,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -87688,7 +88776,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -87696,13 +88784,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>78972.60000000001</v>
+        <v>2483.49</v>
       </c>
       <c r="H2" t="n">
-        <v>36.35</v>
+        <v>47.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.679</v>
+        <v>0.345</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -87710,54 +88798,54 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="L2" t="n">
-        <v>81000</v>
+        <v>2500</v>
       </c>
       <c r="M2" t="n">
-        <v>81500</v>
+        <v>2350</v>
       </c>
       <c r="N2" t="n">
-        <v>81500</v>
+        <v>2900</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0339</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.021</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>23.86</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>96.14</v>
+        <v>0</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>IV rank 97% rich — sell premium</t>
+          <t>IV rank 92% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08T00:24</t>
+          <t>2026-09-08T13:46</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -87766,7 +88854,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -87774,13 +88862,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2483.49</v>
+        <v>77780.39999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>47.8</v>
+        <v>37.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.345</v>
+        <v>0.612</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -87788,44 +88876,44 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="L3" t="n">
-        <v>2500</v>
+        <v>81000</v>
       </c>
       <c r="M3" t="n">
-        <v>2350</v>
+        <v>81500</v>
       </c>
       <c r="N3" t="n">
-        <v>2900</v>
+        <v>87000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-98.78</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>98.78</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 92% rich — sell premium</t>
+          <t>trending down -4.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08T13:46</t>
+          <t>2026-09-14T16:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -87835,16 +88923,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -87852,58 +88940,58 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>77780.39999999999</v>
+        <v>78743.5</v>
       </c>
       <c r="H4" t="n">
-        <v>37.6</v>
+        <v>24.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.612</v>
+        <v>0.661</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.12</v>
+        <v>2.91</v>
       </c>
       <c r="L4" t="n">
-        <v>81000</v>
+        <v>78200</v>
       </c>
       <c r="M4" t="n">
-        <v>81500</v>
+        <v>75600</v>
       </c>
       <c r="N4" t="n">
-        <v>87000</v>
+        <v>80000</v>
       </c>
       <c r="O4" t="n">
         <v>0.0001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.1237</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0044</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-98.78</v>
+        <v>7.06</v>
       </c>
       <c r="T4" t="n">
-        <v>98.78</v>
+        <v>104.94</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending down -4.2% — skewed fly</t>
+          <t>IV rank 77% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13T14:32</t>
+          <t>2026-09-14T16:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -87913,16 +89001,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -87930,58 +89018,58 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>77113.7</v>
+        <v>78743.5</v>
       </c>
       <c r="H5" t="n">
-        <v>26.95</v>
+        <v>36.85</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="L5" t="n">
-        <v>77000</v>
+        <v>81000</v>
       </c>
       <c r="M5" t="n">
-        <v>76000</v>
+        <v>81000</v>
       </c>
       <c r="N5" t="n">
-        <v>82000</v>
+        <v>89000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.17</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0155</v>
       </c>
       <c r="S5" t="n">
-        <v>10.07</v>
+        <v>17.73</v>
       </c>
       <c r="T5" t="n">
-        <v>101.93</v>
+        <v>102.27</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 83% rich — sell premium</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13T19:47</t>
+          <t>2026-09-14T20:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -87991,16 +89079,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -88008,51 +89096,129 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2505.43</v>
+        <v>2598.25</v>
       </c>
       <c r="H6" t="n">
-        <v>29.25</v>
+        <v>48.35</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.832</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="L6" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M6" t="n">
         <v>2500</v>
       </c>
-      <c r="M6" t="n">
-        <v>2400</v>
-      </c>
       <c r="N6" t="n">
-        <v>2800</v>
+        <v>2680</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003</v>
+        <v>-0.0029</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1142</v>
+        <v>0.0573</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0043</v>
+        <v>-0.0016</v>
       </c>
       <c r="S6" t="n">
-        <v>14.01</v>
+        <v>-99.31999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>100.99</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 67% — default sell</t>
+          <t>trending up +5.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>330</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2598.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-98.59999999999999</v>
+      </c>
+      <c r="T7" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>trending up +5.6% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -88073,7 +89239,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13T21:54:26.651452 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-14T22:50:30.831314 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y963"/>
+  <dimension ref="A1:Y971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -83039,7 +83039,7 @@
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G905" t="n">
@@ -83084,7 +83084,17 @@
         <v>98.78</v>
       </c>
       <c r="U905" t="inlineStr"/>
-      <c r="X905" t="inlineStr"/>
+      <c r="V905" t="n">
+        <v>-60.25</v>
+      </c>
+      <c r="W905" t="n">
+        <v>-6.025</v>
+      </c>
+      <c r="X905" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="Y905" t="inlineStr">
         <is>
           <t>trending down -4.2% — skewed fly</t>
@@ -87927,7 +87937,7 @@
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G959" t="n">
@@ -87971,8 +87981,22 @@
       <c r="T959" t="n">
         <v>104.94</v>
       </c>
-      <c r="U959" t="inlineStr"/>
-      <c r="X959" t="inlineStr"/>
+      <c r="U959" t="inlineStr">
+        <is>
+          <t>77984.1</t>
+        </is>
+      </c>
+      <c r="V959" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W959" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="X959" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="Y959" t="inlineStr">
         <is>
           <t>IV rank 77% rich — sell premium</t>
@@ -88005,7 +88029,7 @@
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G960" t="n">
@@ -88050,7 +88074,17 @@
         <v>102.27</v>
       </c>
       <c r="U960" t="inlineStr"/>
-      <c r="X960" t="inlineStr"/>
+      <c r="V960" t="n">
+        <v>-22.56</v>
+      </c>
+      <c r="W960" t="n">
+        <v>-2.256</v>
+      </c>
+      <c r="X960" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="Y960" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -88171,7 +88205,7 @@
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G962" t="n">
@@ -88215,8 +88249,22 @@
       <c r="T962" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="U962" t="inlineStr"/>
-      <c r="X962" t="inlineStr"/>
+      <c r="U962" t="inlineStr">
+        <is>
+          <t>2514.78</t>
+        </is>
+      </c>
+      <c r="V962" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="W962" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="X962" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="Y962" t="inlineStr">
         <is>
           <t>trending up +5.6% — skewed fly</t>
@@ -88298,6 +88346,682 @@
       <c r="Y963" t="inlineStr">
         <is>
           <t>trending up +5.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:16</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E964" t="n">
+        <v>180</v>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G964" t="n">
+        <v>2525.47</v>
+      </c>
+      <c r="H964" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I964" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K964" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L964" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M964" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N964" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O964" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P964" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="Q964" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S964" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="T964" t="n">
+        <v>97.88</v>
+      </c>
+      <c r="U964" t="inlineStr">
+        <is>
+          <t>2514.78</t>
+        </is>
+      </c>
+      <c r="V964" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="W964" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="X964" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Y964" t="inlineStr">
+        <is>
+          <t>IV rank 67% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:39</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E965" t="n">
+        <v>60</v>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G965" t="n">
+        <v>77984.10000000001</v>
+      </c>
+      <c r="H965" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="I965" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K965" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="L965" t="n">
+        <v>77500</v>
+      </c>
+      <c r="M965" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N965" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O965" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P965" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="Q965" t="n">
+        <v>-0.0193</v>
+      </c>
+      <c r="S965" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="T965" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="U965" t="inlineStr"/>
+      <c r="X965" t="inlineStr"/>
+      <c r="Y965" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:39</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E966" t="n">
+        <v>120</v>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G966" t="n">
+        <v>2514.78</v>
+      </c>
+      <c r="H966" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="I966" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K966" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="L966" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M966" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N966" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O966" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P966" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="Q966" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S966" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="T966" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="U966" t="inlineStr"/>
+      <c r="X966" t="inlineStr"/>
+      <c r="Y966" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-09-15T06:42</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E967" t="n">
+        <v>70</v>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G967" t="n">
+        <v>77442.8</v>
+      </c>
+      <c r="H967" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="I967" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K967" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L967" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M967" t="n">
+        <v>77000</v>
+      </c>
+      <c r="N967" t="n">
+        <v>80000</v>
+      </c>
+      <c r="O967" t="n">
+        <v>0</v>
+      </c>
+      <c r="P967" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="Q967" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="S967" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="T967" t="n">
+        <v>104.59</v>
+      </c>
+      <c r="U967" t="inlineStr">
+        <is>
+          <t>77442.8</t>
+        </is>
+      </c>
+      <c r="V967" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="W967" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="X967" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Y967" t="inlineStr">
+        <is>
+          <t>IV rank 82% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-09-15T06:42</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E968" t="n">
+        <v>220</v>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G968" t="n">
+        <v>2489.57</v>
+      </c>
+      <c r="H968" t="n">
+        <v>35</v>
+      </c>
+      <c r="I968" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K968" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L968" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M968" t="n">
+        <v>2450</v>
+      </c>
+      <c r="N968" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O968" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P968" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="Q968" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S968" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="T968" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="U968" t="inlineStr">
+        <is>
+          <t>2489.57</t>
+        </is>
+      </c>
+      <c r="V968" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="W968" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="X968" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Y968" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-09-15T12:09</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E969" t="n">
+        <v>70</v>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G969" t="n">
+        <v>76869.39999999999</v>
+      </c>
+      <c r="H969" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="I969" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K969" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L969" t="n">
+        <v>77200</v>
+      </c>
+      <c r="M969" t="n">
+        <v>75200</v>
+      </c>
+      <c r="N969" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O969" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P969" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="Q969" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="S969" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="T969" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U969" t="inlineStr"/>
+      <c r="V969" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W969" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="X969" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Y969" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-09-15T12:09</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E970" t="n">
+        <v>290</v>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G970" t="n">
+        <v>2477.61</v>
+      </c>
+      <c r="H970" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I970" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K970" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L970" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M970" t="n">
+        <v>2420</v>
+      </c>
+      <c r="N970" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O970" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P970" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="Q970" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S970" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="T970" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="U970" t="inlineStr"/>
+      <c r="X970" t="inlineStr"/>
+      <c r="Y970" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-09-15T20:03</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E971" t="n">
+        <v>70</v>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G971" t="n">
+        <v>76172.89999999999</v>
+      </c>
+      <c r="H971" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I971" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K971" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L971" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M971" t="n">
+        <v>75400</v>
+      </c>
+      <c r="N971" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O971" t="n">
+        <v>0</v>
+      </c>
+      <c r="P971" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="Q971" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="S971" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="T971" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="U971" t="inlineStr"/>
+      <c r="X971" t="inlineStr"/>
+      <c r="Y971" t="inlineStr">
+        <is>
+          <t>IV rank 95% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -88368,22 +89092,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C2" t="n">
         <v>96.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="E2" t="n">
-        <v>2569.02</v>
+        <v>2608.83</v>
       </c>
       <c r="F2" t="n">
-        <v>5.28</v>
+        <v>5.3</v>
       </c>
       <c r="G2" t="n">
-        <v>256.9</v>
+        <v>260.88</v>
       </c>
     </row>
     <row r="3">
@@ -88443,22 +89167,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>69.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="E5" t="n">
-        <v>-234.21</v>
+        <v>-256.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.23</v>
+        <v>-1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>-23.42</v>
+        <v>-25.61</v>
       </c>
     </row>
     <row r="6">
@@ -88468,22 +89192,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>65.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>-267.58</v>
+        <v>-290.14</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.29</v>
+        <v>-10.75</v>
       </c>
       <c r="G6" t="n">
-        <v>-26.76</v>
+        <v>-29.01</v>
       </c>
     </row>
     <row r="7">
@@ -88493,22 +89217,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>23.1</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="E7" t="n">
-        <v>-540.03</v>
+        <v>-600.28</v>
       </c>
       <c r="F7" t="n">
-        <v>-41.54</v>
+        <v>-42.88</v>
       </c>
       <c r="G7" t="n">
-        <v>-54</v>
+        <v>-60.03</v>
       </c>
     </row>
     <row r="8">
@@ -88835,12 +89559,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08T13:46</t>
+          <t>2026-09-14T20:23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -88854,7 +89578,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -88862,58 +89586,58 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>77780.39999999999</v>
+        <v>2598.25</v>
       </c>
       <c r="H3" t="n">
-        <v>37.6</v>
+        <v>59.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.612</v>
+        <v>0.652</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.12</v>
+        <v>0.85</v>
       </c>
       <c r="L3" t="n">
-        <v>81000</v>
+        <v>2500</v>
       </c>
       <c r="M3" t="n">
-        <v>81500</v>
+        <v>2300</v>
       </c>
       <c r="N3" t="n">
-        <v>87000</v>
+        <v>2900</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001</v>
+        <v>-0.0015</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0044</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="S3" t="n">
-        <v>-98.78</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>98.78</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending down -4.2% — skewed fly</t>
+          <t>trending up +5.6% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14T16:26</t>
+          <t>2026-09-15T01:39</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -88923,16 +89647,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -88940,13 +89664,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>78743.5</v>
+        <v>77984.10000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>24.05</v>
+        <v>36.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.661</v>
+        <v>0.677</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -88954,49 +89678,49 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.91</v>
+        <v>5.94</v>
       </c>
       <c r="L4" t="n">
-        <v>78200</v>
+        <v>77500</v>
       </c>
       <c r="M4" t="n">
-        <v>75600</v>
+        <v>51000</v>
       </c>
       <c r="N4" t="n">
-        <v>80000</v>
+        <v>93000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1237</v>
+        <v>0.0301</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0193</v>
       </c>
       <c r="S4" t="n">
-        <v>7.06</v>
+        <v>22.19</v>
       </c>
       <c r="T4" t="n">
-        <v>104.94</v>
+        <v>97.81</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 77% rich — sell premium</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14T16:26</t>
+          <t>2026-09-15T01:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -89006,11 +89730,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -89018,45 +89742,45 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>78743.5</v>
+        <v>2514.78</v>
       </c>
       <c r="H5" t="n">
-        <v>36.85</v>
+        <v>53.55</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.57</v>
+        <v>3.34</v>
       </c>
       <c r="L5" t="n">
-        <v>81000</v>
+        <v>2400</v>
       </c>
       <c r="M5" t="n">
-        <v>81000</v>
+        <v>1500</v>
       </c>
       <c r="N5" t="n">
-        <v>89000</v>
+        <v>3100</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>-0.0001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0107</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0046</v>
       </c>
       <c r="S5" t="n">
-        <v>17.73</v>
+        <v>16.15</v>
       </c>
       <c r="T5" t="n">
-        <v>102.27</v>
+        <v>103.85</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -89069,7 +89793,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14T20:23</t>
+          <t>2026-09-15T12:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -89079,16 +89803,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -89096,77 +89820,77 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2598.25</v>
+        <v>2477.61</v>
       </c>
       <c r="H6" t="n">
-        <v>48.35</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.832</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.99</v>
+        <v>0.48</v>
       </c>
       <c r="L6" t="n">
-        <v>2520</v>
+        <v>2480</v>
       </c>
       <c r="M6" t="n">
-        <v>2500</v>
+        <v>2420</v>
       </c>
       <c r="N6" t="n">
-        <v>2680</v>
+        <v>2720</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0029</v>
+        <v>-0.0001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0573</v>
+        <v>0.055</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0016</v>
+        <v>-0.0017</v>
       </c>
       <c r="S6" t="n">
-        <v>-99.31999999999999</v>
+        <v>16.99</v>
       </c>
       <c r="T6" t="n">
-        <v>99.31999999999999</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +5.6% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14T20:23</t>
+          <t>2026-09-15T20:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -89174,51 +89898,51 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2598.25</v>
+        <v>76172.89999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>59.2</v>
+        <v>31.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.85</v>
+        <v>0.29</v>
       </c>
       <c r="L7" t="n">
-        <v>2500</v>
+        <v>76400</v>
       </c>
       <c r="M7" t="n">
-        <v>2300</v>
+        <v>75400</v>
       </c>
       <c r="N7" t="n">
-        <v>2900</v>
+        <v>81600</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0044</v>
+        <v>0.2767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002</v>
+        <v>-0.0103</v>
       </c>
       <c r="S7" t="n">
-        <v>-98.59999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="T7" t="n">
-        <v>98.59999999999999</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending up +5.6% — skewed fly</t>
+          <t>IV rank 95% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -89239,7 +89963,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-14T22:50:30.831314 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-15T22:31:37.106429 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y971"/>
+  <dimension ref="A1:Y984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -88895,7 +88895,7 @@
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G970" t="n">
@@ -88939,8 +88939,22 @@
       <c r="T970" t="n">
         <v>99.01000000000001</v>
       </c>
-      <c r="U970" t="inlineStr"/>
-      <c r="X970" t="inlineStr"/>
+      <c r="U970" t="inlineStr">
+        <is>
+          <t>2401.29</t>
+        </is>
+      </c>
+      <c r="V970" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="W970" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="X970" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="Y970" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -88973,7 +88987,7 @@
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G971" t="n">
@@ -89017,11 +89031,1121 @@
       <c r="T971" t="n">
         <v>99.84999999999999</v>
       </c>
-      <c r="U971" t="inlineStr"/>
-      <c r="X971" t="inlineStr"/>
+      <c r="U971" t="inlineStr">
+        <is>
+          <t>75828.1</t>
+        </is>
+      </c>
+      <c r="V971" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="W971" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="X971" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="Y971" t="inlineStr">
         <is>
           <t>IV rank 95% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:00</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E972" t="n">
+        <v>240</v>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G972" t="n">
+        <v>2401.29</v>
+      </c>
+      <c r="H972" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I972" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K972" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L972" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M972" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N972" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O972" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="P972" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="Q972" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="S972" t="n">
+        <v>-99.05</v>
+      </c>
+      <c r="T972" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="U972" t="inlineStr">
+        <is>
+          <t>2401.29</t>
+        </is>
+      </c>
+      <c r="V972" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="W972" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="X972" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y972" t="inlineStr">
+        <is>
+          <t>trending down -4.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:00</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E973" t="n">
+        <v>2620</v>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G973" t="n">
+        <v>2401.29</v>
+      </c>
+      <c r="H973" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="I973" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K973" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L973" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M973" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N973" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O973" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P973" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Q973" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="S973" t="n">
+        <v>-99.81999999999999</v>
+      </c>
+      <c r="T973" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="U973" t="inlineStr"/>
+      <c r="X973" t="inlineStr"/>
+      <c r="Y973" t="inlineStr">
+        <is>
+          <t>trending down -4.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:20</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E974" t="n">
+        <v>3530</v>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G974" t="n">
+        <v>75969.89999999999</v>
+      </c>
+      <c r="H974" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I974" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K974" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L974" t="n">
+        <v>75800</v>
+      </c>
+      <c r="M974" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N974" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O974" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P974" t="n">
+        <v>-1.5544</v>
+      </c>
+      <c r="Q974" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S974" t="n">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="T974" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U974" t="inlineStr">
+        <is>
+          <t>75969.9</t>
+        </is>
+      </c>
+      <c r="V974" t="n">
+        <v>-104.13</v>
+      </c>
+      <c r="W974" t="n">
+        <v>-10.414</v>
+      </c>
+      <c r="X974" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y974" t="inlineStr">
+        <is>
+          <t>IV rank 11% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:20</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E975" t="n">
+        <v>32440</v>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G975" t="n">
+        <v>75969.89999999999</v>
+      </c>
+      <c r="H975" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I975" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K975" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L975" t="n">
+        <v>75800</v>
+      </c>
+      <c r="M975" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N975" t="n">
+        <v>81600</v>
+      </c>
+      <c r="O975" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P975" t="n">
+        <v>-0.3589</v>
+      </c>
+      <c r="Q975" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="S975" t="n">
+        <v>-100.56</v>
+      </c>
+      <c r="T975" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="U975" t="inlineStr">
+        <is>
+          <t>75969.9</t>
+        </is>
+      </c>
+      <c r="V975" t="n">
+        <v>-103.81</v>
+      </c>
+      <c r="W975" t="n">
+        <v>-10.381</v>
+      </c>
+      <c r="X975" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y975" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:20</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E976" t="n">
+        <v>4580</v>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G976" t="n">
+        <v>2406.46</v>
+      </c>
+      <c r="H976" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I976" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K976" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L976" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M976" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N976" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O976" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="P976" t="n">
+        <v>-0.7875</v>
+      </c>
+      <c r="Q976" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="S976" t="n">
+        <v>-99.84</v>
+      </c>
+      <c r="T976" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="U976" t="inlineStr">
+        <is>
+          <t>2406.46</t>
+        </is>
+      </c>
+      <c r="V976" t="n">
+        <v>-103.97</v>
+      </c>
+      <c r="W976" t="n">
+        <v>-10.397</v>
+      </c>
+      <c r="X976" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y976" t="inlineStr">
+        <is>
+          <t>IV rank 4% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:21</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E977" t="n">
+        <v>160</v>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G977" t="n">
+        <v>2406.46</v>
+      </c>
+      <c r="H977" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I977" t="n">
+        <v>1</v>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K977" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L977" t="n">
+        <v>2410</v>
+      </c>
+      <c r="M977" t="n">
+        <v>2360</v>
+      </c>
+      <c r="N977" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O977" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="P977" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q977" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="S977" t="n">
+        <v>-101.86</v>
+      </c>
+      <c r="T977" t="n">
+        <v>101.86</v>
+      </c>
+      <c r="U977" t="inlineStr">
+        <is>
+          <t>2406.46</t>
+        </is>
+      </c>
+      <c r="V977" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="W977" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="X977" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y977" t="inlineStr">
+        <is>
+          <t>trending down -4.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:28</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E978" t="n">
+        <v>70</v>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G978" t="n">
+        <v>75717.3</v>
+      </c>
+      <c r="H978" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="I978" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K978" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L978" t="n">
+        <v>76000</v>
+      </c>
+      <c r="M978" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N978" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O978" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P978" t="n">
+        <v>0.2089</v>
+      </c>
+      <c r="Q978" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="S978" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="T978" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="U978" t="inlineStr"/>
+      <c r="V978" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="W978" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="X978" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y978" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:28</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E979" t="n">
+        <v>170</v>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G979" t="n">
+        <v>2389.05</v>
+      </c>
+      <c r="H979" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="I979" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K979" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L979" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M979" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N979" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O979" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P979" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="Q979" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="S979" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T979" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="U979" t="inlineStr"/>
+      <c r="V979" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W979" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X979" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y979" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:28</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E980" t="n">
+        <v>480</v>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G980" t="n">
+        <v>2389.05</v>
+      </c>
+      <c r="H980" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="I980" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K980" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L980" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M980" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N980" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O980" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P980" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="Q980" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S980" t="n">
+        <v>-99.02</v>
+      </c>
+      <c r="T980" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="U980" t="inlineStr"/>
+      <c r="X980" t="inlineStr"/>
+      <c r="Y980" t="inlineStr">
+        <is>
+          <t>trending down -5.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:28</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E981" t="n">
+        <v>1</v>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G981" t="n">
+        <v>4348.64</v>
+      </c>
+      <c r="S981" t="n">
+        <v>0</v>
+      </c>
+      <c r="T981" t="n">
+        <v>10</v>
+      </c>
+      <c r="U981" t="inlineStr">
+        <is>
+          <t>4322.04</t>
+        </is>
+      </c>
+      <c r="V981" t="n">
+        <v>-11.93</v>
+      </c>
+      <c r="W981" t="n">
+        <v>-1.193</v>
+      </c>
+      <c r="X981" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y981" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:00</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E982" t="n">
+        <v>240</v>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G982" t="n">
+        <v>2407.33</v>
+      </c>
+      <c r="H982" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="I982" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K982" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L982" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M982" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N982" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O982" t="n">
+        <v>0</v>
+      </c>
+      <c r="P982" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="Q982" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S982" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="T982" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="U982" t="inlineStr"/>
+      <c r="V982" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="W982" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="X982" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Y982" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-09-16T22:09</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E983" t="n">
+        <v>70</v>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G983" t="n">
+        <v>75678.8</v>
+      </c>
+      <c r="H983" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="I983" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K983" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L983" t="n">
+        <v>76000</v>
+      </c>
+      <c r="M983" t="n">
+        <v>73600</v>
+      </c>
+      <c r="N983" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O983" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P983" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="Q983" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="S983" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="T983" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="U983" t="inlineStr"/>
+      <c r="X983" t="inlineStr"/>
+      <c r="Y983" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-09-16T22:09</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E984" t="n">
+        <v>230</v>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G984" t="n">
+        <v>2390.23</v>
+      </c>
+      <c r="H984" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="I984" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K984" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L984" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M984" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N984" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O984" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P984" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="Q984" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S984" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="T984" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="U984" t="inlineStr"/>
+      <c r="X984" t="inlineStr"/>
+      <c r="Y984" t="inlineStr">
+        <is>
+          <t>IV rank 73% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -89092,22 +90216,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C2" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1</v>
+        <v>5.13</v>
       </c>
       <c r="E2" t="n">
-        <v>2608.83</v>
+        <v>2652.78</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3</v>
+        <v>5.34</v>
       </c>
       <c r="G2" t="n">
-        <v>260.88</v>
+        <v>265.28</v>
       </c>
     </row>
     <row r="3">
@@ -89117,22 +90241,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="E3" t="n">
-        <v>-24.82</v>
+        <v>-36.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.76</v>
+        <v>-3.68</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.48</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="4">
@@ -89167,22 +90291,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-256.11</v>
+        <v>-248.13</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.34</v>
+        <v>-1.29</v>
       </c>
       <c r="G5" t="n">
-        <v>-25.61</v>
+        <v>-24.81</v>
       </c>
     </row>
     <row r="6">
@@ -89267,22 +90391,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-7948.59</v>
+        <v>-8156.69</v>
       </c>
       <c r="F9" t="n">
-        <v>-100.62</v>
+        <v>-100.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-794.86</v>
+        <v>-815.67</v>
       </c>
     </row>
     <row r="10">
@@ -89292,7 +90416,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -89301,13 +90425,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-9773.059999999999</v>
+        <v>-9876.870000000001</v>
       </c>
       <c r="F10" t="n">
         <v>-103.97</v>
       </c>
       <c r="G10" t="n">
-        <v>-977.3099999999999</v>
+        <v>-987.6900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -89321,7 +90445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -89793,7 +90917,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15T12:09</t>
+          <t>2026-09-16T01:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -89803,16 +90927,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>290</v>
+        <v>2620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -89820,77 +90944,77 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2477.61</v>
+        <v>2401.29</v>
       </c>
       <c r="H6" t="n">
-        <v>64.09999999999999</v>
+        <v>52.85</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.517</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.48</v>
+        <v>4.25</v>
       </c>
       <c r="L6" t="n">
-        <v>2480</v>
+        <v>2500</v>
       </c>
       <c r="M6" t="n">
-        <v>2420</v>
+        <v>1600</v>
       </c>
       <c r="N6" t="n">
-        <v>2720</v>
+        <v>3100</v>
       </c>
       <c r="O6" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="P6" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.0017</v>
-      </c>
       <c r="S6" t="n">
-        <v>16.99</v>
+        <v>-99.81999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>99.01000000000001</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending down -4.5% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15T20:03</t>
+          <t>2026-09-16T15:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -89898,13 +91022,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>76172.89999999999</v>
+        <v>2389.05</v>
       </c>
       <c r="H7" t="n">
-        <v>31.25</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.672</v>
+        <v>0.705</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -89912,37 +91036,193 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="L7" t="n">
-        <v>76400</v>
+        <v>2400</v>
       </c>
       <c r="M7" t="n">
-        <v>75400</v>
+        <v>2300</v>
       </c>
       <c r="N7" t="n">
-        <v>81600</v>
+        <v>2760</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2767</v>
+        <v>-0.0026</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0103</v>
+        <v>0.0001</v>
       </c>
       <c r="S7" t="n">
-        <v>12.15</v>
+        <v>-99.02</v>
       </c>
       <c r="T7" t="n">
-        <v>99.84999999999999</v>
+        <v>99.02</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 95% rich — sell premium</t>
+          <t>trending down -5.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-16T22:09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>70</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>75678.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>76000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>73600</v>
+      </c>
+      <c r="N8" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>IV rank 80% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-16T22:09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>230</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2390.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="T9" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>IV rank 73% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -89963,7 +91243,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-15T22:31:37.106429 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-16T22:27:56.855786 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y984"/>
+  <dimension ref="A1:Y991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -88297,7 +88297,7 @@
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G963" t="n">
@@ -88342,7 +88342,17 @@
         <v>98.59999999999999</v>
       </c>
       <c r="U963" t="inlineStr"/>
-      <c r="X963" t="inlineStr"/>
+      <c r="V963" t="n">
+        <v>81.94</v>
+      </c>
+      <c r="W963" t="n">
+        <v>8.194000000000001</v>
+      </c>
+      <c r="X963" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="Y963" t="inlineStr">
         <is>
           <t>trending up +5.6% — skewed fly</t>
@@ -88467,7 +88477,7 @@
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G965" t="n">
@@ -88512,7 +88522,17 @@
         <v>97.81</v>
       </c>
       <c r="U965" t="inlineStr"/>
-      <c r="X965" t="inlineStr"/>
+      <c r="V965" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="W965" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="X965" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="Y965" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -89793,7 +89813,7 @@
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G980" t="n">
@@ -89837,8 +89857,22 @@
       <c r="T980" t="n">
         <v>99.02</v>
       </c>
-      <c r="U980" t="inlineStr"/>
-      <c r="X980" t="inlineStr"/>
+      <c r="U980" t="inlineStr">
+        <is>
+          <t>2421.77</t>
+        </is>
+      </c>
+      <c r="V980" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="W980" t="n">
+        <v>7.968</v>
+      </c>
+      <c r="X980" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="Y980" t="inlineStr">
         <is>
           <t>trending down -5.0% — skewed fly</t>
@@ -90019,7 +90053,7 @@
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G983" t="n">
@@ -90063,8 +90097,22 @@
       <c r="T983" t="n">
         <v>101.3</v>
       </c>
-      <c r="U983" t="inlineStr"/>
-      <c r="X983" t="inlineStr"/>
+      <c r="U983" t="inlineStr">
+        <is>
+          <t>76393.1</t>
+        </is>
+      </c>
+      <c r="V983" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="W983" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="X983" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="Y983" t="inlineStr">
         <is>
           <t>IV rank 80% rich — sell premium</t>
@@ -90097,7 +90145,7 @@
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G984" t="n">
@@ -90141,11 +90189,619 @@
       <c r="T984" t="n">
         <v>101.45</v>
       </c>
-      <c r="U984" t="inlineStr"/>
-      <c r="X984" t="inlineStr"/>
+      <c r="U984" t="inlineStr">
+        <is>
+          <t>2421.77</t>
+        </is>
+      </c>
+      <c r="V984" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="W984" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="X984" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="Y984" t="inlineStr">
         <is>
           <t>IV rank 73% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-09-17T05:13</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E985" t="n">
+        <v>70</v>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G985" t="n">
+        <v>76488.8</v>
+      </c>
+      <c r="H985" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="I985" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K985" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L985" t="n">
+        <v>76400</v>
+      </c>
+      <c r="M985" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N985" t="n">
+        <v>82400</v>
+      </c>
+      <c r="O985" t="n">
+        <v>0</v>
+      </c>
+      <c r="P985" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="Q985" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="S985" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T985" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="U985" t="inlineStr">
+        <is>
+          <t>76488.8</t>
+        </is>
+      </c>
+      <c r="V985" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="W985" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="X985" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Y985" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-09-17T05:13</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E986" t="n">
+        <v>210</v>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G986" t="n">
+        <v>2441.84</v>
+      </c>
+      <c r="H986" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I986" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K986" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L986" t="n">
+        <v>2430</v>
+      </c>
+      <c r="M986" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N986" t="n">
+        <v>2660</v>
+      </c>
+      <c r="O986" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="P986" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="Q986" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S986" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="T986" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="U986" t="inlineStr">
+        <is>
+          <t>2441.84</t>
+        </is>
+      </c>
+      <c r="V986" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="W986" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="X986" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Y986" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-09-17T14:59</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E987" t="n">
+        <v>60</v>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G987" t="n">
+        <v>76515.39999999999</v>
+      </c>
+      <c r="H987" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I987" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="K987" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L987" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M987" t="n">
+        <v>74000</v>
+      </c>
+      <c r="N987" t="n">
+        <v>89000</v>
+      </c>
+      <c r="O987" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P987" t="n">
+        <v>0.1976</v>
+      </c>
+      <c r="Q987" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="S987" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="T987" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="U987" t="inlineStr"/>
+      <c r="V987" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="W987" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="X987" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Y987" t="inlineStr">
+        <is>
+          <t>IV rank 83% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-09-17T14:59</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E988" t="n">
+        <v>230</v>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G988" t="n">
+        <v>2463.66</v>
+      </c>
+      <c r="H988" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="I988" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K988" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L988" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M988" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N988" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O988" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P988" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="Q988" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="S988" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="T988" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="U988" t="inlineStr"/>
+      <c r="V988" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="W988" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="X988" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Y988" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:52</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E989" t="n">
+        <v>80</v>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G989" t="n">
+        <v>76442.2</v>
+      </c>
+      <c r="H989" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="I989" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K989" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L989" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M989" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N989" t="n">
+        <v>89000</v>
+      </c>
+      <c r="O989" t="n">
+        <v>0</v>
+      </c>
+      <c r="P989" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="Q989" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="S989" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="T989" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="U989" t="inlineStr"/>
+      <c r="X989" t="inlineStr"/>
+      <c r="Y989" t="inlineStr">
+        <is>
+          <t>IV rank 35% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:52</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E990" t="n">
+        <v>60</v>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G990" t="n">
+        <v>76442.2</v>
+      </c>
+      <c r="H990" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I990" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K990" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="L990" t="n">
+        <v>77000</v>
+      </c>
+      <c r="M990" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N990" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O990" t="n">
+        <v>0</v>
+      </c>
+      <c r="P990" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="Q990" t="n">
+        <v>-0.0193</v>
+      </c>
+      <c r="S990" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="T990" t="n">
+        <v>104.89</v>
+      </c>
+      <c r="U990" t="inlineStr"/>
+      <c r="X990" t="inlineStr"/>
+      <c r="Y990" t="inlineStr">
+        <is>
+          <t>IV rank 87% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:52</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E991" t="n">
+        <v>290</v>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G991" t="n">
+        <v>2448.86</v>
+      </c>
+      <c r="H991" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I991" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K991" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L991" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M991" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N991" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O991" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P991" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="Q991" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="S991" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T991" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="U991" t="inlineStr"/>
+      <c r="X991" t="inlineStr"/>
+      <c r="Y991" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
         </is>
       </c>
     </row>
@@ -90216,22 +90872,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C2" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
       <c r="E2" t="n">
-        <v>2652.78</v>
+        <v>2702.55</v>
       </c>
       <c r="F2" t="n">
-        <v>5.34</v>
+        <v>5.37</v>
       </c>
       <c r="G2" t="n">
-        <v>265.28</v>
+        <v>270.25</v>
       </c>
     </row>
     <row r="3">
@@ -90291,22 +90947,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>68.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="E5" t="n">
-        <v>-248.13</v>
+        <v>-168.45</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.29</v>
+        <v>-0.87</v>
       </c>
       <c r="G5" t="n">
-        <v>-24.81</v>
+        <v>-16.85</v>
       </c>
     </row>
     <row r="6">
@@ -90316,22 +90972,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>64.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>-290.14</v>
+        <v>-279.38</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.75</v>
+        <v>-9.98</v>
       </c>
       <c r="G6" t="n">
-        <v>-29.01</v>
+        <v>-27.94</v>
       </c>
     </row>
     <row r="7">
@@ -90341,22 +90997,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>26.7</v>
       </c>
       <c r="D7" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="E7" t="n">
-        <v>-600.28</v>
+        <v>-518.34</v>
       </c>
       <c r="F7" t="n">
-        <v>-42.88</v>
+        <v>-34.56</v>
       </c>
       <c r="G7" t="n">
-        <v>-60.03</v>
+        <v>-51.83</v>
       </c>
     </row>
     <row r="8">
@@ -90445,7 +91101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -90683,7 +91339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14T20:23</t>
+          <t>2026-09-15T01:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -90693,16 +91349,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -90710,68 +91366,68 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2598.25</v>
+        <v>2514.78</v>
       </c>
       <c r="H3" t="n">
-        <v>59.2</v>
+        <v>53.55</v>
       </c>
       <c r="I3" t="n">
-        <v>0.652</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.85</v>
+        <v>3.34</v>
       </c>
       <c r="L3" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="M3" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="N3" t="n">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0015</v>
+        <v>-0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0044</v>
+        <v>0.0107</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002</v>
+        <v>-0.0046</v>
       </c>
       <c r="S3" t="n">
-        <v>-98.59999999999999</v>
+        <v>16.15</v>
       </c>
       <c r="T3" t="n">
-        <v>98.59999999999999</v>
+        <v>103.85</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending up +5.6% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:39</t>
+          <t>2026-09-16T01:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -90780,7 +91436,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>2620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -90788,77 +91444,77 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>77984.10000000001</v>
+        <v>2401.29</v>
       </c>
       <c r="H4" t="n">
-        <v>36.25</v>
+        <v>52.85</v>
       </c>
       <c r="I4" t="n">
-        <v>0.677</v>
+        <v>0.517</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.94</v>
+        <v>4.25</v>
       </c>
       <c r="L4" t="n">
-        <v>77500</v>
+        <v>2500</v>
       </c>
       <c r="M4" t="n">
-        <v>51000</v>
+        <v>1600</v>
       </c>
       <c r="N4" t="n">
-        <v>93000</v>
+        <v>3100</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0.0002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0301</v>
+        <v>0.0001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0193</v>
+        <v>-0.0001</v>
       </c>
       <c r="S4" t="n">
-        <v>22.19</v>
+        <v>-99.81999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>97.81</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending down -4.5% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15T01:39</t>
+          <t>2026-09-17T21:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -90866,68 +91522,68 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2514.78</v>
+        <v>76442.2</v>
       </c>
       <c r="H5" t="n">
-        <v>53.55</v>
+        <v>15.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3.34</v>
+        <v>0.75</v>
       </c>
       <c r="L5" t="n">
-        <v>2400</v>
+        <v>77000</v>
       </c>
       <c r="M5" t="n">
-        <v>1500</v>
+        <v>75000</v>
       </c>
       <c r="N5" t="n">
-        <v>3100</v>
+        <v>89000</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0107</v>
+        <v>0.2115</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0122</v>
       </c>
       <c r="S5" t="n">
-        <v>16.15</v>
+        <v>7.3</v>
       </c>
       <c r="T5" t="n">
-        <v>103.85</v>
+        <v>104.7</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>IV rank 35% — default sell</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16T01:00</t>
+          <t>2026-09-17T21:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -90936,7 +91592,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2620</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -90944,58 +91600,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2401.29</v>
+        <v>76442.2</v>
       </c>
       <c r="H6" t="n">
-        <v>52.85</v>
+        <v>27.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.517</v>
+        <v>0.71</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.25</v>
+        <v>4.83</v>
       </c>
       <c r="L6" t="n">
-        <v>2500</v>
+        <v>77000</v>
       </c>
       <c r="M6" t="n">
-        <v>1600</v>
+        <v>51000</v>
       </c>
       <c r="N6" t="n">
-        <v>3100</v>
+        <v>93000</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001</v>
+        <v>0.0323</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0001</v>
+        <v>-0.0193</v>
       </c>
       <c r="S6" t="n">
-        <v>-99.81999999999999</v>
+        <v>15.11</v>
       </c>
       <c r="T6" t="n">
-        <v>99.81999999999999</v>
+        <v>104.89</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending down -4.5% — skewed fly</t>
+          <t>IV rank 87% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16T15:28</t>
+          <t>2026-09-17T21:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -91005,16 +91661,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>480</v>
+        <v>290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -91022,207 +91678,51 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2389.05</v>
+        <v>2448.86</v>
       </c>
       <c r="H7" t="n">
-        <v>65.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.705</v>
+        <v>0.665</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="L7" t="n">
-        <v>2400</v>
+        <v>2460</v>
       </c>
       <c r="M7" t="n">
-        <v>2300</v>
+        <v>2340</v>
       </c>
       <c r="N7" t="n">
-        <v>2760</v>
+        <v>2700</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0026</v>
+        <v>0.1022</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001</v>
+        <v>-0.0039</v>
       </c>
       <c r="S7" t="n">
-        <v>-99.02</v>
+        <v>14.5</v>
       </c>
       <c r="T7" t="n">
-        <v>99.02</v>
+        <v>101.5</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending down -5.0% — skewed fly</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-16T22:09</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>70</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>75678.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>24.65</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="L8" t="n">
-        <v>76000</v>
-      </c>
-      <c r="M8" t="n">
-        <v>73600</v>
-      </c>
-      <c r="N8" t="n">
-        <v>82400</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.0105</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>IV rank 80% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-16T22:09</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>230</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2390.23</v>
-      </c>
-      <c r="H9" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2400</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2300</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2760</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.1153</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.0034</v>
-      </c>
-      <c r="S9" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="T9" t="n">
-        <v>101.45</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>IV rank 73% rich — sell premium</t>
+          <t>IV rank 33% — default sell</t>
         </is>
       </c>
     </row>
@@ -91243,7 +91743,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16T22:27:56.855786 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-17T22:31:18.544364 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y991"/>
+  <dimension ref="A1:Y1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -82505,7 +82505,7 @@
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G899" t="n">
@@ -82549,8 +82549,22 @@
       <c r="T899" t="n">
         <v>0</v>
       </c>
-      <c r="U899" t="inlineStr"/>
-      <c r="X899" t="inlineStr"/>
+      <c r="U899" t="inlineStr">
+        <is>
+          <t>2464.37</t>
+        </is>
+      </c>
+      <c r="V899" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="W899" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="X899" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="Y899" t="inlineStr">
         <is>
           <t>IV rank 92% rich — sell premium</t>
@@ -88565,7 +88579,7 @@
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G966" t="n">
@@ -88610,7 +88624,17 @@
         <v>103.85</v>
       </c>
       <c r="U966" t="inlineStr"/>
-      <c r="X966" t="inlineStr"/>
+      <c r="V966" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="W966" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="X966" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="Y966" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -90597,7 +90621,7 @@
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G989" t="n">
@@ -90641,8 +90665,22 @@
       <c r="T989" t="n">
         <v>104.7</v>
       </c>
-      <c r="U989" t="inlineStr"/>
-      <c r="X989" t="inlineStr"/>
+      <c r="U989" t="inlineStr">
+        <is>
+          <t>77038.2</t>
+        </is>
+      </c>
+      <c r="V989" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="W989" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="X989" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="Y989" t="inlineStr">
         <is>
           <t>IV rank 35% — default sell</t>
@@ -90675,7 +90713,7 @@
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G990" t="n">
@@ -90720,7 +90758,17 @@
         <v>104.89</v>
       </c>
       <c r="U990" t="inlineStr"/>
-      <c r="X990" t="inlineStr"/>
+      <c r="V990" t="n">
+        <v>-24.55</v>
+      </c>
+      <c r="W990" t="n">
+        <v>-2.455</v>
+      </c>
+      <c r="X990" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="Y990" t="inlineStr">
         <is>
           <t>IV rank 87% rich — sell premium</t>
@@ -90753,7 +90801,7 @@
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G991" t="n">
@@ -90797,11 +90845,1033 @@
       <c r="T991" t="n">
         <v>101.5</v>
       </c>
-      <c r="U991" t="inlineStr"/>
-      <c r="X991" t="inlineStr"/>
+      <c r="U991" t="inlineStr">
+        <is>
+          <t>2464.37</t>
+        </is>
+      </c>
+      <c r="V991" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="W991" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="X991" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="Y991" t="inlineStr">
         <is>
           <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-09-18T02:55</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E992" t="n">
+        <v>240</v>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G992" t="n">
+        <v>2464.37</v>
+      </c>
+      <c r="H992" t="n">
+        <v>43</v>
+      </c>
+      <c r="I992" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K992" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L992" t="n">
+        <v>2450</v>
+      </c>
+      <c r="M992" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N992" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O992" t="n">
+        <v>0</v>
+      </c>
+      <c r="P992" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="Q992" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S992" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="T992" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="U992" t="inlineStr"/>
+      <c r="V992" t="n">
+        <v>-39.41</v>
+      </c>
+      <c r="W992" t="n">
+        <v>-3.941</v>
+      </c>
+      <c r="X992" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Y992" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-09-18T07:55</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E993" t="n">
+        <v>70</v>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G993" t="n">
+        <v>77780.7</v>
+      </c>
+      <c r="H993" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="I993" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K993" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L993" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M993" t="n">
+        <v>73000</v>
+      </c>
+      <c r="N993" t="n">
+        <v>89000</v>
+      </c>
+      <c r="O993" t="n">
+        <v>0</v>
+      </c>
+      <c r="P993" t="n">
+        <v>0.6541</v>
+      </c>
+      <c r="Q993" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="S993" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T993" t="n">
+        <v>106.76</v>
+      </c>
+      <c r="U993" t="inlineStr">
+        <is>
+          <t>77780.7</t>
+        </is>
+      </c>
+      <c r="V993" t="n">
+        <v>5</v>
+      </c>
+      <c r="W993" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X993" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Y993" t="inlineStr">
+        <is>
+          <t>IV rank 79% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-09-18T07:55</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E994" t="n">
+        <v>750</v>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G994" t="n">
+        <v>77780.7</v>
+      </c>
+      <c r="H994" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="I994" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K994" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L994" t="n">
+        <v>77600</v>
+      </c>
+      <c r="M994" t="n">
+        <v>73000</v>
+      </c>
+      <c r="N994" t="n">
+        <v>89000</v>
+      </c>
+      <c r="O994" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P994" t="n">
+        <v>-0.9179</v>
+      </c>
+      <c r="Q994" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S994" t="n">
+        <v>-99.83</v>
+      </c>
+      <c r="T994" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="U994" t="inlineStr">
+        <is>
+          <t>77780.7</t>
+        </is>
+      </c>
+      <c r="V994" t="n">
+        <v>-103.95</v>
+      </c>
+      <c r="W994" t="n">
+        <v>-10.395</v>
+      </c>
+      <c r="X994" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Y994" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-09-18T07:55</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E995" t="n">
+        <v>220</v>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G995" t="n">
+        <v>2491.34</v>
+      </c>
+      <c r="H995" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="I995" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K995" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L995" t="n">
+        <v>2480</v>
+      </c>
+      <c r="M995" t="n">
+        <v>2340</v>
+      </c>
+      <c r="N995" t="n">
+        <v>2650</v>
+      </c>
+      <c r="O995" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P995" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="Q995" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S995" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="T995" t="n">
+        <v>97.83</v>
+      </c>
+      <c r="U995" t="inlineStr">
+        <is>
+          <t>2491.34</t>
+        </is>
+      </c>
+      <c r="V995" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="W995" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="X995" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Y995" t="inlineStr">
+        <is>
+          <t>IV rank 70% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-09-18T16:43</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E996" t="n">
+        <v>70</v>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G996" t="n">
+        <v>80953.10000000001</v>
+      </c>
+      <c r="H996" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I996" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K996" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="L996" t="n">
+        <v>80600</v>
+      </c>
+      <c r="M996" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N996" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O996" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P996" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="Q996" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="S996" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="T996" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="U996" t="inlineStr"/>
+      <c r="V996" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W996" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="X996" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Y996" t="inlineStr">
+        <is>
+          <t>IV rank 79% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-09-18T16:43</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E997" t="n">
+        <v>70</v>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G997" t="n">
+        <v>80953.10000000001</v>
+      </c>
+      <c r="H997" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I997" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K997" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="L997" t="n">
+        <v>80600</v>
+      </c>
+      <c r="M997" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N997" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O997" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P997" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="Q997" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="S997" t="n">
+        <v>-102.42</v>
+      </c>
+      <c r="T997" t="n">
+        <v>102.42</v>
+      </c>
+      <c r="U997" t="inlineStr"/>
+      <c r="X997" t="inlineStr"/>
+      <c r="Y997" t="inlineStr">
+        <is>
+          <t>trending up +4.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-09-18T16:43</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E998" t="n">
+        <v>60</v>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G998" t="n">
+        <v>80953.10000000001</v>
+      </c>
+      <c r="H998" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="I998" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K998" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="L998" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M998" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N998" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O998" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P998" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="Q998" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="S998" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="T998" t="n">
+        <v>100.94</v>
+      </c>
+      <c r="U998" t="inlineStr"/>
+      <c r="X998" t="inlineStr"/>
+      <c r="Y998" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-09-18T16:43</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E999" t="n">
+        <v>140</v>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G999" t="n">
+        <v>80953.10000000001</v>
+      </c>
+      <c r="H999" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="I999" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K999" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="L999" t="n">
+        <v>78000</v>
+      </c>
+      <c r="M999" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N999" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O999" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P999" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="Q999" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="S999" t="n">
+        <v>-103.28</v>
+      </c>
+      <c r="T999" t="n">
+        <v>103.28</v>
+      </c>
+      <c r="U999" t="inlineStr"/>
+      <c r="X999" t="inlineStr"/>
+      <c r="Y999" t="inlineStr">
+        <is>
+          <t>trending up +4.9% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-09-18T16:43</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E1000" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1000" t="n">
+        <v>2601.12</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1000" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L1000" t="n">
+        <v>2580</v>
+      </c>
+      <c r="M1000" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N1000" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O1000" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="P1000" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="Q1000" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="S1000" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="T1000" t="n">
+        <v>102.21</v>
+      </c>
+      <c r="U1000" t="inlineStr"/>
+      <c r="V1000" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W1000" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="X1000" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Y1000" t="inlineStr">
+        <is>
+          <t>IV rank 89% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-09-18T16:43</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E1001" t="n">
+        <v>280</v>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1001" t="n">
+        <v>2601.12</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="I1001" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1001" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L1001" t="n">
+        <v>2580</v>
+      </c>
+      <c r="M1001" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N1001" t="n">
+        <v>2680</v>
+      </c>
+      <c r="O1001" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="P1001" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="Q1001" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S1001" t="n">
+        <v>-101.47</v>
+      </c>
+      <c r="T1001" t="n">
+        <v>101.47</v>
+      </c>
+      <c r="U1001" t="inlineStr"/>
+      <c r="X1001" t="inlineStr"/>
+      <c r="Y1001" t="inlineStr">
+        <is>
+          <t>trending up +4.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-09-18T21:42</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E1002" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1002" t="n">
+        <v>2635.34</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>27</v>
+      </c>
+      <c r="I1002" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1002" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L1002" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M1002" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1002" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O1002" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="P1002" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="Q1002" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S1002" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="T1002" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U1002" t="inlineStr"/>
+      <c r="X1002" t="inlineStr"/>
+      <c r="Y1002" t="inlineStr">
+        <is>
+          <t>IV rank 53% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-09-18T21:42</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1003" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1003" t="n">
+        <v>2635.34</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="I1003" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1003" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L1003" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M1003" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N1003" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1003" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P1003" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="Q1003" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S1003" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T1003" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="U1003" t="inlineStr"/>
+      <c r="X1003" t="inlineStr"/>
+      <c r="Y1003" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -90872,22 +91942,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C2" t="n">
-        <v>96.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.21</v>
+        <v>5.28</v>
       </c>
       <c r="E2" t="n">
-        <v>2702.55</v>
+        <v>2749.75</v>
       </c>
       <c r="F2" t="n">
-        <v>5.37</v>
+        <v>5.4</v>
       </c>
       <c r="G2" t="n">
-        <v>270.25</v>
+        <v>274.97</v>
       </c>
     </row>
     <row r="3">
@@ -90972,22 +92042,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>64.3</v>
+        <v>59.4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>-279.38</v>
+        <v>-336.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.98</v>
+        <v>-10.52</v>
       </c>
       <c r="G6" t="n">
-        <v>-27.94</v>
+        <v>-33.66</v>
       </c>
     </row>
     <row r="7">
@@ -91072,7 +92142,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -91081,13 +92151,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-9876.870000000001</v>
+        <v>-9980.82</v>
       </c>
       <c r="F10" t="n">
         <v>-103.97</v>
       </c>
       <c r="G10" t="n">
-        <v>-987.6900000000001</v>
+        <v>-998.08</v>
       </c>
     </row>
   </sheetData>
@@ -91101,7 +92171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -91261,7 +92331,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:24</t>
+          <t>2026-09-16T01:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -91271,16 +92341,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>2620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -91288,77 +92358,77 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2483.49</v>
+        <v>2401.29</v>
       </c>
       <c r="H2" t="n">
-        <v>47.8</v>
+        <v>52.85</v>
       </c>
       <c r="I2" t="n">
-        <v>0.345</v>
+        <v>0.517</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.99</v>
+        <v>4.25</v>
       </c>
       <c r="L2" t="n">
         <v>2500</v>
       </c>
       <c r="M2" t="n">
-        <v>2350</v>
+        <v>1600</v>
       </c>
       <c r="N2" t="n">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-99.81999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>IV rank 92% rich — sell premium</t>
+          <t>trending down -4.5% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15T01:39</t>
+          <t>2026-09-18T16:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -91366,68 +92436,68 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2514.78</v>
+        <v>80953.10000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>53.55</v>
+        <v>24.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="L3" t="n">
-        <v>2400</v>
+        <v>80600</v>
       </c>
       <c r="M3" t="n">
-        <v>1500</v>
+        <v>79000</v>
       </c>
       <c r="N3" t="n">
-        <v>3100</v>
+        <v>82800</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0107</v>
+        <v>0.1686</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0046</v>
+        <v>-0.0124</v>
       </c>
       <c r="S3" t="n">
-        <v>16.15</v>
+        <v>-102.42</v>
       </c>
       <c r="T3" t="n">
-        <v>103.85</v>
+        <v>102.42</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending up +4.9% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16T01:00</t>
+          <t>2026-09-18T16:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -91436,7 +92506,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2620</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -91444,58 +92514,58 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2401.29</v>
+        <v>80953.10000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>52.85</v>
+        <v>31.75</v>
       </c>
       <c r="I4" t="n">
-        <v>0.517</v>
+        <v>0.68</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.25</v>
+        <v>5.11</v>
       </c>
       <c r="L4" t="n">
-        <v>2500</v>
+        <v>78000</v>
       </c>
       <c r="M4" t="n">
-        <v>1600</v>
+        <v>51000</v>
       </c>
       <c r="N4" t="n">
-        <v>3100</v>
+        <v>93000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001</v>
+        <v>0.0424</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0001</v>
+        <v>-0.0192</v>
       </c>
       <c r="S4" t="n">
-        <v>-99.81999999999999</v>
+        <v>19.06</v>
       </c>
       <c r="T4" t="n">
-        <v>99.81999999999999</v>
+        <v>100.94</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending down -4.5% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17T21:52</t>
+          <t>2026-09-18T16:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -91505,16 +92575,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -91522,77 +92592,77 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>76442.2</v>
+        <v>80953.10000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>15.15</v>
+        <v>31.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.711</v>
+        <v>0.654</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.75</v>
+        <v>5.11</v>
       </c>
       <c r="L5" t="n">
-        <v>77000</v>
+        <v>78000</v>
       </c>
       <c r="M5" t="n">
-        <v>75000</v>
+        <v>51000</v>
       </c>
       <c r="N5" t="n">
-        <v>89000</v>
+        <v>93000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2115</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0122</v>
+        <v>0.0033</v>
       </c>
       <c r="S5" t="n">
-        <v>7.3</v>
+        <v>-103.28</v>
       </c>
       <c r="T5" t="n">
-        <v>104.7</v>
+        <v>103.28</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 35% — default sell</t>
+          <t>trending up +4.9% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17T21:52</t>
+          <t>2026-09-18T16:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -91600,58 +92670,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>76442.2</v>
+        <v>2601.12</v>
       </c>
       <c r="H6" t="n">
-        <v>27.2</v>
+        <v>37.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.71</v>
+        <v>0.912</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.83</v>
+        <v>2.31</v>
       </c>
       <c r="L6" t="n">
-        <v>77000</v>
+        <v>2580</v>
       </c>
       <c r="M6" t="n">
-        <v>51000</v>
+        <v>2440</v>
       </c>
       <c r="N6" t="n">
-        <v>93000</v>
+        <v>2680</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0323</v>
+        <v>0.0334</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0193</v>
+        <v>-0.0017</v>
       </c>
       <c r="S6" t="n">
-        <v>15.11</v>
+        <v>-101.47</v>
       </c>
       <c r="T6" t="n">
-        <v>104.89</v>
+        <v>101.47</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 87% rich — sell premium</t>
+          <t>trending up +4.0% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17T21:52</t>
+          <t>2026-09-18T21:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -91666,11 +92736,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -91678,51 +92748,129 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2448.86</v>
+        <v>2635.34</v>
       </c>
       <c r="H7" t="n">
-        <v>23.6</v>
+        <v>27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.665</v>
+        <v>0.698</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.74</v>
+        <v>2.7</v>
       </c>
       <c r="L7" t="n">
-        <v>2460</v>
+        <v>2600</v>
       </c>
       <c r="M7" t="n">
-        <v>2340</v>
+        <v>2500</v>
       </c>
       <c r="N7" t="n">
-        <v>2700</v>
+        <v>2720</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1022</v>
+        <v>0.0663</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0039</v>
+        <v>-0.003</v>
       </c>
       <c r="S7" t="n">
-        <v>14.5</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>101.5</v>
+        <v>100.28</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 33% — default sell</t>
+          <t>IV rank 53% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-18T21:42</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>250</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2635.34</v>
+      </c>
+      <c r="H8" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -91743,7 +92891,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-17T22:31:18.544364 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-18T22:01:52.274182 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1003"/>
+  <dimension ref="A1:Y1010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -91345,7 +91345,7 @@
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G997" t="n">
@@ -91389,8 +91389,22 @@
       <c r="T997" t="n">
         <v>102.42</v>
       </c>
-      <c r="U997" t="inlineStr"/>
-      <c r="X997" t="inlineStr"/>
+      <c r="U997" t="inlineStr">
+        <is>
+          <t>81075.4</t>
+        </is>
+      </c>
+      <c r="V997" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="W997" t="n">
+        <v>-0.589</v>
+      </c>
+      <c r="X997" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
       <c r="Y997" t="inlineStr">
         <is>
           <t>trending up +4.9% — skewed fly</t>
@@ -91667,7 +91681,7 @@
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1001" t="n">
@@ -91711,8 +91725,22 @@
       <c r="T1001" t="n">
         <v>101.47</v>
       </c>
-      <c r="U1001" t="inlineStr"/>
-      <c r="X1001" t="inlineStr"/>
+      <c r="U1001" t="inlineStr">
+        <is>
+          <t>2605.58</t>
+        </is>
+      </c>
+      <c r="V1001" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="W1001" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="X1001" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
       <c r="Y1001" t="inlineStr">
         <is>
           <t>trending up +4.0% — skewed fly</t>
@@ -91745,7 +91773,7 @@
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1002" t="n">
@@ -91789,8 +91817,22 @@
       <c r="T1002" t="n">
         <v>100.28</v>
       </c>
-      <c r="U1002" t="inlineStr"/>
-      <c r="X1002" t="inlineStr"/>
+      <c r="U1002" t="inlineStr">
+        <is>
+          <t>2605.58</t>
+        </is>
+      </c>
+      <c r="V1002" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="W1002" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="X1002" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
       <c r="Y1002" t="inlineStr">
         <is>
           <t>IV rank 53% — default sell</t>
@@ -91872,6 +91914,608 @@
       <c r="Y1003" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:35</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E1004" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1004" t="n">
+        <v>80975.89999999999</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I1004" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1004" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L1004" t="n">
+        <v>80600</v>
+      </c>
+      <c r="M1004" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N1004" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1004" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="Q1004" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="S1004" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="T1004" t="n">
+        <v>104.29</v>
+      </c>
+      <c r="U1004" t="inlineStr">
+        <is>
+          <t>81075.4</t>
+        </is>
+      </c>
+      <c r="V1004" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="W1004" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="X1004" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Y1004" t="inlineStr">
+        <is>
+          <t>IV rank 28% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-09-19T06:38</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E1005" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1005" t="n">
+        <v>81068.5</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I1005" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1005" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L1005" t="n">
+        <v>81000</v>
+      </c>
+      <c r="M1005" t="n">
+        <v>79000</v>
+      </c>
+      <c r="N1005" t="n">
+        <v>83000</v>
+      </c>
+      <c r="O1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1005" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="Q1005" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="S1005" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T1005" t="n">
+        <v>93.11</v>
+      </c>
+      <c r="U1005" t="inlineStr">
+        <is>
+          <t>81068.5</t>
+        </is>
+      </c>
+      <c r="V1005" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W1005" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="X1005" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Y1005" t="inlineStr">
+        <is>
+          <t>IV rank 54% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-09-19T06:38</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E1006" t="n">
+        <v>150</v>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1006" t="n">
+        <v>2628.28</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I1006" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1006" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L1006" t="n">
+        <v>2620</v>
+      </c>
+      <c r="M1006" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1006" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O1006" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P1006" t="n">
+        <v>0.1787</v>
+      </c>
+      <c r="Q1006" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S1006" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T1006" t="n">
+        <v>100.71</v>
+      </c>
+      <c r="U1006" t="inlineStr">
+        <is>
+          <t>2628.28</t>
+        </is>
+      </c>
+      <c r="V1006" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W1006" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="X1006" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Y1006" t="inlineStr">
+        <is>
+          <t>IV rank 58% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-09-19T06:38</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E1007" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1007" t="n">
+        <v>2628.28</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I1007" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1007" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L1007" t="n">
+        <v>2620</v>
+      </c>
+      <c r="M1007" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1007" t="n">
+        <v>2720</v>
+      </c>
+      <c r="O1007" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="P1007" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="Q1007" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="S1007" t="n">
+        <v>-100.53</v>
+      </c>
+      <c r="T1007" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="U1007" t="inlineStr">
+        <is>
+          <t>2628.28</t>
+        </is>
+      </c>
+      <c r="V1007" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W1007" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="X1007" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Y1007" t="inlineStr">
+        <is>
+          <t>trending up +4.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-09-19T14:48</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1008" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1008" t="n">
+        <v>81529.5</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I1008" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1008" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L1008" t="n">
+        <v>81200</v>
+      </c>
+      <c r="M1008" t="n">
+        <v>81000</v>
+      </c>
+      <c r="N1008" t="n">
+        <v>82800</v>
+      </c>
+      <c r="O1008" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1008" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="Q1008" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="S1008" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="T1008" t="n">
+        <v>105.99</v>
+      </c>
+      <c r="U1008" t="inlineStr"/>
+      <c r="X1008" t="inlineStr"/>
+      <c r="Y1008" t="inlineStr">
+        <is>
+          <t>IV rank 58% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-09-19T14:48</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1009" t="n">
+        <v>180</v>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1009" t="n">
+        <v>2639</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="I1009" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1009" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L1009" t="n">
+        <v>2630</v>
+      </c>
+      <c r="M1009" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N1009" t="n">
+        <v>2740</v>
+      </c>
+      <c r="O1009" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1009" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="Q1009" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S1009" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="T1009" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="U1009" t="inlineStr"/>
+      <c r="X1009" t="inlineStr"/>
+      <c r="Y1009" t="inlineStr">
+        <is>
+          <t>IV rank 54% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-09-19T14:48</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1010" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1010" t="n">
+        <v>2639</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="I1010" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1010" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L1010" t="n">
+        <v>2630</v>
+      </c>
+      <c r="M1010" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N1010" t="n">
+        <v>2740</v>
+      </c>
+      <c r="O1010" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="P1010" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="Q1010" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S1010" t="n">
+        <v>-99.45999999999999</v>
+      </c>
+      <c r="T1010" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="U1010" t="inlineStr"/>
+      <c r="X1010" t="inlineStr"/>
+      <c r="Y1010" t="inlineStr">
+        <is>
+          <t>trending up +4.5% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -91942,22 +92586,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C2" t="n">
         <v>96.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
       <c r="E2" t="n">
-        <v>2749.75</v>
+        <v>2773</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="G2" t="n">
-        <v>274.97</v>
+        <v>277.3</v>
       </c>
     </row>
     <row r="3">
@@ -92017,22 +92661,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C5" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="D5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="E5" t="n">
-        <v>-168.45</v>
+        <v>-153.18</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
       <c r="G5" t="n">
-        <v>-16.85</v>
+        <v>-15.32</v>
       </c>
     </row>
     <row r="6">
@@ -92419,16 +93063,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -92439,48 +93083,48 @@
         <v>80953.10000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>24.6</v>
+        <v>31.75</v>
       </c>
       <c r="I3" t="n">
-        <v>0.965</v>
+        <v>0.68</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.62</v>
+        <v>5.11</v>
       </c>
       <c r="L3" t="n">
-        <v>80600</v>
+        <v>78000</v>
       </c>
       <c r="M3" t="n">
-        <v>79000</v>
+        <v>51000</v>
       </c>
       <c r="N3" t="n">
-        <v>82800</v>
+        <v>93000</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0005</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1686</v>
+        <v>0.0424</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0124</v>
+        <v>-0.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>-102.42</v>
+        <v>19.06</v>
       </c>
       <c r="T3" t="n">
-        <v>102.42</v>
+        <v>100.94</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending up +4.9% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -92497,7 +93141,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -92506,7 +93150,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -92520,7 +93164,7 @@
         <v>31.75</v>
       </c>
       <c r="I4" t="n">
-        <v>0.68</v>
+        <v>0.654</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -92540,42 +93184,42 @@
         <v>93000</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>-0.0002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0424</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0192</v>
+        <v>0.0033</v>
       </c>
       <c r="S4" t="n">
-        <v>19.06</v>
+        <v>-103.28</v>
       </c>
       <c r="T4" t="n">
-        <v>100.94</v>
+        <v>103.28</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending up +4.9% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43</t>
+          <t>2026-09-18T21:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -92584,7 +93228,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -92592,13 +93236,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>80953.10000000001</v>
+        <v>2635.34</v>
       </c>
       <c r="H5" t="n">
-        <v>31.75</v>
+        <v>44.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.654</v>
+        <v>0.675</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -92606,63 +93250,63 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.11</v>
+        <v>2.63</v>
       </c>
       <c r="L5" t="n">
-        <v>78000</v>
+        <v>2500</v>
       </c>
       <c r="M5" t="n">
-        <v>51000</v>
+        <v>1600</v>
       </c>
       <c r="N5" t="n">
-        <v>93000</v>
+        <v>3100</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0127</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0033</v>
+        <v>-0.004</v>
       </c>
       <c r="S5" t="n">
-        <v>-103.28</v>
+        <v>25.8</v>
       </c>
       <c r="T5" t="n">
-        <v>103.28</v>
+        <v>99.2</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>trending up +4.9% — skewed fly</t>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43</t>
+          <t>2026-09-19T14:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -92670,58 +93314,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2601.12</v>
+        <v>81529.5</v>
       </c>
       <c r="H6" t="n">
-        <v>37.7</v>
+        <v>19.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.912</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.31</v>
+        <v>3.22</v>
       </c>
       <c r="L6" t="n">
-        <v>2580</v>
+        <v>81200</v>
       </c>
       <c r="M6" t="n">
-        <v>2440</v>
+        <v>81000</v>
       </c>
       <c r="N6" t="n">
-        <v>2680</v>
+        <v>82800</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0044</v>
+        <v>0.0001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0334</v>
+        <v>0.1034</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0017</v>
+        <v>-0.0105</v>
       </c>
       <c r="S6" t="n">
-        <v>-101.47</v>
+        <v>6.01</v>
       </c>
       <c r="T6" t="n">
-        <v>101.47</v>
+        <v>105.99</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +4.0% — skewed fly</t>
+          <t>IV rank 58% — default sell</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18T21:42</t>
+          <t>2026-09-19T14:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -92736,11 +93380,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -92748,58 +93392,58 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2635.34</v>
+        <v>2639</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>26.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.698</v>
+        <v>0.711</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="L7" t="n">
+        <v>2630</v>
+      </c>
+      <c r="M7" t="n">
         <v>2600</v>
       </c>
-      <c r="M7" t="n">
-        <v>2500</v>
-      </c>
       <c r="N7" t="n">
-        <v>2720</v>
+        <v>2740</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009</v>
+        <v>0.0001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0663</v>
+        <v>0.0689</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.003</v>
+        <v>-0.0046</v>
       </c>
       <c r="S7" t="n">
-        <v>9.720000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>100.28</v>
+        <v>98.86</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 53% — default sell</t>
+          <t>IV rank 54% — default sell</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18T21:42</t>
+          <t>2026-09-19T14:48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -92809,16 +93453,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -92826,51 +93470,51 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2635.34</v>
+        <v>2639</v>
       </c>
       <c r="H8" t="n">
-        <v>44.05</v>
+        <v>26.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.675</v>
+        <v>0.994</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2.63</v>
+        <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>2500</v>
+        <v>2630</v>
       </c>
       <c r="M8" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="N8" t="n">
-        <v>3100</v>
+        <v>2740</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0003</v>
+        <v>-0.0041</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0127</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.004</v>
+        <v>-0.0059</v>
       </c>
       <c r="S8" t="n">
-        <v>25.8</v>
+        <v>-99.45999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>99.2</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>trending up +4.5% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -92891,7 +93535,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-18T22:01:52.274182 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-19T21:54:14.244905 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1010"/>
+  <dimension ref="A1:Y1023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -89215,7 +89215,7 @@
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G973" t="n">
@@ -89260,7 +89260,17 @@
         <v>99.81999999999999</v>
       </c>
       <c r="U973" t="inlineStr"/>
-      <c r="X973" t="inlineStr"/>
+      <c r="V973" t="n">
+        <v>-202.53</v>
+      </c>
+      <c r="W973" t="n">
+        <v>-20.253</v>
+      </c>
+      <c r="X973" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
       <c r="Y973" t="inlineStr">
         <is>
           <t>trending down -4.5% — skewed fly</t>
@@ -92311,7 +92321,7 @@
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1008" t="n">
@@ -92356,7 +92366,17 @@
         <v>105.99</v>
       </c>
       <c r="U1008" t="inlineStr"/>
-      <c r="X1008" t="inlineStr"/>
+      <c r="V1008" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="W1008" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="X1008" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
       <c r="Y1008" t="inlineStr">
         <is>
           <t>IV rank 58% — default sell</t>
@@ -92389,7 +92409,7 @@
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1009" t="n">
@@ -92434,7 +92454,17 @@
         <v>98.86</v>
       </c>
       <c r="U1009" t="inlineStr"/>
-      <c r="X1009" t="inlineStr"/>
+      <c r="V1009" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="W1009" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="X1009" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
       <c r="Y1009" t="inlineStr">
         <is>
           <t>IV rank 54% — default sell</t>
@@ -92467,7 +92497,7 @@
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1010" t="n">
@@ -92511,11 +92541,1147 @@
       <c r="T1010" t="n">
         <v>99.45999999999999</v>
       </c>
-      <c r="U1010" t="inlineStr"/>
-      <c r="X1010" t="inlineStr"/>
+      <c r="U1010" t="inlineStr">
+        <is>
+          <t>2579.87</t>
+        </is>
+      </c>
+      <c r="V1010" t="n">
+        <v>-42.26</v>
+      </c>
+      <c r="W1010" t="n">
+        <v>-4.226</v>
+      </c>
+      <c r="X1010" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
       <c r="Y1010" t="inlineStr">
         <is>
           <t>trending up +4.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:05</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1011" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1011" t="n">
+        <v>80430.89999999999</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1011" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L1011" t="n">
+        <v>80800</v>
+      </c>
+      <c r="M1011" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N1011" t="n">
+        <v>83400</v>
+      </c>
+      <c r="O1011" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1011" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="Q1011" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="S1011" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="T1011" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="U1011" t="inlineStr">
+        <is>
+          <t>80430.9</t>
+        </is>
+      </c>
+      <c r="V1011" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="W1011" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="X1011" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1011" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:05</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1012" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1012" t="n">
+        <v>80430.89999999999</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="I1012" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1012" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L1012" t="n">
+        <v>80800</v>
+      </c>
+      <c r="M1012" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N1012" t="n">
+        <v>83400</v>
+      </c>
+      <c r="O1012" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P1012" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="Q1012" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="S1012" t="n">
+        <v>-91.72</v>
+      </c>
+      <c r="T1012" t="n">
+        <v>91.72</v>
+      </c>
+      <c r="U1012" t="inlineStr">
+        <is>
+          <t>80430.9</t>
+        </is>
+      </c>
+      <c r="V1012" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="W1012" t="n">
+        <v>-0.171</v>
+      </c>
+      <c r="X1012" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1012" t="inlineStr">
+        <is>
+          <t>trending up +6.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:05</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1013" t="n">
+        <v>210</v>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1013" t="n">
+        <v>2579.87</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1013" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L1013" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M1013" t="n">
+        <v>2560</v>
+      </c>
+      <c r="N1013" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1013" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P1013" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="Q1013" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="S1013" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="T1013" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="U1013" t="inlineStr">
+        <is>
+          <t>2579.87</t>
+        </is>
+      </c>
+      <c r="V1013" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="W1013" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="X1013" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1013" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:33</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1014" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1014" t="n">
+        <v>80412.60000000001</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1014" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L1014" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N1014" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1014" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="Q1014" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="S1014" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T1014" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="U1014" t="inlineStr">
+        <is>
+          <t>80412.6</t>
+        </is>
+      </c>
+      <c r="V1014" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W1014" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="X1014" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1014" t="inlineStr">
+        <is>
+          <t>IV rank 35% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:33</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1015" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1015" t="n">
+        <v>80412.60000000001</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1015" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L1015" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N1015" t="n">
+        <v>82000</v>
+      </c>
+      <c r="O1015" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1015" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="Q1015" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="S1015" t="n">
+        <v>-105</v>
+      </c>
+      <c r="T1015" t="n">
+        <v>105</v>
+      </c>
+      <c r="U1015" t="inlineStr">
+        <is>
+          <t>80412.6</t>
+        </is>
+      </c>
+      <c r="V1015" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="W1015" t="n">
+        <v>-0.484</v>
+      </c>
+      <c r="X1015" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1015" t="inlineStr">
+        <is>
+          <t>trending up +6.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:33</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1016" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1016" t="n">
+        <v>2579.47</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1016" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L1016" t="n">
+        <v>2580</v>
+      </c>
+      <c r="M1016" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N1016" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1016" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="P1016" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="Q1016" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S1016" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T1016" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="U1016" t="inlineStr">
+        <is>
+          <t>2579.47</t>
+        </is>
+      </c>
+      <c r="V1016" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W1016" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="X1016" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1016" t="inlineStr">
+        <is>
+          <t>IV rank 39% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:33</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E1017" t="n">
+        <v>150</v>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1017" t="n">
+        <v>2579.47</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1017" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L1017" t="n">
+        <v>2580</v>
+      </c>
+      <c r="M1017" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N1017" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1017" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="P1017" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="Q1017" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S1017" t="n">
+        <v>-97.8</v>
+      </c>
+      <c r="T1017" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="U1017" t="inlineStr">
+        <is>
+          <t>2579.47</t>
+        </is>
+      </c>
+      <c r="V1017" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="W1017" t="n">
+        <v>-0.107</v>
+      </c>
+      <c r="X1017" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1017" t="inlineStr">
+        <is>
+          <t>trending up +7.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-09-20T08:33</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1018" t="n">
+        <v>310</v>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1018" t="n">
+        <v>2579.47</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1018" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L1018" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M1018" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N1018" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1018" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="P1018" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="Q1018" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="S1018" t="n">
+        <v>-101.43</v>
+      </c>
+      <c r="T1018" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="U1018" t="inlineStr"/>
+      <c r="X1018" t="inlineStr"/>
+      <c r="Y1018" t="inlineStr">
+        <is>
+          <t>trending up +7.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:13</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1019" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>80559</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1019" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>77800</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O1019" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1019" t="n">
+        <v>0.2299</v>
+      </c>
+      <c r="Q1019" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="S1019" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="T1019" t="n">
+        <v>96.97</v>
+      </c>
+      <c r="U1019" t="inlineStr"/>
+      <c r="X1019" t="inlineStr"/>
+      <c r="Y1019" t="inlineStr">
+        <is>
+          <t>IV rank 86% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:13</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1020" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1020" t="n">
+        <v>80559</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1020" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L1020" t="n">
+        <v>80400</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>77800</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O1020" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1020" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="Q1020" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="S1020" t="n">
+        <v>-99.56</v>
+      </c>
+      <c r="T1020" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="U1020" t="inlineStr"/>
+      <c r="X1020" t="inlineStr"/>
+      <c r="Y1020" t="inlineStr">
+        <is>
+          <t>trending up +6.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:13</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1021" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1021" t="n">
+        <v>2582.01</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1021" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L1021" t="n">
+        <v>2580</v>
+      </c>
+      <c r="M1021" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1021" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1021" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1021" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="Q1021" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S1021" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="T1021" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="U1021" t="inlineStr"/>
+      <c r="X1021" t="inlineStr"/>
+      <c r="Y1021" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:13</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1022" t="n">
+        <v>320</v>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>2582.01</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1022" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L1022" t="n">
+        <v>2580</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1022" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="P1022" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="Q1022" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S1022" t="n">
+        <v>-99.65000000000001</v>
+      </c>
+      <c r="T1022" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="U1022" t="inlineStr"/>
+      <c r="V1022" t="n">
+        <v>-56.26</v>
+      </c>
+      <c r="W1022" t="n">
+        <v>-5.626</v>
+      </c>
+      <c r="X1022" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Y1022" t="inlineStr">
+        <is>
+          <t>trending up +7.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:14</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1023" t="n">
+        <v>280</v>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1023" t="n">
+        <v>2629.02</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1023" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L1023" t="n">
+        <v>2610</v>
+      </c>
+      <c r="M1023" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N1023" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1023" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="P1023" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="Q1023" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S1023" t="n">
+        <v>-101.72</v>
+      </c>
+      <c r="T1023" t="n">
+        <v>101.72</v>
+      </c>
+      <c r="U1023" t="inlineStr"/>
+      <c r="X1023" t="inlineStr"/>
+      <c r="Y1023" t="inlineStr">
+        <is>
+          <t>trending up +9.5% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -92586,22 +93752,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C2" t="n">
         <v>96.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.32</v>
+        <v>5.36</v>
       </c>
       <c r="E2" t="n">
-        <v>2773</v>
+        <v>2800.38</v>
       </c>
       <c r="F2" t="n">
-        <v>5.41</v>
+        <v>5.4</v>
       </c>
       <c r="G2" t="n">
-        <v>277.3</v>
+        <v>280.04</v>
       </c>
     </row>
     <row r="3">
@@ -92661,22 +93827,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>67.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-153.18</v>
+        <v>-259.32</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.78</v>
+        <v>-1.28</v>
       </c>
       <c r="G5" t="n">
-        <v>-15.32</v>
+        <v>-25.93</v>
       </c>
     </row>
     <row r="6">
@@ -92711,22 +93877,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="E7" t="n">
-        <v>-518.34</v>
+        <v>-720.87</v>
       </c>
       <c r="F7" t="n">
-        <v>-34.56</v>
+        <v>-45.05</v>
       </c>
       <c r="G7" t="n">
-        <v>-51.83</v>
+        <v>-72.09</v>
       </c>
     </row>
     <row r="8">
@@ -92815,7 +93981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -92975,17 +94141,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16T01:00</t>
+          <t>2026-09-18T16:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -92994,7 +94160,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2620</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -93002,51 +94168,51 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2401.29</v>
+        <v>80953.10000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>52.85</v>
+        <v>31.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.517</v>
+        <v>0.68</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.25</v>
+        <v>5.11</v>
       </c>
       <c r="L2" t="n">
-        <v>2500</v>
+        <v>78000</v>
       </c>
       <c r="M2" t="n">
-        <v>1600</v>
+        <v>51000</v>
       </c>
       <c r="N2" t="n">
-        <v>3100</v>
+        <v>93000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001</v>
+        <v>0.0424</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0001</v>
+        <v>-0.0192</v>
       </c>
       <c r="S2" t="n">
-        <v>-99.81999999999999</v>
+        <v>19.06</v>
       </c>
       <c r="T2" t="n">
-        <v>99.81999999999999</v>
+        <v>100.94</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>trending down -4.5% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -93063,7 +94229,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -93072,7 +94238,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -93086,7 +94252,7 @@
         <v>31.75</v>
       </c>
       <c r="I3" t="n">
-        <v>0.68</v>
+        <v>0.654</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -93106,42 +94272,42 @@
         <v>93000</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>-0.0002</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0424</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0192</v>
+        <v>0.0033</v>
       </c>
       <c r="S3" t="n">
-        <v>19.06</v>
+        <v>-103.28</v>
       </c>
       <c r="T3" t="n">
-        <v>100.94</v>
+        <v>103.28</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending up +4.9% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43</t>
+          <t>2026-09-18T21:42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -93150,7 +94316,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -93158,13 +94324,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>80953.10000000001</v>
+        <v>2635.34</v>
       </c>
       <c r="H4" t="n">
-        <v>31.75</v>
+        <v>44.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.654</v>
+        <v>0.675</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -93172,44 +94338,44 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.11</v>
+        <v>2.63</v>
       </c>
       <c r="L4" t="n">
-        <v>78000</v>
+        <v>2500</v>
       </c>
       <c r="M4" t="n">
-        <v>51000</v>
+        <v>1600</v>
       </c>
       <c r="N4" t="n">
-        <v>93000</v>
+        <v>3100</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0127</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0033</v>
+        <v>-0.004</v>
       </c>
       <c r="S4" t="n">
-        <v>-103.28</v>
+        <v>25.8</v>
       </c>
       <c r="T4" t="n">
-        <v>103.28</v>
+        <v>99.2</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending up +4.9% — skewed fly</t>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18T21:42</t>
+          <t>2026-09-20T08:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -93219,7 +94385,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -93228,7 +94394,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -93236,13 +94402,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2635.34</v>
+        <v>2579.47</v>
       </c>
       <c r="H5" t="n">
-        <v>44.05</v>
+        <v>46.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.675</v>
+        <v>0.721</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -93250,7 +94416,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="L5" t="n">
         <v>2500</v>
@@ -93262,32 +94428,32 @@
         <v>3100</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003</v>
+        <v>-0.0018</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0127</v>
+        <v>-0.0003</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.004</v>
+        <v>-0.0003</v>
       </c>
       <c r="S5" t="n">
-        <v>25.8</v>
+        <v>-101.43</v>
       </c>
       <c r="T5" t="n">
-        <v>99.2</v>
+        <v>101.43</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>trending up +7.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19T14:48</t>
+          <t>2026-09-20T13:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -93302,11 +94468,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -93314,13 +94480,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>81529.5</v>
+        <v>80559</v>
       </c>
       <c r="H6" t="n">
-        <v>19.1</v>
+        <v>25.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -93328,63 +94494,63 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.22</v>
+        <v>1.37</v>
       </c>
       <c r="L6" t="n">
-        <v>81200</v>
+        <v>80400</v>
       </c>
       <c r="M6" t="n">
-        <v>81000</v>
+        <v>77800</v>
       </c>
       <c r="N6" t="n">
-        <v>82800</v>
+        <v>84000</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1034</v>
+        <v>0.2299</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0105</v>
+        <v>-0.0148</v>
       </c>
       <c r="S6" t="n">
-        <v>6.01</v>
+        <v>11.03</v>
       </c>
       <c r="T6" t="n">
-        <v>105.99</v>
+        <v>96.97</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 58% — default sell</t>
+          <t>IV rank 86% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19T14:48</t>
+          <t>2026-09-20T13:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -93392,13 +94558,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2639</v>
+        <v>80559</v>
       </c>
       <c r="H7" t="n">
-        <v>26.15</v>
+        <v>25.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.711</v>
+        <v>0.989</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -93406,44 +94572,44 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="L7" t="n">
-        <v>2630</v>
+        <v>80400</v>
       </c>
       <c r="M7" t="n">
-        <v>2600</v>
+        <v>77800</v>
       </c>
       <c r="N7" t="n">
-        <v>2740</v>
+        <v>84000</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0689</v>
+        <v>0.1255</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0046</v>
+        <v>-0.0116</v>
       </c>
       <c r="S7" t="n">
-        <v>9.140000000000001</v>
+        <v>-99.56</v>
       </c>
       <c r="T7" t="n">
-        <v>98.86</v>
+        <v>99.56</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 54% — default sell</t>
+          <t>trending up +6.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19T14:48</t>
+          <t>2026-09-20T13:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -93453,16 +94619,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -93470,51 +94636,129 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2639</v>
+        <v>2582.01</v>
       </c>
       <c r="H8" t="n">
-        <v>26.15</v>
+        <v>38.85</v>
       </c>
       <c r="I8" t="n">
-        <v>0.994</v>
+        <v>0.674</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="L8" t="n">
-        <v>2630</v>
+        <v>2580</v>
       </c>
       <c r="M8" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="N8" t="n">
-        <v>2740</v>
+        <v>2760</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0041</v>
+        <v>0.0001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0916</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0059</v>
+        <v>-0.0043</v>
       </c>
       <c r="S8" t="n">
-        <v>-99.45999999999999</v>
+        <v>14.88</v>
       </c>
       <c r="T8" t="n">
-        <v>99.45999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +4.5% — skewed fly</t>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-20T19:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2629.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2610</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-101.72</v>
+      </c>
+      <c r="T9" t="n">
+        <v>101.72</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>trending up +9.5% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -93535,7 +94779,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19T21:54:14.244905 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-20T22:01:25.997842 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1023"/>
+  <dimension ref="A1:Y1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -91447,7 +91447,7 @@
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G998" t="n">
@@ -91492,7 +91492,17 @@
         <v>100.94</v>
       </c>
       <c r="U998" t="inlineStr"/>
-      <c r="X998" t="inlineStr"/>
+      <c r="V998" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="W998" t="n">
+        <v>-2.438</v>
+      </c>
+      <c r="X998" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y998" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -91525,7 +91535,7 @@
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G999" t="n">
@@ -91570,7 +91580,17 @@
         <v>103.28</v>
       </c>
       <c r="U999" t="inlineStr"/>
-      <c r="X999" t="inlineStr"/>
+      <c r="V999" t="n">
+        <v>-79.02</v>
+      </c>
+      <c r="W999" t="n">
+        <v>-7.902</v>
+      </c>
+      <c r="X999" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y999" t="inlineStr">
         <is>
           <t>trending up +4.9% — skewed fly</t>
@@ -93233,7 +93253,7 @@
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1018" t="n">
@@ -93278,7 +93298,17 @@
         <v>101.43</v>
       </c>
       <c r="U1018" t="inlineStr"/>
-      <c r="X1018" t="inlineStr"/>
+      <c r="V1018" t="n">
+        <v>-63.3</v>
+      </c>
+      <c r="W1018" t="n">
+        <v>-6.33</v>
+      </c>
+      <c r="X1018" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y1018" t="inlineStr">
         <is>
           <t>trending up +7.4% — skewed fly</t>
@@ -93311,7 +93341,7 @@
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1019" t="n">
@@ -93355,8 +93385,22 @@
       <c r="T1019" t="n">
         <v>96.97</v>
       </c>
-      <c r="U1019" t="inlineStr"/>
-      <c r="X1019" t="inlineStr"/>
+      <c r="U1019" t="inlineStr">
+        <is>
+          <t>81426.6</t>
+        </is>
+      </c>
+      <c r="V1019" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="W1019" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="X1019" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y1019" t="inlineStr">
         <is>
           <t>IV rank 86% rich — sell premium</t>
@@ -93389,7 +93433,7 @@
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1020" t="n">
@@ -93434,7 +93478,17 @@
         <v>99.56</v>
       </c>
       <c r="U1020" t="inlineStr"/>
-      <c r="X1020" t="inlineStr"/>
+      <c r="V1020" t="n">
+        <v>-57.72</v>
+      </c>
+      <c r="W1020" t="n">
+        <v>-5.772</v>
+      </c>
+      <c r="X1020" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y1020" t="inlineStr">
         <is>
           <t>trending up +6.4% — skewed fly</t>
@@ -93467,7 +93521,7 @@
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1021" t="n">
@@ -93512,7 +93566,17 @@
         <v>99.12</v>
       </c>
       <c r="U1021" t="inlineStr"/>
-      <c r="X1021" t="inlineStr"/>
+      <c r="V1021" t="n">
+        <v>-56.75</v>
+      </c>
+      <c r="W1021" t="n">
+        <v>-5.675</v>
+      </c>
+      <c r="X1021" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y1021" t="inlineStr">
         <is>
           <t>IV rank 90% rich — sell premium</t>
@@ -93633,7 +93697,7 @@
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1023" t="n">
@@ -93678,10 +93742,1562 @@
         <v>101.72</v>
       </c>
       <c r="U1023" t="inlineStr"/>
-      <c r="X1023" t="inlineStr"/>
+      <c r="V1023" t="n">
+        <v>-66.47</v>
+      </c>
+      <c r="W1023" t="n">
+        <v>-6.647</v>
+      </c>
+      <c r="X1023" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y1023" t="inlineStr">
         <is>
           <t>trending up +9.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-09-21T01:41</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1024" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
+        <v>81426.60000000001</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1024" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L1024" t="n">
+        <v>81200</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O1024" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1024" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="Q1024" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="S1024" t="n">
+        <v>-95.79000000000001</v>
+      </c>
+      <c r="T1024" t="n">
+        <v>95.79000000000001</v>
+      </c>
+      <c r="U1024" t="inlineStr">
+        <is>
+          <t>81426.6</t>
+        </is>
+      </c>
+      <c r="V1024" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="W1024" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="X1024" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1024" t="inlineStr">
+        <is>
+          <t>trending up +7.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-09-21T01:41</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1025" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1025" t="n">
+        <v>2678.47</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1025" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>2640</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N1025" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1025" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P1025" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="Q1025" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="S1025" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="T1025" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="U1025" t="inlineStr">
+        <is>
+          <t>2678.47</t>
+        </is>
+      </c>
+      <c r="V1025" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="W1025" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="X1025" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1025" t="inlineStr">
+        <is>
+          <t>IV rank 100% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-09-21T01:41</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1026" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1026" t="n">
+        <v>2678.47</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1026" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L1026" t="n">
+        <v>2640</v>
+      </c>
+      <c r="M1026" t="n">
+        <v>2440</v>
+      </c>
+      <c r="N1026" t="n">
+        <v>2760</v>
+      </c>
+      <c r="O1026" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="P1026" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="Q1026" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="S1026" t="n">
+        <v>-98.95</v>
+      </c>
+      <c r="T1026" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="U1026" t="inlineStr">
+        <is>
+          <t>2678.47</t>
+        </is>
+      </c>
+      <c r="V1026" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="W1026" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="X1026" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1026" t="inlineStr">
+        <is>
+          <t>trending up +12.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-09-21T01:41</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1027" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>2678.47</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1027" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N1027" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1027" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="P1027" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="Q1027" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="S1027" t="n">
+        <v>-98.45999999999999</v>
+      </c>
+      <c r="T1027" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="U1027" t="inlineStr"/>
+      <c r="V1027" t="n">
+        <v>-64.29000000000001</v>
+      </c>
+      <c r="W1027" t="n">
+        <v>-6.429</v>
+      </c>
+      <c r="X1027" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1027" t="inlineStr">
+        <is>
+          <t>trending up +12.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-09-21T07:11</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1028" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1028" t="n">
+        <v>81513.5</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1028" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L1028" t="n">
+        <v>81600</v>
+      </c>
+      <c r="M1028" t="n">
+        <v>79600</v>
+      </c>
+      <c r="N1028" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O1028" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1028" t="n">
+        <v>0.7043</v>
+      </c>
+      <c r="Q1028" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="S1028" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="T1028" t="n">
+        <v>101.97</v>
+      </c>
+      <c r="U1028" t="inlineStr">
+        <is>
+          <t>81513.5</t>
+        </is>
+      </c>
+      <c r="V1028" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="W1028" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="X1028" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1028" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-09-21T07:11</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1029" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1029" t="n">
+        <v>81513.5</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1029" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L1029" t="n">
+        <v>81600</v>
+      </c>
+      <c r="M1029" t="n">
+        <v>79600</v>
+      </c>
+      <c r="N1029" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O1029" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P1029" t="n">
+        <v>0.8788</v>
+      </c>
+      <c r="Q1029" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="S1029" t="n">
+        <v>-93.36</v>
+      </c>
+      <c r="T1029" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="U1029" t="inlineStr">
+        <is>
+          <t>81513.5</t>
+        </is>
+      </c>
+      <c r="V1029" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W1029" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="X1029" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1029" t="inlineStr">
+        <is>
+          <t>trending up +7.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-09-21T07:11</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1030" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1030" t="n">
+        <v>2657.85</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="I1030" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1030" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="L1030" t="n">
+        <v>2650</v>
+      </c>
+      <c r="M1030" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1030" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O1030" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P1030" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="Q1030" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S1030" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="T1030" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="U1030" t="inlineStr">
+        <is>
+          <t>2657.85</t>
+        </is>
+      </c>
+      <c r="V1030" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="W1030" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="X1030" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1030" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-09-21T07:11</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E1031" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1031" t="n">
+        <v>2657.85</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="I1031" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1031" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="L1031" t="n">
+        <v>2650</v>
+      </c>
+      <c r="M1031" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1031" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O1031" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="P1031" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="Q1031" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S1031" t="n">
+        <v>-101.38</v>
+      </c>
+      <c r="T1031" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="U1031" t="inlineStr">
+        <is>
+          <t>2657.85</t>
+        </is>
+      </c>
+      <c r="V1031" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="W1031" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="X1031" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1031" t="inlineStr">
+        <is>
+          <t>trending up +11.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:08</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1032" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1032" t="n">
+        <v>85154</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I1032" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1032" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="L1032" t="n">
+        <v>84800</v>
+      </c>
+      <c r="M1032" t="n">
+        <v>79200</v>
+      </c>
+      <c r="N1032" t="n">
+        <v>88000</v>
+      </c>
+      <c r="O1032" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1032" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="Q1032" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="S1032" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="T1032" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="U1032" t="inlineStr"/>
+      <c r="X1032" t="inlineStr"/>
+      <c r="Y1032" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:08</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1033" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1033" t="n">
+        <v>85154</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I1033" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1033" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="L1033" t="n">
+        <v>84800</v>
+      </c>
+      <c r="M1033" t="n">
+        <v>79200</v>
+      </c>
+      <c r="N1033" t="n">
+        <v>88000</v>
+      </c>
+      <c r="O1033" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P1033" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="Q1033" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S1033" t="n">
+        <v>-94.37</v>
+      </c>
+      <c r="T1033" t="n">
+        <v>94.37</v>
+      </c>
+      <c r="U1033" t="inlineStr"/>
+      <c r="V1033" t="n">
+        <v>-79.09</v>
+      </c>
+      <c r="W1033" t="n">
+        <v>-7.909</v>
+      </c>
+      <c r="X1033" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1033" t="inlineStr">
+        <is>
+          <t>trending up +12.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:09</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1034" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1034" t="n">
+        <v>85154</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="I1034" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1034" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="L1034" t="n">
+        <v>81000</v>
+      </c>
+      <c r="M1034" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N1034" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1034" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="Q1034" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="S1034" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="T1034" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="U1034" t="inlineStr"/>
+      <c r="X1034" t="inlineStr"/>
+      <c r="Y1034" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:09</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1035" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1035" t="n">
+        <v>85154</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1035" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="L1035" t="n">
+        <v>81000</v>
+      </c>
+      <c r="M1035" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N1035" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1035" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P1035" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="Q1035" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="S1035" t="n">
+        <v>-101.41</v>
+      </c>
+      <c r="T1035" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="U1035" t="inlineStr"/>
+      <c r="V1035" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="W1035" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="X1035" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1035" t="inlineStr">
+        <is>
+          <t>trending up +12.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:09</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1036" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1036" t="n">
+        <v>2714.77</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I1036" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1036" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L1036" t="n">
+        <v>2690</v>
+      </c>
+      <c r="M1036" t="n">
+        <v>2520</v>
+      </c>
+      <c r="N1036" t="n">
+        <v>2880</v>
+      </c>
+      <c r="O1036" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P1036" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="Q1036" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="S1036" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="T1036" t="n">
+        <v>101.36</v>
+      </c>
+      <c r="U1036" t="inlineStr"/>
+      <c r="X1036" t="inlineStr"/>
+      <c r="Y1036" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:09</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1037" t="n">
+        <v>340</v>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1037" t="n">
+        <v>2714.77</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I1037" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1037" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L1037" t="n">
+        <v>2690</v>
+      </c>
+      <c r="M1037" t="n">
+        <v>2520</v>
+      </c>
+      <c r="N1037" t="n">
+        <v>2880</v>
+      </c>
+      <c r="O1037" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="P1037" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="Q1037" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="S1037" t="n">
+        <v>-98.94</v>
+      </c>
+      <c r="T1037" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="U1037" t="inlineStr"/>
+      <c r="V1037" t="n">
+        <v>-78.2</v>
+      </c>
+      <c r="W1037" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="X1037" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y1037" t="inlineStr">
+        <is>
+          <t>trending up +13.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-09-21T22:43</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1038" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1038" t="n">
+        <v>86437.10000000001</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I1038" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1038" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="L1038" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M1038" t="n">
+        <v>83000</v>
+      </c>
+      <c r="N1038" t="n">
+        <v>88400</v>
+      </c>
+      <c r="O1038" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1038" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="Q1038" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="S1038" t="n">
+        <v>-107.37</v>
+      </c>
+      <c r="T1038" t="n">
+        <v>107.37</v>
+      </c>
+      <c r="U1038" t="inlineStr"/>
+      <c r="X1038" t="inlineStr"/>
+      <c r="Y1038" t="inlineStr">
+        <is>
+          <t>trending up +14.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-09-21T22:43</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1039" t="n">
+        <v>150</v>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1039" t="n">
+        <v>86437.10000000001</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="I1039" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1039" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="L1039" t="n">
+        <v>82000</v>
+      </c>
+      <c r="M1039" t="n">
+        <v>51000</v>
+      </c>
+      <c r="N1039" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1039" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P1039" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="Q1039" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S1039" t="n">
+        <v>-98.22</v>
+      </c>
+      <c r="T1039" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="U1039" t="inlineStr"/>
+      <c r="X1039" t="inlineStr"/>
+      <c r="Y1039" t="inlineStr">
+        <is>
+          <t>trending up +14.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-09-21T22:43</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1040" t="n">
+        <v>270</v>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1040" t="n">
+        <v>2776.26</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I1040" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1040" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L1040" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1040" t="n">
+        <v>2520</v>
+      </c>
+      <c r="N1040" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1040" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="P1040" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="Q1040" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="S1040" t="n">
+        <v>-99.41</v>
+      </c>
+      <c r="T1040" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="U1040" t="inlineStr"/>
+      <c r="X1040" t="inlineStr"/>
+      <c r="Y1040" t="inlineStr">
+        <is>
+          <t>trending up +16.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-09-21T22:43</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1041" t="n">
+        <v>310</v>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1041" t="n">
+        <v>2776.26</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="I1041" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1041" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="L1041" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M1041" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N1041" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1041" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="P1041" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="Q1041" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="S1041" t="n">
+        <v>-100.81</v>
+      </c>
+      <c r="T1041" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="U1041" t="inlineStr"/>
+      <c r="X1041" t="inlineStr"/>
+      <c r="Y1041" t="inlineStr">
+        <is>
+          <t>trending up +16.2% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -93752,22 +95368,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C2" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>5.36</v>
+        <v>4.98</v>
       </c>
       <c r="E2" t="n">
-        <v>2800.38</v>
+        <v>2781.22</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="G2" t="n">
-        <v>280.04</v>
+        <v>278.12</v>
       </c>
     </row>
     <row r="3">
@@ -93823,51 +95439,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>202</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>67.3</v>
+        <v>57.6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="E5" t="n">
-        <v>-259.32</v>
+        <v>-361.02</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.28</v>
+        <v>-10.94</v>
       </c>
       <c r="G5" t="n">
-        <v>-25.93</v>
+        <v>-36.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>210</v>
       </c>
       <c r="C6" t="n">
-        <v>59.4</v>
+        <v>66.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.34</v>
+        <v>0.68</v>
       </c>
       <c r="E6" t="n">
-        <v>-336.64</v>
+        <v>-519.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.52</v>
+        <v>-2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>-33.66</v>
+        <v>-51.98</v>
       </c>
     </row>
     <row r="7">
@@ -93877,22 +95493,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="E7" t="n">
-        <v>-720.87</v>
+        <v>-987.98</v>
       </c>
       <c r="F7" t="n">
-        <v>-45.05</v>
+        <v>-49.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-72.09</v>
+        <v>-98.8</v>
       </c>
     </row>
     <row r="8">
@@ -94141,12 +95757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43</t>
+          <t>2026-09-18T21:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -94160,7 +95776,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -94168,13 +95784,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>80953.10000000001</v>
+        <v>2635.34</v>
       </c>
       <c r="H2" t="n">
-        <v>31.75</v>
+        <v>44.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -94182,44 +95798,44 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.11</v>
+        <v>2.63</v>
       </c>
       <c r="L2" t="n">
-        <v>78000</v>
+        <v>2500</v>
       </c>
       <c r="M2" t="n">
-        <v>51000</v>
+        <v>1600</v>
       </c>
       <c r="N2" t="n">
-        <v>93000</v>
+        <v>3100</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0.0003</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0424</v>
+        <v>0.0127</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0192</v>
+        <v>-0.004</v>
       </c>
       <c r="S2" t="n">
-        <v>19.06</v>
+        <v>25.8</v>
       </c>
       <c r="T2" t="n">
-        <v>100.94</v>
+        <v>99.2</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43</t>
+          <t>2026-09-21T14:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -94229,16 +95845,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -94246,63 +95862,63 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>80953.10000000001</v>
+        <v>85154</v>
       </c>
       <c r="H3" t="n">
-        <v>31.75</v>
+        <v>44.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.654</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="L3" t="n">
-        <v>78000</v>
+        <v>84800</v>
       </c>
       <c r="M3" t="n">
-        <v>51000</v>
+        <v>79200</v>
       </c>
       <c r="N3" t="n">
-        <v>93000</v>
+        <v>88000</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.1628</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0033</v>
+        <v>-0.0072</v>
       </c>
       <c r="S3" t="n">
-        <v>-103.28</v>
+        <v>9.25</v>
       </c>
       <c r="T3" t="n">
-        <v>103.28</v>
+        <v>98.75</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending up +4.9% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18T21:42</t>
+          <t>2026-09-21T14:09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -94316,7 +95932,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -94324,13 +95940,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2635.34</v>
+        <v>85154</v>
       </c>
       <c r="H4" t="n">
-        <v>44.05</v>
+        <v>44.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.675</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -94338,44 +95954,44 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.63</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>2500</v>
+        <v>81000</v>
       </c>
       <c r="M4" t="n">
-        <v>1600</v>
+        <v>51000</v>
       </c>
       <c r="N4" t="n">
-        <v>3100</v>
+        <v>93000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0127</v>
+        <v>0.0684</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.004</v>
+        <v>-0.0131</v>
       </c>
       <c r="S4" t="n">
-        <v>25.8</v>
+        <v>18.62</v>
       </c>
       <c r="T4" t="n">
-        <v>99.2</v>
+        <v>101.38</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20T08:33</t>
+          <t>2026-09-21T14:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -94385,16 +96001,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -94402,58 +96018,58 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2579.47</v>
+        <v>2714.77</v>
       </c>
       <c r="H5" t="n">
-        <v>46.6</v>
+        <v>55.7</v>
       </c>
       <c r="I5" t="n">
-        <v>0.721</v>
+        <v>0.666</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.43</v>
+        <v>0.87</v>
       </c>
       <c r="L5" t="n">
-        <v>2500</v>
+        <v>2690</v>
       </c>
       <c r="M5" t="n">
-        <v>1600</v>
+        <v>2520</v>
       </c>
       <c r="N5" t="n">
-        <v>3100</v>
+        <v>2880</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0018</v>
+        <v>0.0004</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0003</v>
+        <v>0.1027</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0033</v>
       </c>
       <c r="S5" t="n">
-        <v>-101.43</v>
+        <v>18.64</v>
       </c>
       <c r="T5" t="n">
-        <v>101.43</v>
+        <v>101.36</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>trending up +7.4% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20T13:13</t>
+          <t>2026-09-21T22:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -94463,16 +96079,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -94480,58 +96096,58 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>80559</v>
+        <v>86437.10000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.966</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.37</v>
+        <v>6.22</v>
       </c>
       <c r="L6" t="n">
-        <v>80400</v>
+        <v>86000</v>
       </c>
       <c r="M6" t="n">
-        <v>77800</v>
+        <v>83000</v>
       </c>
       <c r="N6" t="n">
-        <v>84000</v>
+        <v>88400</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>-0.0005</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2299</v>
+        <v>0.2744</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0148</v>
+        <v>-0.0102</v>
       </c>
       <c r="S6" t="n">
-        <v>11.03</v>
+        <v>-107.37</v>
       </c>
       <c r="T6" t="n">
-        <v>96.97</v>
+        <v>107.37</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>IV rank 86% rich — sell premium</t>
+          <t>trending up +14.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20T13:13</t>
+          <t>2026-09-21T22:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -94541,16 +96157,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -94558,58 +96174,58 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>80559</v>
+        <v>86437.10000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>25.7</v>
+        <v>37.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.989</v>
+        <v>0.629</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.37</v>
+        <v>11.88</v>
       </c>
       <c r="L7" t="n">
-        <v>80400</v>
+        <v>82000</v>
       </c>
       <c r="M7" t="n">
-        <v>77800</v>
+        <v>51000</v>
       </c>
       <c r="N7" t="n">
-        <v>84000</v>
+        <v>93000</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1255</v>
+        <v>-0.0001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0116</v>
+        <v>0.0002</v>
       </c>
       <c r="S7" t="n">
-        <v>-99.56</v>
+        <v>-98.22</v>
       </c>
       <c r="T7" t="n">
-        <v>99.56</v>
+        <v>98.22</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending up +6.4% — skewed fly</t>
+          <t>trending up +14.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20T13:13</t>
+          <t>2026-09-21T22:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -94619,16 +96235,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -94636,58 +96252,58 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2582.01</v>
+        <v>2776.26</v>
       </c>
       <c r="H8" t="n">
-        <v>38.85</v>
+        <v>39.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.674</v>
+        <v>0.848</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.18</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>2580</v>
+        <v>2740</v>
       </c>
       <c r="M8" t="n">
-        <v>2500</v>
+        <v>2520</v>
       </c>
       <c r="N8" t="n">
-        <v>2760</v>
+        <v>2920</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0001</v>
+        <v>-0.0034</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0916</v>
+        <v>0.0793</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0043</v>
+        <v>-0.0019</v>
       </c>
       <c r="S8" t="n">
-        <v>14.88</v>
+        <v>-99.41</v>
       </c>
       <c r="T8" t="n">
-        <v>99.12</v>
+        <v>99.41</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>IV rank 90% rich — sell premium</t>
+          <t>trending up +16.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20T19:14</t>
+          <t>2026-09-21T22:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -94697,16 +96313,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -94714,13 +96330,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2629.02</v>
+        <v>2776.26</v>
       </c>
       <c r="H9" t="n">
-        <v>38.45</v>
+        <v>52.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.84</v>
+        <v>0.741</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -94728,37 +96344,37 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.56</v>
+        <v>3.74</v>
       </c>
       <c r="L9" t="n">
-        <v>2610</v>
+        <v>2600</v>
       </c>
       <c r="M9" t="n">
-        <v>2440</v>
+        <v>1600</v>
       </c>
       <c r="N9" t="n">
-        <v>2760</v>
+        <v>3100</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0039</v>
+        <v>-0.0016</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0496</v>
+        <v>0.0027</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0018</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-101.72</v>
+        <v>-100.81</v>
       </c>
       <c r="T9" t="n">
-        <v>101.72</v>
+        <v>100.81</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>trending up +9.5% — skewed fly</t>
+          <t>trending up +16.2% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -94779,7 +96395,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20T22:01:25.997842 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-21T22:55:13.447826 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1041"/>
+  <dimension ref="A1:Y1060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -94517,7 +94517,7 @@
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1032" t="n">
@@ -94562,7 +94562,17 @@
         <v>98.75</v>
       </c>
       <c r="U1032" t="inlineStr"/>
-      <c r="X1032" t="inlineStr"/>
+      <c r="V1032" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="W1032" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="X1032" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="Y1032" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -94683,7 +94693,7 @@
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1034" t="n">
@@ -94728,7 +94738,17 @@
         <v>101.38</v>
       </c>
       <c r="U1034" t="inlineStr"/>
-      <c r="X1034" t="inlineStr"/>
+      <c r="V1034" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="W1034" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="X1034" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="Y1034" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -94849,7 +94869,7 @@
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1036" t="n">
@@ -94893,8 +94913,22 @@
       <c r="T1036" t="n">
         <v>101.36</v>
       </c>
-      <c r="U1036" t="inlineStr"/>
-      <c r="X1036" t="inlineStr"/>
+      <c r="U1036" t="inlineStr">
+        <is>
+          <t>2751.41</t>
+        </is>
+      </c>
+      <c r="V1036" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="W1036" t="n">
+        <v>1.698</v>
+      </c>
+      <c r="X1036" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="Y1036" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -95015,7 +95049,7 @@
       </c>
       <c r="F1038" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1038" t="n">
@@ -95059,8 +95093,22 @@
       <c r="T1038" t="n">
         <v>107.37</v>
       </c>
-      <c r="U1038" t="inlineStr"/>
-      <c r="X1038" t="inlineStr"/>
+      <c r="U1038" t="inlineStr">
+        <is>
+          <t>85837.9</t>
+        </is>
+      </c>
+      <c r="V1038" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="W1038" t="n">
+        <v>4.474</v>
+      </c>
+      <c r="X1038" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="Y1038" t="inlineStr">
         <is>
           <t>trending up +14.2% — skewed fly</t>
@@ -95171,7 +95219,7 @@
       </c>
       <c r="F1040" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1040" t="n">
@@ -95215,8 +95263,22 @@
       <c r="T1040" t="n">
         <v>99.41</v>
       </c>
-      <c r="U1040" t="inlineStr"/>
-      <c r="X1040" t="inlineStr"/>
+      <c r="U1040" t="inlineStr">
+        <is>
+          <t>2751.41</t>
+        </is>
+      </c>
+      <c r="V1040" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="W1040" t="n">
+        <v>7.015</v>
+      </c>
+      <c r="X1040" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="Y1040" t="inlineStr">
         <is>
           <t>trending up +16.2% — skewed fly</t>
@@ -95298,6 +95360,1638 @@
       <c r="Y1041" t="inlineStr">
         <is>
           <t>trending up +16.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-09-22T01:12</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1042" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1042" t="n">
+        <v>85837.89999999999</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I1042" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1042" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L1042" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M1042" t="n">
+        <v>83400</v>
+      </c>
+      <c r="N1042" t="n">
+        <v>88800</v>
+      </c>
+      <c r="O1042" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1042" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="Q1042" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="S1042" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="T1042" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="U1042" t="inlineStr">
+        <is>
+          <t>85837.9</t>
+        </is>
+      </c>
+      <c r="V1042" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="W1042" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="X1042" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1042" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-09-22T01:12</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E1043" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1043" t="n">
+        <v>85818.60000000001</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="I1043" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1043" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L1043" t="n">
+        <v>78500</v>
+      </c>
+      <c r="M1043" t="n">
+        <v>78500</v>
+      </c>
+      <c r="N1043" t="n">
+        <v>87000</v>
+      </c>
+      <c r="O1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1043" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="Q1043" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="S1043" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="T1043" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="U1043" t="inlineStr"/>
+      <c r="X1043" t="inlineStr"/>
+      <c r="Y1043" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-09-22T01:12</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E1044" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1044" t="n">
+        <v>85818.60000000001</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="I1044" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1044" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L1044" t="n">
+        <v>78500</v>
+      </c>
+      <c r="M1044" t="n">
+        <v>78500</v>
+      </c>
+      <c r="N1044" t="n">
+        <v>87000</v>
+      </c>
+      <c r="O1044" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P1044" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="Q1044" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="S1044" t="n">
+        <v>-102.28</v>
+      </c>
+      <c r="T1044" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="U1044" t="inlineStr"/>
+      <c r="X1044" t="inlineStr"/>
+      <c r="Y1044" t="inlineStr">
+        <is>
+          <t>trending up +12.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-09-22T01:12</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E1045" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1045" t="n">
+        <v>2751.41</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="I1045" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1045" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L1045" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M1045" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1045" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1045" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P1045" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q1045" t="n">
+        <v>-0.0055</v>
+      </c>
+      <c r="S1045" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="T1045" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="U1045" t="inlineStr"/>
+      <c r="X1045" t="inlineStr"/>
+      <c r="Y1045" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-09-22T01:12</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly_wk</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E1046" t="n">
+        <v>420</v>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1046" t="n">
+        <v>2751.41</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="I1046" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1046" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L1046" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M1046" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1046" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1046" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P1046" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="Q1046" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="S1046" t="n">
+        <v>-99.41</v>
+      </c>
+      <c r="T1046" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="U1046" t="inlineStr"/>
+      <c r="X1046" t="inlineStr"/>
+      <c r="Y1046" t="inlineStr">
+        <is>
+          <t>trending up +12.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:14</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1047" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1047" t="n">
+        <v>85379.5</v>
+      </c>
+      <c r="H1047" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="I1047" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1047" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L1047" t="n">
+        <v>85400</v>
+      </c>
+      <c r="M1047" t="n">
+        <v>84000</v>
+      </c>
+      <c r="N1047" t="n">
+        <v>88800</v>
+      </c>
+      <c r="O1047" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1047" t="n">
+        <v>0.6027</v>
+      </c>
+      <c r="Q1047" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="S1047" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="T1047" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="U1047" t="inlineStr">
+        <is>
+          <t>85379.5</t>
+        </is>
+      </c>
+      <c r="V1047" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="W1047" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="X1047" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1047" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:14</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1048" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1048" t="n">
+        <v>85379.5</v>
+      </c>
+      <c r="H1048" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="I1048" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1048" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L1048" t="n">
+        <v>85400</v>
+      </c>
+      <c r="M1048" t="n">
+        <v>84000</v>
+      </c>
+      <c r="N1048" t="n">
+        <v>88800</v>
+      </c>
+      <c r="O1048" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P1048" t="n">
+        <v>0.8809</v>
+      </c>
+      <c r="Q1048" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="S1048" t="n">
+        <v>-98.78</v>
+      </c>
+      <c r="T1048" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="U1048" t="inlineStr">
+        <is>
+          <t>85379.5</t>
+        </is>
+      </c>
+      <c r="V1048" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W1048" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="X1048" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1048" t="inlineStr">
+        <is>
+          <t>trending up +11.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:14</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1049" t="n">
+        <v>180</v>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1049" t="n">
+        <v>2730.72</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="I1049" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1049" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L1049" t="n">
+        <v>2730</v>
+      </c>
+      <c r="M1049" t="n">
+        <v>2660</v>
+      </c>
+      <c r="N1049" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1049" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P1049" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="Q1049" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="S1049" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="T1049" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U1049" t="inlineStr">
+        <is>
+          <t>2730.72</t>
+        </is>
+      </c>
+      <c r="V1049" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="W1049" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="X1049" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1049" t="inlineStr">
+        <is>
+          <t>IV rank 90% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:14</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1050" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1050" t="n">
+        <v>2730.72</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="I1050" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1050" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L1050" t="n">
+        <v>2730</v>
+      </c>
+      <c r="M1050" t="n">
+        <v>2660</v>
+      </c>
+      <c r="N1050" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1050" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="P1050" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q1050" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="S1050" t="n">
+        <v>-100.55</v>
+      </c>
+      <c r="T1050" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="U1050" t="inlineStr">
+        <is>
+          <t>2730.72</t>
+        </is>
+      </c>
+      <c r="V1050" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W1050" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="X1050" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1050" t="inlineStr">
+        <is>
+          <t>trending up +11.5% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:44</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1051" t="n">
+        <v>9190</v>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1051" t="n">
+        <v>86129.3</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I1051" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1051" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L1051" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M1051" t="n">
+        <v>86000</v>
+      </c>
+      <c r="N1051" t="n">
+        <v>88400</v>
+      </c>
+      <c r="O1051" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1051" t="n">
+        <v>-1.5229</v>
+      </c>
+      <c r="Q1051" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="S1051" t="n">
+        <v>-100.17</v>
+      </c>
+      <c r="T1051" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U1051" t="inlineStr">
+        <is>
+          <t>86129.3</t>
+        </is>
+      </c>
+      <c r="V1051" t="n">
+        <v>-103.85</v>
+      </c>
+      <c r="W1051" t="n">
+        <v>-10.385</v>
+      </c>
+      <c r="X1051" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1051" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:44</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1052" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1052" t="n">
+        <v>86129.3</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I1052" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1052" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L1052" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M1052" t="n">
+        <v>86000</v>
+      </c>
+      <c r="N1052" t="n">
+        <v>88400</v>
+      </c>
+      <c r="O1052" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P1052" t="n">
+        <v>0.9191</v>
+      </c>
+      <c r="Q1052" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="S1052" t="n">
+        <v>-100.16</v>
+      </c>
+      <c r="T1052" t="n">
+        <v>100.16</v>
+      </c>
+      <c r="U1052" t="inlineStr">
+        <is>
+          <t>86129.3</t>
+        </is>
+      </c>
+      <c r="V1052" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="W1052" t="n">
+        <v>-0.959</v>
+      </c>
+      <c r="X1052" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1052" t="inlineStr">
+        <is>
+          <t>trending up +12.7% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:44</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1053" t="n">
+        <v>103500</v>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1053" t="n">
+        <v>86129.3</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I1053" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1053" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L1053" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M1053" t="n">
+        <v>86000</v>
+      </c>
+      <c r="N1053" t="n">
+        <v>88400</v>
+      </c>
+      <c r="O1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1053" t="n">
+        <v>-0.4218</v>
+      </c>
+      <c r="Q1053" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="S1053" t="n">
+        <v>-103.5</v>
+      </c>
+      <c r="T1053" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="U1053" t="inlineStr">
+        <is>
+          <t>86129.3</t>
+        </is>
+      </c>
+      <c r="V1053" t="n">
+        <v>-103.5</v>
+      </c>
+      <c r="W1053" t="n">
+        <v>-10.35</v>
+      </c>
+      <c r="X1053" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1053" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:44</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1054" t="n">
+        <v>30570</v>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1054" t="n">
+        <v>2746.87</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="I1054" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1054" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L1054" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1054" t="n">
+        <v>2660</v>
+      </c>
+      <c r="N1054" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1054" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="P1054" t="n">
+        <v>-0.5904</v>
+      </c>
+      <c r="Q1054" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="S1054" t="n">
+        <v>-100.88</v>
+      </c>
+      <c r="T1054" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="U1054" t="inlineStr">
+        <is>
+          <t>2746.87</t>
+        </is>
+      </c>
+      <c r="V1054" t="n">
+        <v>-103.94</v>
+      </c>
+      <c r="W1054" t="n">
+        <v>-10.394</v>
+      </c>
+      <c r="X1054" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1054" t="inlineStr">
+        <is>
+          <t>IV rank 0% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:44</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E1055" t="n">
+        <v>130</v>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1055" t="n">
+        <v>2746.87</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="I1055" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1055" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L1055" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1055" t="n">
+        <v>2660</v>
+      </c>
+      <c r="N1055" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1055" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="P1055" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="Q1055" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="S1055" t="n">
+        <v>-96.79000000000001</v>
+      </c>
+      <c r="T1055" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="U1055" t="inlineStr">
+        <is>
+          <t>2746.87</t>
+        </is>
+      </c>
+      <c r="V1055" t="n">
+        <v>-9.67</v>
+      </c>
+      <c r="W1055" t="n">
+        <v>-0.967</v>
+      </c>
+      <c r="X1055" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1055" t="inlineStr">
+        <is>
+          <t>trending up +12.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:44</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1056" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1056" t="n">
+        <v>86500.10000000001</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I1056" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1056" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="L1056" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M1056" t="n">
+        <v>82400</v>
+      </c>
+      <c r="N1056" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1056" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="Q1056" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="S1056" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="T1056" t="n">
+        <v>98.19</v>
+      </c>
+      <c r="U1056" t="inlineStr"/>
+      <c r="X1056" t="inlineStr"/>
+      <c r="Y1056" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:44</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1057" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1057" t="n">
+        <v>86500.10000000001</v>
+      </c>
+      <c r="H1057" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I1057" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1057" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="L1057" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M1057" t="n">
+        <v>82400</v>
+      </c>
+      <c r="N1057" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1057" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P1057" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="Q1057" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="S1057" t="n">
+        <v>-94.84999999999999</v>
+      </c>
+      <c r="T1057" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="U1057" t="inlineStr"/>
+      <c r="X1057" t="inlineStr"/>
+      <c r="Y1057" t="inlineStr">
+        <is>
+          <t>trending up +13.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:44</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1058" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1058" t="n">
+        <v>2748.44</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>46</v>
+      </c>
+      <c r="I1058" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1058" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L1058" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1058" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N1058" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1058" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1058" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="Q1058" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S1058" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="T1058" t="n">
+        <v>97.45</v>
+      </c>
+      <c r="U1058" t="inlineStr"/>
+      <c r="V1058" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="W1058" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="X1058" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Y1058" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:44</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1059" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1059" t="n">
+        <v>2748.44</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>46</v>
+      </c>
+      <c r="I1059" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1059" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L1059" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1059" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N1059" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1059" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="P1059" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="Q1059" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S1059" t="n">
+        <v>-101.28</v>
+      </c>
+      <c r="T1059" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="U1059" t="inlineStr"/>
+      <c r="X1059" t="inlineStr"/>
+      <c r="Y1059" t="inlineStr">
+        <is>
+          <t>trending up +12.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-09-22T22:13</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1060" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1060" t="n">
+        <v>2738.91</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="I1060" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1060" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L1060" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1060" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N1060" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1060" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1060" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q1060" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="S1060" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T1060" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="U1060" t="inlineStr"/>
+      <c r="X1060" t="inlineStr"/>
+      <c r="Y1060" t="inlineStr">
+        <is>
+          <t>IV rank 61% — default sell</t>
         </is>
       </c>
     </row>
@@ -95368,22 +97062,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C2" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>4.98</v>
+        <v>5.05</v>
       </c>
       <c r="E2" t="n">
-        <v>2781.22</v>
+        <v>2833.3</v>
       </c>
       <c r="F2" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="G2" t="n">
-        <v>278.12</v>
+        <v>283.33</v>
       </c>
     </row>
     <row r="3">
@@ -95443,22 +97137,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>57.6</v>
+        <v>58.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="E5" t="n">
-        <v>-361.02</v>
+        <v>-352.36</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.94</v>
+        <v>-10.36</v>
       </c>
       <c r="G5" t="n">
-        <v>-36.1</v>
+        <v>-35.24</v>
       </c>
     </row>
     <row r="6">
@@ -95468,22 +97162,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C6" t="n">
         <v>66.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="n">
-        <v>-519.8</v>
+        <v>-419.58</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.48</v>
+        <v>-1.94</v>
       </c>
       <c r="G6" t="n">
-        <v>-51.98</v>
+        <v>-41.96</v>
       </c>
     </row>
     <row r="7">
@@ -95543,7 +97237,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
         <v>1.2</v>
@@ -95552,13 +97246,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-8156.69</v>
+        <v>-8364.48</v>
       </c>
       <c r="F9" t="n">
-        <v>-100.7</v>
+        <v>-100.78</v>
       </c>
       <c r="G9" t="n">
-        <v>-815.67</v>
+        <v>-836.45</v>
       </c>
     </row>
     <row r="10">
@@ -95568,7 +97262,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -95577,13 +97271,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-9980.82</v>
+        <v>-10084.32</v>
       </c>
       <c r="F10" t="n">
-        <v>-103.97</v>
+        <v>-103.96</v>
       </c>
       <c r="G10" t="n">
-        <v>-998.08</v>
+        <v>-1008.43</v>
       </c>
     </row>
   </sheetData>
@@ -95597,7 +97291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -95835,7 +97529,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21T14:08</t>
+          <t>2026-09-21T22:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -95845,16 +97539,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -95862,68 +97556,68 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>85154</v>
+        <v>86437.10000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>44.6</v>
+        <v>37.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.629</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5.08</v>
+        <v>11.88</v>
       </c>
       <c r="L3" t="n">
-        <v>84800</v>
+        <v>82000</v>
       </c>
       <c r="M3" t="n">
-        <v>79200</v>
+        <v>51000</v>
       </c>
       <c r="N3" t="n">
-        <v>88000</v>
+        <v>93000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1628</v>
+        <v>-0.0001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0072</v>
+        <v>0.0002</v>
       </c>
       <c r="S3" t="n">
-        <v>9.25</v>
+        <v>-98.22</v>
       </c>
       <c r="T3" t="n">
-        <v>98.75</v>
+        <v>98.22</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending up +14.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21T14:09</t>
+          <t>2026-09-21T22:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -95932,7 +97626,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -95940,13 +97634,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>85154</v>
+        <v>2776.26</v>
       </c>
       <c r="H4" t="n">
-        <v>44.25</v>
+        <v>52.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.741</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -95954,63 +97648,63 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.619999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="L4" t="n">
-        <v>81000</v>
+        <v>2600</v>
       </c>
       <c r="M4" t="n">
-        <v>51000</v>
+        <v>1600</v>
       </c>
       <c r="N4" t="n">
-        <v>93000</v>
+        <v>3100</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0684</v>
+        <v>0.0027</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0131</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>18.62</v>
+        <v>-100.81</v>
       </c>
       <c r="T4" t="n">
-        <v>101.38</v>
+        <v>100.81</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending up +16.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21T14:09</t>
+          <t>2026-09-22T01:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -96018,45 +97712,45 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2714.77</v>
+        <v>85818.60000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>55.7</v>
+        <v>38.35</v>
       </c>
       <c r="I5" t="n">
-        <v>0.666</v>
+        <v>0.678</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.87</v>
+        <v>1.28</v>
       </c>
       <c r="L5" t="n">
-        <v>2690</v>
+        <v>78500</v>
       </c>
       <c r="M5" t="n">
-        <v>2520</v>
+        <v>78500</v>
       </c>
       <c r="N5" t="n">
-        <v>2880</v>
+        <v>87000</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1027</v>
+        <v>0.0216</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0033</v>
+        <v>-0.013</v>
       </c>
       <c r="S5" t="n">
-        <v>18.64</v>
+        <v>22.65</v>
       </c>
       <c r="T5" t="n">
-        <v>101.36</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -96069,7 +97763,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21T22:43</t>
+          <t>2026-09-22T01:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -96079,16 +97773,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -96096,13 +97790,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>86437.10000000001</v>
+        <v>85818.60000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>26.5</v>
+        <v>38.35</v>
       </c>
       <c r="I6" t="n">
-        <v>0.966</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -96110,63 +97804,63 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.22</v>
+        <v>1.28</v>
       </c>
       <c r="L6" t="n">
-        <v>86000</v>
+        <v>78500</v>
       </c>
       <c r="M6" t="n">
-        <v>83000</v>
+        <v>78500</v>
       </c>
       <c r="N6" t="n">
-        <v>88400</v>
+        <v>87000</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2744</v>
+        <v>-0.0012</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0102</v>
+        <v>0.0012</v>
       </c>
       <c r="S6" t="n">
-        <v>-107.37</v>
+        <v>-102.28</v>
       </c>
       <c r="T6" t="n">
-        <v>107.37</v>
+        <v>102.28</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +14.2% — skewed fly</t>
+          <t>trending up +12.3% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21T22:43</t>
+          <t>2026-09-22T01:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -96174,58 +97868,58 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>86437.10000000001</v>
+        <v>2751.41</v>
       </c>
       <c r="H7" t="n">
-        <v>37.4</v>
+        <v>51.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.629</v>
+        <v>0.638</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>11.88</v>
+        <v>1.05</v>
       </c>
       <c r="L7" t="n">
-        <v>82000</v>
+        <v>2600</v>
       </c>
       <c r="M7" t="n">
-        <v>51000</v>
+        <v>2500</v>
       </c>
       <c r="N7" t="n">
-        <v>93000</v>
+        <v>3100</v>
       </c>
       <c r="O7" t="n">
         <v>-0.0002</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0001</v>
+        <v>0.012</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002</v>
+        <v>-0.0055</v>
       </c>
       <c r="S7" t="n">
-        <v>-98.22</v>
+        <v>20.53</v>
       </c>
       <c r="T7" t="n">
-        <v>98.22</v>
+        <v>99.47</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending up +14.2% — skewed fly</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21T22:43</t>
+          <t>2026-09-22T01:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -96235,16 +97929,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>270</v>
+        <v>420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -96252,13 +97946,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2776.26</v>
+        <v>2751.41</v>
       </c>
       <c r="H8" t="n">
-        <v>39.8</v>
+        <v>51.6</v>
       </c>
       <c r="I8" t="n">
-        <v>0.848</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -96266,25 +97960,25 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="L8" t="n">
-        <v>2740</v>
+        <v>2600</v>
       </c>
       <c r="M8" t="n">
-        <v>2520</v>
+        <v>2500</v>
       </c>
       <c r="N8" t="n">
-        <v>2920</v>
+        <v>3100</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0034</v>
+        <v>-0.0009</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0793</v>
+        <v>-0.0032</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0019</v>
+        <v>0.0012</v>
       </c>
       <c r="S8" t="n">
         <v>-99.41</v>
@@ -96296,33 +97990,33 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +16.2% — skewed fly</t>
+          <t>trending up +12.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21T22:43</t>
+          <t>2026-09-22T15:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -96330,13 +98024,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2776.26</v>
+        <v>86500.10000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>52.2</v>
+        <v>32.6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.741</v>
+        <v>0.696</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -96344,37 +98038,271 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="L9" t="n">
-        <v>2600</v>
+        <v>86000</v>
       </c>
       <c r="M9" t="n">
-        <v>1600</v>
+        <v>82400</v>
       </c>
       <c r="N9" t="n">
-        <v>3100</v>
+        <v>89600</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0016</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0027</v>
+        <v>0.2024</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0112</v>
       </c>
       <c r="S9" t="n">
-        <v>-100.81</v>
+        <v>9.81</v>
       </c>
       <c r="T9" t="n">
-        <v>100.81</v>
+        <v>98.19</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>trending up +16.2% — skewed fly</t>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:44</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>86500.10000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>82400</v>
+      </c>
+      <c r="N10" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-94.84999999999999</v>
+      </c>
+      <c r="T10" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>trending up +13.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:44</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>300</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2748.44</v>
+      </c>
+      <c r="H11" t="n">
+        <v>46</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-101.28</v>
+      </c>
+      <c r="T11" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>trending up +12.2% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-22T22:13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>190</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2738.91</v>
+      </c>
+      <c r="H12" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>IV rank 61% — default sell</t>
         </is>
       </c>
     </row>
@@ -96395,7 +98323,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21T22:55:13.447826 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-22T22:29:45.292684 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1060"/>
+  <dimension ref="A1:Y1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -91895,7 +91895,7 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1003" t="n">
@@ -91940,7 +91940,17 @@
         <v>99.2</v>
       </c>
       <c r="U1003" t="inlineStr"/>
-      <c r="X1003" t="inlineStr"/>
+      <c r="V1003" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="W1003" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="X1003" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="Y1003" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
@@ -95141,7 +95151,7 @@
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1039" t="n">
@@ -95186,7 +95196,17 @@
         <v>98.22</v>
       </c>
       <c r="U1039" t="inlineStr"/>
-      <c r="X1039" t="inlineStr"/>
+      <c r="V1039" t="n">
+        <v>72.91</v>
+      </c>
+      <c r="W1039" t="n">
+        <v>7.291</v>
+      </c>
+      <c r="X1039" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="Y1039" t="inlineStr">
         <is>
           <t>trending up +14.2% — skewed fly</t>
@@ -96621,7 +96641,7 @@
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1056" t="n">
@@ -96665,8 +96685,22 @@
       <c r="T1056" t="n">
         <v>98.19</v>
       </c>
-      <c r="U1056" t="inlineStr"/>
-      <c r="X1056" t="inlineStr"/>
+      <c r="U1056" t="inlineStr">
+        <is>
+          <t>86514.6</t>
+        </is>
+      </c>
+      <c r="V1056" t="n">
+        <v>9</v>
+      </c>
+      <c r="W1056" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X1056" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="Y1056" t="inlineStr">
         <is>
           <t>IV rank 96% rich — sell premium</t>
@@ -96699,7 +96733,7 @@
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1057" t="n">
@@ -96743,8 +96777,22 @@
       <c r="T1057" t="n">
         <v>94.84999999999999</v>
       </c>
-      <c r="U1057" t="inlineStr"/>
-      <c r="X1057" t="inlineStr"/>
+      <c r="U1057" t="inlineStr">
+        <is>
+          <t>86514.6</t>
+        </is>
+      </c>
+      <c r="V1057" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="W1057" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="X1057" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="Y1057" t="inlineStr">
         <is>
           <t>trending up +13.2% — skewed fly</t>
@@ -96865,7 +96913,7 @@
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1059" t="n">
@@ -96909,8 +96957,22 @@
       <c r="T1059" t="n">
         <v>101.28</v>
       </c>
-      <c r="U1059" t="inlineStr"/>
-      <c r="X1059" t="inlineStr"/>
+      <c r="U1059" t="inlineStr">
+        <is>
+          <t>2764.32</t>
+        </is>
+      </c>
+      <c r="V1059" t="n">
+        <v>-37.02</v>
+      </c>
+      <c r="W1059" t="n">
+        <v>-3.702</v>
+      </c>
+      <c r="X1059" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="Y1059" t="inlineStr">
         <is>
           <t>trending up +12.2% — skewed fly</t>
@@ -96943,7 +97005,7 @@
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1060" t="n">
@@ -96987,11 +97049,1587 @@
       <c r="T1060" t="n">
         <v>99.5</v>
       </c>
-      <c r="U1060" t="inlineStr"/>
-      <c r="X1060" t="inlineStr"/>
+      <c r="U1060" t="inlineStr">
+        <is>
+          <t>2764.32</t>
+        </is>
+      </c>
+      <c r="V1060" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="W1060" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="X1060" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="Y1060" t="inlineStr">
         <is>
           <t>IV rank 61% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:11</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1061" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1061" t="n">
+        <v>86956.60000000001</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="I1061" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1061" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L1061" t="n">
+        <v>86800</v>
+      </c>
+      <c r="M1061" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N1061" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1061" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="Q1061" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="S1061" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="T1061" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="U1061" t="inlineStr">
+        <is>
+          <t>86956.6</t>
+        </is>
+      </c>
+      <c r="V1061" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="W1061" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="X1061" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1061" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:11</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1062" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1062" t="n">
+        <v>86956.60000000001</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="I1062" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1062" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L1062" t="n">
+        <v>86800</v>
+      </c>
+      <c r="M1062" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N1062" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1062" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1062" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="Q1062" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="S1062" t="n">
+        <v>-101.3</v>
+      </c>
+      <c r="T1062" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="U1062" t="inlineStr">
+        <is>
+          <t>86956.6</t>
+        </is>
+      </c>
+      <c r="V1062" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="W1062" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="X1062" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1062" t="inlineStr">
+        <is>
+          <t>trending up +7.4% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:11</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1063" t="n">
+        <v>170</v>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1063" t="n">
+        <v>2771.67</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="I1063" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1063" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L1063" t="n">
+        <v>2760</v>
+      </c>
+      <c r="M1063" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N1063" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1063" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="P1063" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="Q1063" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S1063" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T1063" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="U1063" t="inlineStr">
+        <is>
+          <t>2771.67</t>
+        </is>
+      </c>
+      <c r="V1063" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W1063" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="X1063" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1063" t="inlineStr">
+        <is>
+          <t>IV rank 92% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:11</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1064" t="n">
+        <v>210</v>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1064" t="n">
+        <v>2771.67</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1064" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L1064" t="n">
+        <v>2760</v>
+      </c>
+      <c r="M1064" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N1064" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1064" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="P1064" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="Q1064" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="S1064" t="n">
+        <v>-100.86</v>
+      </c>
+      <c r="T1064" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="U1064" t="inlineStr">
+        <is>
+          <t>2771.67</t>
+        </is>
+      </c>
+      <c r="V1064" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="W1064" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="X1064" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1064" t="inlineStr">
+        <is>
+          <t>trending up +6.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:58</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1065" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1065" t="n">
+        <v>85863.39999999999</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I1065" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1065" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L1065" t="n">
+        <v>85800</v>
+      </c>
+      <c r="M1065" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N1065" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1065" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P1065" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="Q1065" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="S1065" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T1065" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="U1065" t="inlineStr">
+        <is>
+          <t>85863.4</t>
+        </is>
+      </c>
+      <c r="V1065" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="W1065" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="X1065" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1065" t="inlineStr">
+        <is>
+          <t>IV rank 40% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:58</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1066" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1066" t="n">
+        <v>85863.39999999999</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I1066" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1066" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L1066" t="n">
+        <v>85800</v>
+      </c>
+      <c r="M1066" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N1066" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1066" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1066" t="n">
+        <v>1.1861</v>
+      </c>
+      <c r="Q1066" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="S1066" t="n">
+        <v>-89.16</v>
+      </c>
+      <c r="T1066" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="U1066" t="inlineStr">
+        <is>
+          <t>85863.4</t>
+        </is>
+      </c>
+      <c r="V1066" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="W1066" t="n">
+        <v>-0.359</v>
+      </c>
+      <c r="X1066" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1066" t="inlineStr">
+        <is>
+          <t>trending up +6.0% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:58</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1067" t="n">
+        <v>1570</v>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1067" t="n">
+        <v>85863.39999999999</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I1067" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1067" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L1067" t="n">
+        <v>85800</v>
+      </c>
+      <c r="M1067" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N1067" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1067" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1067" t="n">
+        <v>-1.0742</v>
+      </c>
+      <c r="Q1067" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="S1067" t="n">
+        <v>-99.84999999999999</v>
+      </c>
+      <c r="T1067" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="U1067" t="inlineStr">
+        <is>
+          <t>85863.4</t>
+        </is>
+      </c>
+      <c r="V1067" t="n">
+        <v>-104.09</v>
+      </c>
+      <c r="W1067" t="n">
+        <v>-10.409</v>
+      </c>
+      <c r="X1067" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1067" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:58</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1068" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1068" t="n">
+        <v>85863.39999999999</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I1068" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1068" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L1068" t="n">
+        <v>85800</v>
+      </c>
+      <c r="M1068" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N1068" t="n">
+        <v>89600</v>
+      </c>
+      <c r="O1068" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P1068" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="Q1068" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="R1068" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S1068" t="n">
+        <v>-28.66</v>
+      </c>
+      <c r="T1068" t="n">
+        <v>100.66</v>
+      </c>
+      <c r="U1068" t="inlineStr">
+        <is>
+          <t>85863.4</t>
+        </is>
+      </c>
+      <c r="V1068" t="n">
+        <v>-17.35</v>
+      </c>
+      <c r="W1068" t="n">
+        <v>-1.735</v>
+      </c>
+      <c r="X1068" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1068" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.1 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:58</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1069" t="n">
+        <v>180</v>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1069" t="n">
+        <v>2734.3</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="I1069" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1069" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L1069" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1069" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N1069" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1069" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="P1069" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="Q1069" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="S1069" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="T1069" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="U1069" t="inlineStr">
+        <is>
+          <t>2734.3</t>
+        </is>
+      </c>
+      <c r="V1069" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="W1069" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="X1069" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1069" t="inlineStr">
+        <is>
+          <t>IV rank 37% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:58</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1070" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1070" t="n">
+        <v>2734.3</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="I1070" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1070" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L1070" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1070" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N1070" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1070" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="P1070" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="Q1070" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S1070" t="n">
+        <v>-99.70999999999999</v>
+      </c>
+      <c r="T1070" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="U1070" t="inlineStr">
+        <is>
+          <t>2734.3</t>
+        </is>
+      </c>
+      <c r="V1070" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W1070" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X1070" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1070" t="inlineStr">
+        <is>
+          <t>trending up +4.6% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-09-23T09:58</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E1071" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1071" t="n">
+        <v>2734.3</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="I1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1071" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L1071" t="n">
+        <v>2740</v>
+      </c>
+      <c r="M1071" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N1071" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O1071" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="P1071" t="n">
+        <v>-0.0958</v>
+      </c>
+      <c r="Q1071" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="R1071" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S1071" t="n">
+        <v>-41.12</v>
+      </c>
+      <c r="T1071" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="U1071" t="inlineStr">
+        <is>
+          <t>2734.3</t>
+        </is>
+      </c>
+      <c r="V1071" t="n">
+        <v>-77.64</v>
+      </c>
+      <c r="W1071" t="n">
+        <v>-7.764</v>
+      </c>
+      <c r="X1071" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1071" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.9 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:49</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1072" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1072" t="n">
+        <v>84296.3</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="I1072" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1072" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L1072" t="n">
+        <v>84800</v>
+      </c>
+      <c r="M1072" t="n">
+        <v>83600</v>
+      </c>
+      <c r="N1072" t="n">
+        <v>90400</v>
+      </c>
+      <c r="O1072" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P1072" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="Q1072" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="S1072" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="T1072" t="n">
+        <v>103.47</v>
+      </c>
+      <c r="U1072" t="inlineStr"/>
+      <c r="V1072" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W1072" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="X1072" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1072" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:49</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1073" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1073" t="n">
+        <v>84296.3</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="I1073" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1073" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L1073" t="n">
+        <v>84800</v>
+      </c>
+      <c r="M1073" t="n">
+        <v>83600</v>
+      </c>
+      <c r="N1073" t="n">
+        <v>90400</v>
+      </c>
+      <c r="O1073" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1073" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="Q1073" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="S1073" t="n">
+        <v>-100.47</v>
+      </c>
+      <c r="T1073" t="n">
+        <v>100.47</v>
+      </c>
+      <c r="U1073" t="inlineStr"/>
+      <c r="X1073" t="inlineStr"/>
+      <c r="Y1073" t="inlineStr">
+        <is>
+          <t>trending up +4.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:49</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1074" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1074" t="n">
+        <v>2665.92</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I1074" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1074" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L1074" t="n">
+        <v>2670</v>
+      </c>
+      <c r="M1074" t="n">
+        <v>2660</v>
+      </c>
+      <c r="N1074" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1074" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="P1074" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="Q1074" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="S1074" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T1074" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="U1074" t="inlineStr"/>
+      <c r="V1074" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W1074" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="X1074" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1074" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-09-23T18:13</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>XAUTUSD</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>gold_ema</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>perpetual</t>
+        </is>
+      </c>
+      <c r="E1075" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1075" t="n">
+        <v>4300.41</v>
+      </c>
+      <c r="S1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1075" t="n">
+        <v>10</v>
+      </c>
+      <c r="U1075" t="inlineStr"/>
+      <c r="X1075" t="inlineStr"/>
+      <c r="Y1075" t="inlineStr">
+        <is>
+          <t>20/50 EMA 3rd retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-09-23T18:47</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1076" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1076" t="n">
+        <v>2663.29</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I1076" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1076" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L1076" t="n">
+        <v>2670</v>
+      </c>
+      <c r="M1076" t="n">
+        <v>2640</v>
+      </c>
+      <c r="N1076" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1076" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P1076" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="Q1076" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S1076" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="T1076" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="U1076" t="inlineStr"/>
+      <c r="V1076" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="W1076" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="X1076" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Y1076" t="inlineStr">
+        <is>
+          <t>IV rank 75% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:59</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1077" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1077" t="n">
+        <v>84422.7</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I1077" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1077" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L1077" t="n">
+        <v>84400</v>
+      </c>
+      <c r="M1077" t="n">
+        <v>84000</v>
+      </c>
+      <c r="N1077" t="n">
+        <v>90400</v>
+      </c>
+      <c r="O1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1077" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="Q1077" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="S1077" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="T1077" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="U1077" t="inlineStr"/>
+      <c r="X1077" t="inlineStr"/>
+      <c r="Y1077" t="inlineStr">
+        <is>
+          <t>IV rank 50% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:59</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1078" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1078" t="n">
+        <v>2677.01</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="I1078" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1078" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L1078" t="n">
+        <v>2670</v>
+      </c>
+      <c r="M1078" t="n">
+        <v>2610</v>
+      </c>
+      <c r="N1078" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1078" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1078" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="Q1078" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="S1078" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="T1078" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="U1078" t="inlineStr"/>
+      <c r="X1078" t="inlineStr"/>
+      <c r="Y1078" t="inlineStr">
+        <is>
+          <t>IV rank 37% — default sell</t>
         </is>
       </c>
     </row>
@@ -97062,22 +98700,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="C2" t="n">
-        <v>96.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="E2" t="n">
-        <v>2833.3</v>
+        <v>2892.05</v>
       </c>
       <c r="F2" t="n">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
       <c r="G2" t="n">
-        <v>283.33</v>
+        <v>289.2</v>
       </c>
     </row>
     <row r="3">
@@ -97137,22 +98775,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>-352.36</v>
+        <v>-340.21</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.36</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-35.24</v>
+        <v>-34.02</v>
       </c>
     </row>
     <row r="6">
@@ -97162,22 +98800,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C6" t="n">
-        <v>66.7</v>
+        <v>65.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="E6" t="n">
-        <v>-419.58</v>
+        <v>-453.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.94</v>
+        <v>-2.04</v>
       </c>
       <c r="G6" t="n">
-        <v>-41.96</v>
+        <v>-45.36</v>
       </c>
     </row>
     <row r="7">
@@ -97187,22 +98825,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>23.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="E7" t="n">
-        <v>-987.98</v>
+        <v>-915.0700000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-49.4</v>
+        <v>-43.57</v>
       </c>
       <c r="G7" t="n">
-        <v>-98.8</v>
+        <v>-91.51000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -97212,22 +98850,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="D8" t="n">
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>-3807.33</v>
+        <v>-3902.32</v>
       </c>
       <c r="F8" t="n">
-        <v>-67.98999999999999</v>
+        <v>-67.28</v>
       </c>
       <c r="G8" t="n">
-        <v>-380.73</v>
+        <v>-390.23</v>
       </c>
     </row>
     <row r="9">
@@ -97262,7 +98900,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -97271,13 +98909,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-10084.32</v>
+        <v>-10188.41</v>
       </c>
       <c r="F10" t="n">
         <v>-103.96</v>
       </c>
       <c r="G10" t="n">
-        <v>-1008.43</v>
+        <v>-1018.84</v>
       </c>
     </row>
   </sheetData>
@@ -97291,7 +98929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -97451,7 +99089,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18T21:42</t>
+          <t>2026-09-21T22:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -97461,7 +99099,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -97470,7 +99108,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -97478,13 +99116,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2635.34</v>
+        <v>2776.26</v>
       </c>
       <c r="H2" t="n">
-        <v>44.05</v>
+        <v>52.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.675</v>
+        <v>0.741</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -97492,10 +99130,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.63</v>
+        <v>3.74</v>
       </c>
       <c r="L2" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="M2" t="n">
         <v>1600</v>
@@ -97504,32 +99142,32 @@
         <v>3100</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0003</v>
+        <v>-0.0016</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.004</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>25.8</v>
+        <v>-100.81</v>
       </c>
       <c r="T2" t="n">
-        <v>99.2</v>
+        <v>100.81</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>trending up +16.2% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21T22:43</t>
+          <t>2026-09-22T01:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -97539,16 +99177,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -97556,13 +99194,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>86437.10000000001</v>
+        <v>85818.60000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>37.4</v>
+        <v>38.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.629</v>
+        <v>0.678</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -97570,49 +99208,49 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.88</v>
+        <v>1.28</v>
       </c>
       <c r="L3" t="n">
-        <v>82000</v>
+        <v>78500</v>
       </c>
       <c r="M3" t="n">
-        <v>51000</v>
+        <v>78500</v>
       </c>
       <c r="N3" t="n">
-        <v>93000</v>
+        <v>87000</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0001</v>
+        <v>0.0216</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002</v>
+        <v>-0.013</v>
       </c>
       <c r="S3" t="n">
-        <v>-98.22</v>
+        <v>22.65</v>
       </c>
       <c r="T3" t="n">
-        <v>98.22</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending up +14.2% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21T22:43</t>
+          <t>2026-09-22T01:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -97622,11 +99260,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -97634,13 +99272,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2776.26</v>
+        <v>85818.60000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>52.2</v>
+        <v>38.35</v>
       </c>
       <c r="I4" t="n">
-        <v>0.741</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -97648,37 +99286,37 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.74</v>
+        <v>1.28</v>
       </c>
       <c r="L4" t="n">
-        <v>2600</v>
+        <v>78500</v>
       </c>
       <c r="M4" t="n">
-        <v>1600</v>
+        <v>78500</v>
       </c>
       <c r="N4" t="n">
-        <v>3100</v>
+        <v>87000</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0016</v>
+        <v>-0.0001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0027</v>
+        <v>-0.0012</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="S4" t="n">
-        <v>-100.81</v>
+        <v>-102.28</v>
       </c>
       <c r="T4" t="n">
-        <v>100.81</v>
+        <v>102.28</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending up +16.2% — skewed fly</t>
+          <t>trending up +12.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -97690,7 +99328,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -97704,7 +99342,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -97712,51 +99350,51 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>85818.60000000001</v>
+        <v>2751.41</v>
       </c>
       <c r="H5" t="n">
-        <v>38.35</v>
+        <v>51.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.678</v>
+        <v>0.638</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="L5" t="n">
-        <v>78500</v>
+        <v>2600</v>
       </c>
       <c r="M5" t="n">
-        <v>78500</v>
+        <v>2500</v>
       </c>
       <c r="N5" t="n">
-        <v>87000</v>
+        <v>3100</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0216</v>
+        <v>0.012</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.013</v>
+        <v>-0.0055</v>
       </c>
       <c r="S5" t="n">
-        <v>22.65</v>
+        <v>20.53</v>
       </c>
       <c r="T5" t="n">
-        <v>97.34999999999999</v>
+        <v>99.47</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -97768,7 +99406,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -97782,7 +99420,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>190</v>
+        <v>420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -97790,77 +99428,77 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>85818.60000000001</v>
+        <v>2751.41</v>
       </c>
       <c r="H6" t="n">
-        <v>38.35</v>
+        <v>51.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.607</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="L6" t="n">
-        <v>78500</v>
+        <v>2600</v>
       </c>
       <c r="M6" t="n">
-        <v>78500</v>
+        <v>2500</v>
       </c>
       <c r="N6" t="n">
-        <v>87000</v>
+        <v>3100</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0001</v>
+        <v>-0.0009</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0012</v>
+        <v>-0.0032</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0012</v>
       </c>
       <c r="S6" t="n">
-        <v>-102.28</v>
+        <v>-99.41</v>
       </c>
       <c r="T6" t="n">
-        <v>102.28</v>
+        <v>99.41</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +12.3% — skewed fly</t>
+          <t>trending up +12.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22T01:12</t>
+          <t>2026-09-23T14:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -97868,77 +99506,77 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2751.41</v>
+        <v>84296.3</v>
       </c>
       <c r="H7" t="n">
-        <v>51.6</v>
+        <v>34.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.638</v>
+        <v>0.973</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.05</v>
+        <v>0.51</v>
       </c>
       <c r="L7" t="n">
-        <v>2600</v>
+        <v>84800</v>
       </c>
       <c r="M7" t="n">
-        <v>2500</v>
+        <v>83600</v>
       </c>
       <c r="N7" t="n">
-        <v>3100</v>
+        <v>90400</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005</v>
       </c>
       <c r="P7" t="n">
-        <v>0.012</v>
+        <v>0.1545</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0055</v>
+        <v>-0.0077</v>
       </c>
       <c r="S7" t="n">
-        <v>20.53</v>
+        <v>-100.47</v>
       </c>
       <c r="T7" t="n">
-        <v>99.47</v>
+        <v>100.47</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>trending up +4.1% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22T01:12</t>
+          <t>2026-09-23T18:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -97946,58 +99584,26 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2751.41</v>
-      </c>
-      <c r="H8" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2600</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3100</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.0009</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.0032</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.0012</v>
+        <v>4300.41</v>
       </c>
       <c r="S8" t="n">
-        <v>-99.41</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>99.41</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>trending up +12.4% — skewed fly</t>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22T15:44</t>
+          <t>2026-09-23T21:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -98012,11 +99618,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -98024,77 +99630,77 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>86500.10000000001</v>
+        <v>84422.7</v>
       </c>
       <c r="H9" t="n">
-        <v>32.6</v>
+        <v>17.95</v>
       </c>
       <c r="I9" t="n">
-        <v>0.696</v>
+        <v>0.703</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4.55</v>
+        <v>0.29</v>
       </c>
       <c r="L9" t="n">
-        <v>86000</v>
+        <v>84400</v>
       </c>
       <c r="M9" t="n">
-        <v>82400</v>
+        <v>84000</v>
       </c>
       <c r="N9" t="n">
-        <v>89600</v>
+        <v>90400</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2024</v>
+        <v>0.3009</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0112</v>
+        <v>-0.0128</v>
       </c>
       <c r="S9" t="n">
-        <v>9.81</v>
+        <v>9.44</v>
       </c>
       <c r="T9" t="n">
-        <v>98.19</v>
+        <v>102.56</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>IV rank 50% — default sell</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22T15:44</t>
+          <t>2026-09-23T21:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -98102,207 +99708,51 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>86500.10000000001</v>
+        <v>2677.01</v>
       </c>
       <c r="H10" t="n">
-        <v>32.6</v>
+        <v>24.75</v>
       </c>
       <c r="I10" t="n">
-        <v>0.867</v>
+        <v>0.67</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bullish</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4.55</v>
+        <v>0.47</v>
       </c>
       <c r="L10" t="n">
-        <v>86000</v>
+        <v>2670</v>
       </c>
       <c r="M10" t="n">
-        <v>82400</v>
+        <v>2610</v>
       </c>
       <c r="N10" t="n">
-        <v>89600</v>
+        <v>2960</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0004</v>
+        <v>-0.0005</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0956</v>
+        <v>0.1127</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0041</v>
       </c>
       <c r="S10" t="n">
-        <v>-94.84999999999999</v>
+        <v>12.19</v>
       </c>
       <c r="T10" t="n">
-        <v>94.84999999999999</v>
+        <v>97.81</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>trending up +13.2% — skewed fly</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-22T15:44</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>broken_wing_butterfly</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>300</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>2748.44</v>
-      </c>
-      <c r="H11" t="n">
-        <v>46</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2740</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2600</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2920</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.0027</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-101.28</v>
-      </c>
-      <c r="T11" t="n">
-        <v>101.28</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>trending up +12.2% — skewed fly</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-22T22:13</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>190</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>2738.91</v>
-      </c>
-      <c r="H12" t="n">
-        <v>29.05</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2740</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2700</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2920</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="S12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>IV rank 61% — default sell</t>
+          <t>IV rank 37% — default sell</t>
         </is>
       </c>
     </row>
@@ -98323,7 +99773,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-22T22:29:45.292684 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-23T22:32:34.331893 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1078"/>
+  <dimension ref="A1:Y1087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -95331,7 +95331,7 @@
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1041" t="n">
@@ -95376,7 +95376,17 @@
         <v>100.81</v>
       </c>
       <c r="U1041" t="inlineStr"/>
-      <c r="X1041" t="inlineStr"/>
+      <c r="V1041" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="W1041" t="n">
+        <v>8.122</v>
+      </c>
+      <c r="X1041" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Y1041" t="inlineStr">
         <is>
           <t>trending up +16.2% — skewed fly</t>
@@ -98203,7 +98213,7 @@
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1073" t="n">
@@ -98247,8 +98257,22 @@
       <c r="T1073" t="n">
         <v>100.47</v>
       </c>
-      <c r="U1073" t="inlineStr"/>
-      <c r="X1073" t="inlineStr"/>
+      <c r="U1073" t="inlineStr">
+        <is>
+          <t>84414.8</t>
+        </is>
+      </c>
+      <c r="V1073" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="W1073" t="n">
+        <v>-0.178</v>
+      </c>
+      <c r="X1073" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Y1073" t="inlineStr">
         <is>
           <t>trending up +4.1% — skewed fly</t>
@@ -98503,7 +98527,7 @@
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1077" t="n">
@@ -98547,8 +98571,22 @@
       <c r="T1077" t="n">
         <v>102.56</v>
       </c>
-      <c r="U1077" t="inlineStr"/>
-      <c r="X1077" t="inlineStr"/>
+      <c r="U1077" t="inlineStr">
+        <is>
+          <t>84414.8</t>
+        </is>
+      </c>
+      <c r="V1077" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="W1077" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="X1077" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Y1077" t="inlineStr">
         <is>
           <t>IV rank 50% — default sell</t>
@@ -98581,7 +98619,7 @@
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1078" t="n">
@@ -98625,11 +98663,831 @@
       <c r="T1078" t="n">
         <v>97.81</v>
       </c>
-      <c r="U1078" t="inlineStr"/>
-      <c r="X1078" t="inlineStr"/>
+      <c r="U1078" t="inlineStr">
+        <is>
+          <t>2688.98</t>
+        </is>
+      </c>
+      <c r="V1078" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="W1078" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="X1078" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Y1078" t="inlineStr">
         <is>
           <t>IV rank 37% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-09-24T05:08</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1079" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1079" t="n">
+        <v>84334.3</v>
+      </c>
+      <c r="H1079" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I1079" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1079" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L1079" t="n">
+        <v>84200</v>
+      </c>
+      <c r="M1079" t="n">
+        <v>83000</v>
+      </c>
+      <c r="N1079" t="n">
+        <v>90400</v>
+      </c>
+      <c r="O1079" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1079" t="n">
+        <v>0.5276</v>
+      </c>
+      <c r="Q1079" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="S1079" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="T1079" t="n">
+        <v>103.66</v>
+      </c>
+      <c r="U1079" t="inlineStr">
+        <is>
+          <t>84334.3</t>
+        </is>
+      </c>
+      <c r="V1079" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="W1079" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="X1079" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Y1079" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-09-24T05:08</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1080" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1080" t="n">
+        <v>2698.26</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="I1080" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1080" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L1080" t="n">
+        <v>2680</v>
+      </c>
+      <c r="M1080" t="n">
+        <v>2610</v>
+      </c>
+      <c r="N1080" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1080" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P1080" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="Q1080" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S1080" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="T1080" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="U1080" t="inlineStr">
+        <is>
+          <t>2698.26</t>
+        </is>
+      </c>
+      <c r="V1080" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="W1080" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="X1080" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Y1080" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:59</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1081" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1081" t="n">
+        <v>83265</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="I1081" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1081" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L1081" t="n">
+        <v>83400</v>
+      </c>
+      <c r="M1081" t="n">
+        <v>83000</v>
+      </c>
+      <c r="N1081" t="n">
+        <v>90400</v>
+      </c>
+      <c r="O1081" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P1081" t="n">
+        <v>0.8592</v>
+      </c>
+      <c r="Q1081" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="S1081" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T1081" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="U1081" t="inlineStr">
+        <is>
+          <t>83265.0</t>
+        </is>
+      </c>
+      <c r="V1081" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W1081" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="X1081" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Y1081" t="inlineStr">
+        <is>
+          <t>IV rank 40% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:59</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1082" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1082" t="n">
+        <v>83265</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="I1082" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1082" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L1082" t="n">
+        <v>83400</v>
+      </c>
+      <c r="M1082" t="n">
+        <v>83000</v>
+      </c>
+      <c r="N1082" t="n">
+        <v>90400</v>
+      </c>
+      <c r="O1082" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1082" t="n">
+        <v>-1.0335</v>
+      </c>
+      <c r="Q1082" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="S1082" t="n">
+        <v>-99.95999999999999</v>
+      </c>
+      <c r="T1082" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="U1082" t="inlineStr">
+        <is>
+          <t>83265.0</t>
+        </is>
+      </c>
+      <c r="V1082" t="n">
+        <v>-104.04</v>
+      </c>
+      <c r="W1082" t="n">
+        <v>-10.404</v>
+      </c>
+      <c r="X1082" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Y1082" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:59</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1083" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1083" t="n">
+        <v>83265</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="I1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>Slightly Bullish</t>
+        </is>
+      </c>
+      <c r="K1083" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L1083" t="n">
+        <v>83400</v>
+      </c>
+      <c r="M1083" t="n">
+        <v>83000</v>
+      </c>
+      <c r="N1083" t="n">
+        <v>90400</v>
+      </c>
+      <c r="O1083" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P1083" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="Q1083" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="R1083" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S1083" t="n">
+        <v>-26.82</v>
+      </c>
+      <c r="T1083" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="U1083" t="inlineStr">
+        <is>
+          <t>83265.0</t>
+        </is>
+      </c>
+      <c r="V1083" t="n">
+        <v>-15.98</v>
+      </c>
+      <c r="W1083" t="n">
+        <v>-1.598</v>
+      </c>
+      <c r="X1083" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Y1083" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 1.2 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:59</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1084" t="n">
+        <v>170</v>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1084" t="n">
+        <v>2642.34</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="I1084" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1084" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L1084" t="n">
+        <v>2650</v>
+      </c>
+      <c r="M1084" t="n">
+        <v>2610</v>
+      </c>
+      <c r="N1084" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1084" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="Q1084" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="S1084" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T1084" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="U1084" t="inlineStr">
+        <is>
+          <t>2642.34</t>
+        </is>
+      </c>
+      <c r="V1084" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="W1084" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="X1084" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Y1084" t="inlineStr">
+        <is>
+          <t>IV rank 34% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:59</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1085" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1085" t="n">
+        <v>2642.34</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="I1085" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1085" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L1085" t="n">
+        <v>2650</v>
+      </c>
+      <c r="M1085" t="n">
+        <v>2610</v>
+      </c>
+      <c r="N1085" t="n">
+        <v>2960</v>
+      </c>
+      <c r="O1085" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="P1085" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="Q1085" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="R1085" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="S1085" t="n">
+        <v>-100.17</v>
+      </c>
+      <c r="T1085" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="U1085" t="inlineStr">
+        <is>
+          <t>2642.34</t>
+        </is>
+      </c>
+      <c r="V1085" t="n">
+        <v>105.46</v>
+      </c>
+      <c r="W1085" t="n">
+        <v>10.546</v>
+      </c>
+      <c r="X1085" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Y1085" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 8.4 · 2.0h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-09-24T14:51</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1086" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1086" t="n">
+        <v>83857.60000000001</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="I1086" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1086" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L1086" t="n">
+        <v>84000</v>
+      </c>
+      <c r="M1086" t="n">
+        <v>76000</v>
+      </c>
+      <c r="N1086" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1086" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1086" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="Q1086" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="S1086" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="T1086" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="U1086" t="inlineStr"/>
+      <c r="X1086" t="inlineStr"/>
+      <c r="Y1086" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-09-24T14:51</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1087" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1087" t="n">
+        <v>2662.16</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="I1087" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1087" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L1087" t="n">
+        <v>2660</v>
+      </c>
+      <c r="M1087" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1087" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1087" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1087" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="Q1087" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="S1087" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="T1087" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="U1087" t="inlineStr"/>
+      <c r="X1087" t="inlineStr"/>
+      <c r="Y1087" t="inlineStr">
+        <is>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -98700,22 +99558,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="C2" t="n">
         <v>96.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="E2" t="n">
-        <v>2892.05</v>
+        <v>2936.1</v>
       </c>
       <c r="F2" t="n">
-        <v>5.37</v>
+        <v>5.39</v>
       </c>
       <c r="G2" t="n">
-        <v>289.2</v>
+        <v>293.61</v>
       </c>
     </row>
     <row r="3">
@@ -98800,22 +99658,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C6" t="n">
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="D6" t="n">
         <v>0.73</v>
       </c>
       <c r="E6" t="n">
-        <v>-453.6</v>
+        <v>-455.38</v>
       </c>
       <c r="F6" t="n">
         <v>-2.04</v>
       </c>
       <c r="G6" t="n">
-        <v>-45.36</v>
+        <v>-45.54</v>
       </c>
     </row>
     <row r="7">
@@ -98825,22 +99683,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>23.8</v>
+        <v>27.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="E7" t="n">
-        <v>-915.0700000000001</v>
+        <v>-833.85</v>
       </c>
       <c r="F7" t="n">
-        <v>-43.57</v>
+        <v>-37.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-91.51000000000001</v>
+        <v>-83.38</v>
       </c>
     </row>
     <row r="8">
@@ -98850,22 +99708,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>-3902.32</v>
+        <v>-3812.84</v>
       </c>
       <c r="F8" t="n">
-        <v>-67.28</v>
+        <v>-63.55</v>
       </c>
       <c r="G8" t="n">
-        <v>-390.23</v>
+        <v>-381.28</v>
       </c>
     </row>
     <row r="9">
@@ -98900,7 +99758,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -98909,13 +99767,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-10188.41</v>
+        <v>-10292.45</v>
       </c>
       <c r="F10" t="n">
         <v>-103.96</v>
       </c>
       <c r="G10" t="n">
-        <v>-1018.84</v>
+        <v>-1029.25</v>
       </c>
     </row>
   </sheetData>
@@ -98929,7 +99787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -99089,26 +99947,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21T22:43</t>
+          <t>2026-09-22T01:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>310</v>
+        <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -99116,13 +99974,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2776.26</v>
+        <v>85818.60000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>52.2</v>
+        <v>38.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.741</v>
+        <v>0.678</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -99130,37 +99988,37 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.74</v>
+        <v>1.28</v>
       </c>
       <c r="L2" t="n">
-        <v>2600</v>
+        <v>78500</v>
       </c>
       <c r="M2" t="n">
-        <v>1600</v>
+        <v>78500</v>
       </c>
       <c r="N2" t="n">
-        <v>3100</v>
+        <v>87000</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0016</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0027</v>
+        <v>0.0216</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.013</v>
       </c>
       <c r="S2" t="n">
-        <v>-100.81</v>
+        <v>22.65</v>
       </c>
       <c r="T2" t="n">
-        <v>100.81</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>trending up +16.2% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -99177,7 +100035,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -99186,7 +100044,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -99200,7 +100058,7 @@
         <v>38.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.678</v>
+        <v>0.607</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -99220,25 +100078,25 @@
         <v>87000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0216</v>
+        <v>-0.0012</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.013</v>
+        <v>0.0012</v>
       </c>
       <c r="S3" t="n">
-        <v>22.65</v>
+        <v>-102.28</v>
       </c>
       <c r="T3" t="n">
-        <v>97.34999999999999</v>
+        <v>102.28</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending up +12.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -99250,12 +100108,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -99264,7 +100122,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -99272,51 +100130,51 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>85818.60000000001</v>
+        <v>2751.41</v>
       </c>
       <c r="H4" t="n">
-        <v>38.35</v>
+        <v>51.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.607</v>
+        <v>0.638</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="L4" t="n">
-        <v>78500</v>
+        <v>2600</v>
       </c>
       <c r="M4" t="n">
-        <v>78500</v>
+        <v>2500</v>
       </c>
       <c r="N4" t="n">
-        <v>87000</v>
+        <v>3100</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0012</v>
+        <v>0.012</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0012</v>
+        <v>-0.0055</v>
       </c>
       <c r="S4" t="n">
-        <v>-102.28</v>
+        <v>20.53</v>
       </c>
       <c r="T4" t="n">
-        <v>102.28</v>
+        <v>99.47</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>trending up +12.3% — skewed fly</t>
+          <t>IV rank 96% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -99333,7 +100191,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -99342,7 +100200,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -99356,7 +100214,7 @@
         <v>51.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.638</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -99376,51 +100234,51 @@
         <v>3100</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0009</v>
       </c>
       <c r="P5" t="n">
-        <v>0.012</v>
+        <v>-0.0032</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0055</v>
+        <v>0.0012</v>
       </c>
       <c r="S5" t="n">
-        <v>20.53</v>
+        <v>-99.41</v>
       </c>
       <c r="T5" t="n">
-        <v>99.47</v>
+        <v>99.41</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>trending up +12.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22T01:12</t>
+          <t>2026-09-23T18:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -99428,58 +100286,26 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2751.41</v>
-      </c>
-      <c r="H6" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3100</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.0009</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.0032</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.0012</v>
+        <v>4300.41</v>
       </c>
       <c r="S6" t="n">
-        <v>-99.41</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>99.41</v>
+        <v>10</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trending up +12.4% — skewed fly</t>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23T14:49</t>
+          <t>2026-09-24T14:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -99489,16 +100315,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -99506,77 +100332,77 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>84296.3</v>
+        <v>83857.60000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>34.05</v>
+        <v>34.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.973</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Slightly Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.51</v>
+        <v>2.77</v>
       </c>
       <c r="L7" t="n">
-        <v>84800</v>
+        <v>84000</v>
       </c>
       <c r="M7" t="n">
-        <v>83600</v>
+        <v>76000</v>
       </c>
       <c r="N7" t="n">
-        <v>90400</v>
+        <v>93000</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0005</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1545</v>
+        <v>0.248</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0077</v>
+        <v>-0.0119</v>
       </c>
       <c r="S7" t="n">
-        <v>-100.47</v>
+        <v>14.52</v>
       </c>
       <c r="T7" t="n">
-        <v>100.47</v>
+        <v>97.48</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>trending up +4.1% — skewed fly</t>
+          <t>IV rank 98% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23T18:13</t>
+          <t>2026-09-24T14:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XAUTUSD</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gold_ema</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>perpetual</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -99584,175 +100410,51 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4300.41</v>
+        <v>2662.16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2660</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>16.65</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>20/50 EMA 3rd retest</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-23T21:59</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>70</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>84422.7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L9" t="n">
-        <v>84400</v>
-      </c>
-      <c r="M9" t="n">
-        <v>84000</v>
-      </c>
-      <c r="N9" t="n">
-        <v>90400</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.3009</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.0128</v>
-      </c>
-      <c r="S9" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="T9" t="n">
-        <v>102.56</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>IV rank 50% — default sell</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-23T21:59</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2677.01</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Slightly Bullish</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2670</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2610</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2960</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1127</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.0041</v>
-      </c>
-      <c r="S10" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="T10" t="n">
-        <v>97.81</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>IV rank 37% — default sell</t>
+          <t>IV rank 94% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -99773,7 +100475,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-23T22:32:34.331893 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-24T22:48:38.476063 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>

--- a/OUTPUT FILE.xlsx
+++ b/OUTPUT FILE.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1087"/>
+  <dimension ref="A1:Y1102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -95511,7 +95511,7 @@
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1043" t="n">
@@ -95556,7 +95556,17 @@
         <v>97.34999999999999</v>
       </c>
       <c r="U1043" t="inlineStr"/>
-      <c r="X1043" t="inlineStr"/>
+      <c r="V1043" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W1043" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="X1043" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="Y1043" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -95667,7 +95677,7 @@
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1045" t="n">
@@ -95712,7 +95722,17 @@
         <v>99.47</v>
       </c>
       <c r="U1045" t="inlineStr"/>
-      <c r="X1045" t="inlineStr"/>
+      <c r="V1045" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="W1045" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="X1045" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="Y1045" t="inlineStr">
         <is>
           <t>IV rank 96% rich — sell premium</t>
@@ -99361,7 +99381,7 @@
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1086" t="n">
@@ -99405,8 +99425,22 @@
       <c r="T1086" t="n">
         <v>97.48</v>
       </c>
-      <c r="U1086" t="inlineStr"/>
-      <c r="X1086" t="inlineStr"/>
+      <c r="U1086" t="inlineStr">
+        <is>
+          <t>84661.6</t>
+        </is>
+      </c>
+      <c r="V1086" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="W1086" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="X1086" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="Y1086" t="inlineStr">
         <is>
           <t>IV rank 98% rich — sell premium</t>
@@ -99439,7 +99473,7 @@
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="G1087" t="n">
@@ -99484,10 +99518,1356 @@
         <v>98.34999999999999</v>
       </c>
       <c r="U1087" t="inlineStr"/>
-      <c r="X1087" t="inlineStr"/>
+      <c r="V1087" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="W1087" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="X1087" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Y1087" t="inlineStr">
         <is>
           <t>IV rank 94% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-09-25T00:15</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1088" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1088" t="n">
+        <v>84661.60000000001</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="I1088" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1088" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L1088" t="n">
+        <v>84000</v>
+      </c>
+      <c r="M1088" t="n">
+        <v>82000</v>
+      </c>
+      <c r="N1088" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1088" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="P1088" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="Q1088" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="S1088" t="n">
+        <v>-95.19</v>
+      </c>
+      <c r="T1088" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="U1088" t="inlineStr">
+        <is>
+          <t>84661.6</t>
+        </is>
+      </c>
+      <c r="V1088" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="W1088" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="X1088" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1088" t="inlineStr">
+        <is>
+          <t>trending up +4.3% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-09-25T00:15</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1089" t="n">
+        <v>2694.85</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>51</v>
+      </c>
+      <c r="I1089" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1089" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L1089" t="n">
+        <v>2670</v>
+      </c>
+      <c r="M1089" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N1089" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1089" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="Q1089" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="S1089" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T1089" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="U1089" t="inlineStr">
+        <is>
+          <t>2694.85</t>
+        </is>
+      </c>
+      <c r="V1089" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="W1089" t="n">
+        <v>1.368</v>
+      </c>
+      <c r="X1089" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1089" t="inlineStr">
+        <is>
+          <t>IV rank 96% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-25T05:01</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1090" t="n">
+        <v>84253.8</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="I1090" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1090" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L1090" t="n">
+        <v>84200</v>
+      </c>
+      <c r="M1090" t="n">
+        <v>82000</v>
+      </c>
+      <c r="N1090" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1090" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1090" t="n">
+        <v>0.5839</v>
+      </c>
+      <c r="Q1090" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="S1090" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="T1090" t="n">
+        <v>102.23</v>
+      </c>
+      <c r="U1090" t="inlineStr">
+        <is>
+          <t>84253.8</t>
+        </is>
+      </c>
+      <c r="V1090" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W1090" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X1090" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1090" t="inlineStr">
+        <is>
+          <t>IV rank 98% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-09-25T05:01</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>210</v>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1091" t="n">
+        <v>2682.98</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="I1091" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1091" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L1091" t="n">
+        <v>2680</v>
+      </c>
+      <c r="M1091" t="n">
+        <v>2450</v>
+      </c>
+      <c r="N1091" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1091" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="P1091" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="Q1091" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="S1091" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T1091" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U1091" t="inlineStr">
+        <is>
+          <t>2682.98</t>
+        </is>
+      </c>
+      <c r="V1091" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="W1091" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="X1091" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1091" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-09-25T10:10</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1092" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1092" t="n">
+        <v>84463.3</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1092" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1092" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L1092" t="n">
+        <v>84400</v>
+      </c>
+      <c r="M1092" t="n">
+        <v>84000</v>
+      </c>
+      <c r="N1092" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1092" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1092" t="n">
+        <v>1.1067</v>
+      </c>
+      <c r="Q1092" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="S1092" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T1092" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="U1092" t="inlineStr">
+        <is>
+          <t>84463.3</t>
+        </is>
+      </c>
+      <c r="V1092" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="W1092" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="X1092" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1092" t="inlineStr">
+        <is>
+          <t>IV rank 33% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-25T10:10</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>broken_wing_butterfly</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1093" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1093" t="n">
+        <v>84463.3</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1093" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1093" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L1093" t="n">
+        <v>84400</v>
+      </c>
+      <c r="M1093" t="n">
+        <v>84000</v>
+      </c>
+      <c r="N1093" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1093" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P1093" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="Q1093" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="S1093" t="n">
+        <v>-90.39</v>
+      </c>
+      <c r="T1093" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="U1093" t="inlineStr">
+        <is>
+          <t>84463.3</t>
+        </is>
+      </c>
+      <c r="V1093" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="W1093" t="n">
+        <v>-0.478</v>
+      </c>
+      <c r="X1093" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1093" t="inlineStr">
+        <is>
+          <t>trending up +4.1% — skewed fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-25T10:10</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>cheap_strangle</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1094" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1094" t="n">
+        <v>84463.3</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1094" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1094" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L1094" t="n">
+        <v>84400</v>
+      </c>
+      <c r="M1094" t="n">
+        <v>84000</v>
+      </c>
+      <c r="N1094" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1094" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1094" t="n">
+        <v>-0.8923</v>
+      </c>
+      <c r="Q1094" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="S1094" t="n">
+        <v>-100.02</v>
+      </c>
+      <c r="T1094" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="U1094" t="inlineStr">
+        <is>
+          <t>84463.3</t>
+        </is>
+      </c>
+      <c r="V1094" t="n">
+        <v>-104.11</v>
+      </c>
+      <c r="W1094" t="n">
+        <v>-10.411</v>
+      </c>
+      <c r="X1094" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1094" t="inlineStr">
+        <is>
+          <t>cheap strangle: ±400 premiums ≤ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-25T10:10</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1095" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1095" t="n">
+        <v>84463.3</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1095" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1095" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L1095" t="n">
+        <v>84400</v>
+      </c>
+      <c r="M1095" t="n">
+        <v>84000</v>
+      </c>
+      <c r="N1095" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1095" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="P1095" t="n">
+        <v>-0.3627</v>
+      </c>
+      <c r="Q1095" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="R1095" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="S1095" t="n">
+        <v>-100.36</v>
+      </c>
+      <c r="T1095" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="U1095" t="inlineStr">
+        <is>
+          <t>84463.3</t>
+        </is>
+      </c>
+      <c r="V1095" t="n">
+        <v>-106.08</v>
+      </c>
+      <c r="W1095" t="n">
+        <v>-10.608</v>
+      </c>
+      <c r="X1095" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1095" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 4.2 · 1.8h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-09-25T10:10</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>long_strangle</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1096" t="n">
+        <v>1570</v>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1096" t="n">
+        <v>2699.66</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="I1096" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1096" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L1096" t="n">
+        <v>2690</v>
+      </c>
+      <c r="M1096" t="n">
+        <v>2640</v>
+      </c>
+      <c r="N1096" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1096" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1096" t="n">
+        <v>-0.6326000000000001</v>
+      </c>
+      <c r="Q1096" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S1096" t="n">
+        <v>-100.32</v>
+      </c>
+      <c r="T1096" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="U1096" t="inlineStr">
+        <is>
+          <t>2699.66</t>
+        </is>
+      </c>
+      <c r="V1096" t="n">
+        <v>-104.41</v>
+      </c>
+      <c r="W1096" t="n">
+        <v>-10.441</v>
+      </c>
+      <c r="X1096" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1096" t="inlineStr">
+        <is>
+          <t>IV rank 15% cheap + event — buy vol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-09-25T10:11</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1097" t="n">
+        <v>1840</v>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1097" t="n">
+        <v>2699.66</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="I1097" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1097" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L1097" t="n">
+        <v>2690</v>
+      </c>
+      <c r="M1097" t="n">
+        <v>2640</v>
+      </c>
+      <c r="N1097" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1097" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="P1097" t="n">
+        <v>-0.1729</v>
+      </c>
+      <c r="Q1097" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="R1097" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="S1097" t="n">
+        <v>-100.28</v>
+      </c>
+      <c r="T1097" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="U1097" t="inlineStr">
+        <is>
+          <t>2699.66</t>
+        </is>
+      </c>
+      <c r="V1097" t="n">
+        <v>-400.2</v>
+      </c>
+      <c r="W1097" t="n">
+        <v>-40.02</v>
+      </c>
+      <c r="X1097" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1097" t="inlineStr">
+        <is>
+          <t>butterfly pin · R:R 8.2 · 1.8h to expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-09-25T15:15</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E1098" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1098" t="n">
+        <v>83974</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>23</v>
+      </c>
+      <c r="I1098" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1098" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L1098" t="n">
+        <v>84000</v>
+      </c>
+      <c r="M1098" t="n">
+        <v>82000</v>
+      </c>
+      <c r="N1098" t="n">
+        <v>88400</v>
+      </c>
+      <c r="O1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1098" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="Q1098" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="S1098" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="T1098" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="U1098" t="inlineStr"/>
+      <c r="V1098" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W1098" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="X1098" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1098" t="inlineStr">
+        <is>
+          <t>IV rank 69% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-09-25T15:15</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E1099" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="G1099" t="n">
+        <v>2697.03</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="I1099" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1099" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L1099" t="n">
+        <v>2700</v>
+      </c>
+      <c r="M1099" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N1099" t="n">
+        <v>2880</v>
+      </c>
+      <c r="O1099" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P1099" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="Q1099" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S1099" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="T1099" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="U1099" t="inlineStr"/>
+      <c r="V1099" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="W1099" t="n">
+        <v>1.428</v>
+      </c>
+      <c r="X1099" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Y1099" t="inlineStr">
+        <is>
+          <t>IV rank 76% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:23</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E1100" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1100" t="n">
+        <v>84033.7</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="I1100" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="K1100" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L1100" t="n">
+        <v>79500</v>
+      </c>
+      <c r="M1100" t="n">
+        <v>74500</v>
+      </c>
+      <c r="N1100" t="n">
+        <v>93000</v>
+      </c>
+      <c r="O1100" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P1100" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="Q1100" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="S1100" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="T1100" t="n">
+        <v>98.31999999999999</v>
+      </c>
+      <c r="U1100" t="inlineStr"/>
+      <c r="X1100" t="inlineStr"/>
+      <c r="Y1100" t="inlineStr">
+        <is>
+          <t>IV rank 93% rich — sell premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:23</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>iron_condor</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E1101" t="n">
+        <v>180</v>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1101" t="n">
+        <v>2693.88</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I1101" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K1101" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L1101" t="n">
+        <v>2690</v>
+      </c>
+      <c r="M1101" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N1101" t="n">
+        <v>2880</v>
+      </c>
+      <c r="O1101" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P1101" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="Q1101" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="S1101" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="T1101" t="n">
+        <v>100.66</v>
+      </c>
+      <c r="U1101" t="inlineStr"/>
+      <c r="X1101" t="inlineStr"/>
+      <c r="Y1101" t="inlineStr">
+        <is>
+          <t>IV rank 31% — default sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-09-25T19:23</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>iron_condor_wk</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G1102" t="n">
+        <v>2693.88</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="I1102" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>Slightly Bearish</t>
+        </is>
+      </c>
+      <c r="K1102" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L1102" t="n">
+        <v>2700</v>
+      </c>
+      <c r="M1102" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N1102" t="n">
+        <v>3100</v>
+      </c>
+      <c r="O1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1102" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="Q1102" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="S1102" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="T1102" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="U1102" t="inlineStr"/>
+      <c r="X1102" t="inlineStr"/>
+      <c r="Y1102" t="inlineStr">
+        <is>
+          <t>IV rank 91% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -99558,22 +100938,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="C2" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2</v>
+        <v>5.31</v>
       </c>
       <c r="E2" t="n">
-        <v>2936.1</v>
+        <v>3012</v>
       </c>
       <c r="F2" t="n">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
       <c r="G2" t="n">
-        <v>293.61</v>
+        <v>301.2</v>
       </c>
     </row>
     <row r="3">
@@ -99633,22 +101013,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>62.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>-340.21</v>
+        <v>-319.17</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.720000000000001</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-34.02</v>
+        <v>-31.92</v>
       </c>
     </row>
     <row r="6">
@@ -99658,22 +101038,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>65.5</v>
+        <v>65.3</v>
       </c>
       <c r="D6" t="n">
         <v>0.73</v>
       </c>
       <c r="E6" t="n">
-        <v>-455.38</v>
+        <v>-455.14</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.04</v>
+        <v>-2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>-45.54</v>
+        <v>-45.51</v>
       </c>
     </row>
     <row r="7">
@@ -99708,22 +101088,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>-3812.84</v>
+        <v>-4319.12</v>
       </c>
       <c r="F8" t="n">
-        <v>-63.55</v>
+        <v>-69.66</v>
       </c>
       <c r="G8" t="n">
-        <v>-381.28</v>
+        <v>-431.91</v>
       </c>
     </row>
     <row r="9">
@@ -99733,7 +101113,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>1.2</v>
@@ -99742,13 +101122,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-8364.48</v>
+        <v>-8468.889999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-100.78</v>
+        <v>-100.82</v>
       </c>
       <c r="G9" t="n">
-        <v>-836.45</v>
+        <v>-846.89</v>
       </c>
     </row>
     <row r="10">
@@ -99758,7 +101138,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -99767,13 +101147,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-10292.45</v>
+        <v>-10396.56</v>
       </c>
       <c r="F10" t="n">
-        <v>-103.96</v>
+        <v>-103.97</v>
       </c>
       <c r="G10" t="n">
-        <v>-1029.25</v>
+        <v>-1039.66</v>
       </c>
     </row>
   </sheetData>
@@ -99787,7 +101167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -99957,7 +101337,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>broken_wing_butterfly_wk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -99966,7 +101346,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -99980,7 +101360,7 @@
         <v>38.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.678</v>
+        <v>0.607</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -100000,25 +101380,25 @@
         <v>87000</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0216</v>
+        <v>-0.0012</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.013</v>
+        <v>0.0012</v>
       </c>
       <c r="S2" t="n">
-        <v>22.65</v>
+        <v>-102.28</v>
       </c>
       <c r="T2" t="n">
-        <v>97.34999999999999</v>
+        <v>102.28</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
+          <t>trending up +12.3% — skewed fly</t>
         </is>
       </c>
     </row>
@@ -100030,7 +101410,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -100044,7 +101424,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>190</v>
+        <v>420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -100052,77 +101432,77 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>85818.60000000001</v>
+        <v>2751.41</v>
       </c>
       <c r="H3" t="n">
-        <v>38.35</v>
+        <v>51.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.607</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="L3" t="n">
-        <v>78500</v>
+        <v>2600</v>
       </c>
       <c r="M3" t="n">
-        <v>78500</v>
+        <v>2500</v>
       </c>
       <c r="N3" t="n">
-        <v>87000</v>
+        <v>3100</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0001</v>
+        <v>-0.0009</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0012</v>
+        <v>-0.0032</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0012</v>
       </c>
       <c r="S3" t="n">
-        <v>-102.28</v>
+        <v>-99.41</v>
       </c>
       <c r="T3" t="n">
-        <v>102.28</v>
+        <v>99.41</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>trending up +12.3% — skewed fly</t>
+          <t>trending up +12.4% — skewed fly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22T01:12</t>
+          <t>2026-09-23T18:13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>XAUTUSD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iron_condor_wk</t>
+          <t>gold_ema</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>perpetual</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -100130,68 +101510,36 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2751.41</v>
-      </c>
-      <c r="H4" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2600</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3100</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.0055</v>
+        <v>4300.41</v>
       </c>
       <c r="S4" t="n">
-        <v>20.53</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>99.47</v>
+        <v>10</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>IV rank 96% rich — sell premium</t>
+          <t>20/50 EMA 3rd retest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22T01:12</t>
+          <t>2026-09-25T19:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>broken_wing_butterfly_wk</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -100200,7 +101548,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -100208,77 +101556,77 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2751.41</v>
+        <v>84033.7</v>
       </c>
       <c r="H5" t="n">
-        <v>51.6</v>
+        <v>28.35</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Slightly Bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="L5" t="n">
-        <v>2600</v>
+        <v>79500</v>
       </c>
       <c r="M5" t="n">
-        <v>2500</v>
+        <v>74500</v>
       </c>
       <c r="N5" t="n">
-        <v>3100</v>
+        <v>93000</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0009</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0032</v>
+        <v>0.0376</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0012</v>
+        <v>-0.0187</v>
       </c>
       <c r="S5" t="n">
-        <v>-99.41</v>
+        <v>21.68</v>
       </c>
       <c r="T5" t="n">
-        <v>99.41</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>trending up +12.4% — skewed fly</t>
+          <t>IV rank 93% rich — sell premium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23T18:13</t>
+          <t>2026-09-25T19:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUTUSD</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gold_ema</t>
+          <t>iron_condor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>perpetual</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -100286,45 +101634,77 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4300.41</v>
+        <v>2693.88</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2690</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2880</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.0043</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>100.66</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20/50 EMA 3rd retest</t>
+          <t>IV rank 31% — default sell</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24T14:51</t>
+          <t>2026-09-25T19:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iron_condor</t>
+          <t>iron_condor_wk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -100332,129 +101712,51 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>83857.60000000001</v>
+        <v>2693.88</v>
       </c>
       <c r="H7" t="n">
-        <v>34.7</v>
+        <v>37.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Slightly Bearish</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.77</v>
+        <v>1.38</v>
       </c>
       <c r="L7" t="n">
-        <v>84000</v>
+        <v>2700</v>
       </c>
       <c r="M7" t="n">
-        <v>76000</v>
+        <v>2300</v>
       </c>
       <c r="N7" t="n">
-        <v>93000</v>
+        <v>3100</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.248</v>
+        <v>0.0118</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0119</v>
+        <v>-0.0046</v>
       </c>
       <c r="S7" t="n">
-        <v>14.52</v>
+        <v>23.5</v>
       </c>
       <c r="T7" t="n">
-        <v>97.48</v>
+        <v>101.5</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>IV rank 98% rich — sell premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-24T14:51</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>iron_condor</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>230</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2662.16</v>
-      </c>
-      <c r="H8" t="n">
-        <v>42.65</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Slightly Bearish</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2660</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3100</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.0036</v>
-      </c>
-      <c r="S8" t="n">
-        <v>16.65</v>
-      </c>
-      <c r="T8" t="n">
-        <v>98.34999999999999</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>IV rank 94% rich — sell premium</t>
+          <t>IV rank 91% rich — sell premium</t>
         </is>
       </c>
     </row>
@@ -100475,7 +101777,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Generated 2026-09-24T22:48:38.476063 UTC · PAPER trades · $1000 account</t>
+          <t>Generated 2026-09-25T22:55:38.644182 UTC · PAPER trades · $1000 account</t>
         </is>
       </c>
     </row>
